--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -799,7 +799,7 @@
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
         <v>2.34</v>
@@ -820,7 +820,7 @@
         <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>14</v>
@@ -835,10 +835,10 @@
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>18.5</v>
@@ -874,7 +874,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
         <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
@@ -963,22 +963,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
         <v>1.83</v>
@@ -987,134 +987,134 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="K7" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>5.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H11" t="n">
         <v>1.77</v>
@@ -2518,7 +2518,7 @@
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
         <v>6.2</v>
@@ -4067,7 +4067,7 @@
         <v>7.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
         <v>3.65</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
         <v>7.8</v>
@@ -4264,7 +4264,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 11:45:35</t>
+          <t>2026-03-15 14:02:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -784,7 +784,7 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.14</v>
@@ -835,13 +835,13 @@
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
         <v>48</v>
@@ -859,7 +859,7 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
@@ -871,7 +871,7 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
         <v>5.2</v>
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>5</v>
@@ -913,14 +913,14 @@
         <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG2" t="n">
         <v>19</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
@@ -966,19 +966,19 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.83</v>
@@ -987,134 +987,134 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH3" t="n">
         <v>28</v>
       </c>
-      <c r="Z3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>34</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.02</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.08</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.87</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.92</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.12</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.96</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.1</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.06</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.08</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.24</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>13.5</v>
       </c>
       <c r="I4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
         <v>7.2</v>
@@ -1163,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1175,13 +1175,13 @@
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
         <v>2.2</v>
@@ -1190,22 +1190,22 @@
         <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X4" t="n">
         <v>34</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1253,13 +1253,13 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AS4" t="n">
         <v>2.34</v>
@@ -1271,51 +1271,51 @@
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AW4" t="n">
         <v>2.78</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>3.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BF4" t="n">
         <v>3.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.78</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Jagiellonia Bialystock</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
         <v>14.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,184 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.76</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.63</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.77</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>1.84</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2.98</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -3076,25 +3076,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VVV Venlo</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.75</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.92</v>
-      </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>240</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>240</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>240</v>
       </c>
       <c r="J16" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>1.27</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,33 +3653,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>4.1</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>2.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,66 +3847,66 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S. San Lorenzo</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2 Mayo de PJ</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G18" t="n">
-        <v>420</v>
+        <v>1.55</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="n">
-        <v>420</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>5.8</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,378 +4235,1348 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7.8</v>
       </c>
-      <c r="J20" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 14:02:17</t>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>S. San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2 Mayo de PJ</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>420</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>420</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Newells</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Olimpia</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q26" t="n">
         <v>1.01</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-03-15 14:02:17</t>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-15 16:15:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,7 +778,7 @@
         <v>1.36</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
         <v>4.2</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
@@ -838,10 +838,10 @@
         <v>19.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>48</v>
@@ -850,13 +850,13 @@
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
         <v>18</v>
@@ -871,10 +871,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>20</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>5.1</v>
@@ -1354,10 +1354,10 @@
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
@@ -1372,25 +1372,25 @@
         <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X5" t="n">
         <v>34</v>
@@ -1399,19 +1399,19 @@
         <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
         <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>50</v>
@@ -1447,7 +1447,7 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
@@ -1468,7 +1468,7 @@
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1480,7 +1480,7 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1498,11 +1498,11 @@
         <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
         <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
         <v>7.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
         <v>1.94</v>
@@ -1766,19 +1766,19 @@
         <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1951,10 +1951,10 @@
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I9" t="n">
         <v>14.5</v>
@@ -2133,16 +2133,16 @@
         <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.36</v>
@@ -2151,134 +2151,134 @@
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H11" t="n">
         <v>2.52</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.3</v>
-      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
         <v>6.2</v>
@@ -2709,22 +2709,22 @@
         <v>1.84</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
         <v>1.73</v>
@@ -2733,134 +2733,134 @@
         <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.4</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
         <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
         <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
         <v>5.1</v>
@@ -3297,16 +3297,16 @@
         <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
         <v>2.76</v>
@@ -3315,134 +3315,134 @@
         <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="G16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.39</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I16" t="n">
-        <v>240</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>950</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.27</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
         <v>4.1</v>
@@ -3685,16 +3685,16 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P17" t="n">
         <v>2.78</v>
@@ -3703,141 +3703,141 @@
         <v>1.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="G18" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="Z18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
         <v>15.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>27</v>
+        <v>2.78</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>2.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>42</v>
+        <v>3.05</v>
       </c>
       <c r="AS18" t="n">
-        <v>42</v>
+        <v>3.05</v>
       </c>
       <c r="AT18" t="n">
-        <v>11</v>
+        <v>2.44</v>
       </c>
       <c r="AU18" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>19</v>
+        <v>2.92</v>
       </c>
       <c r="AW18" t="n">
-        <v>50</v>
+        <v>3.05</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>2.42</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>2.54</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>2.86</v>
       </c>
       <c r="BA18" t="n">
-        <v>44</v>
+        <v>3.05</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>2.58</v>
       </c>
       <c r="BC18" t="n">
-        <v>12.5</v>
+        <v>2.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>2.92</v>
       </c>
       <c r="BE18" t="n">
-        <v>36</v>
+        <v>3.05</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="BG18" t="n">
-        <v>46</v>
+        <v>3.05</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="G19" t="n">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y19" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>46</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>19.5</v>
+        <v>1.86</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>40</v>
+        <v>1.85</v>
       </c>
       <c r="AS19" t="n">
-        <v>18.5</v>
+        <v>2</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>1.82</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>1.78</v>
       </c>
       <c r="AW19" t="n">
-        <v>55</v>
+        <v>1.89</v>
       </c>
       <c r="AX19" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="AZ19" t="n">
-        <v>28</v>
+        <v>1.84</v>
       </c>
       <c r="BA19" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BC19" t="n">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H20" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>7.2</v>
+        <v>1.84</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X20" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>30</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AK20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL20" t="n">
         <v>55</v>
       </c>
-      <c r="AB20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>25</v>
-      </c>
       <c r="AM20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>2.06</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18.5</v>
+        <v>2.08</v>
       </c>
       <c r="AR20" t="n">
-        <v>24</v>
+        <v>2.28</v>
       </c>
       <c r="AS20" t="n">
-        <v>42</v>
+        <v>2.28</v>
       </c>
       <c r="AT20" t="n">
-        <v>16.5</v>
+        <v>1.93</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>1.93</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>2.12</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>2.24</v>
       </c>
       <c r="AX20" t="n">
-        <v>16.5</v>
+        <v>2.02</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>1.99</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>2.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>24</v>
+        <v>2.24</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>2.12</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>2.12</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>2.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>38</v>
+        <v>2.28</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>2.28</v>
       </c>
       <c r="BG20" t="n">
-        <v>13.5</v>
+        <v>2.28</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>2.92</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
         <v>1.7</v>
       </c>
-      <c r="G22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
         <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S. San Lorenzo</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2 Mayo de PJ</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>420</v>
+        <v>3.3</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I23" t="n">
-        <v>420</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I24" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>2.78</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,378 +5205,1736 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>13</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N25" t="n">
         <v>5</v>
       </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 16:15:49</t>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Paris St-G</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X26" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>La Luz FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Ecu)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>S. San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2 Mayo de PJ</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>420</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>420</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K30" t="n">
+        <v>950</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Newells</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Olimpia</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-03-15 16:15:49</t>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-15 18:28:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
@@ -790,7 +790,7 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
         <v>1.45</v>
@@ -799,7 +799,7 @@
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
         <v>2.34</v>
@@ -871,10 +871,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -951,70 +951,70 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H3" t="n">
         <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
         <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB3" t="n">
         <v>9.199999999999999</v>
@@ -1023,16 +1023,16 @@
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -1041,46 +1041,46 @@
         <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX3" t="n">
         <v>8</v>
@@ -1092,7 +1092,7 @@
         <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1101,20 +1101,20 @@
         <v>16</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>8</v>
@@ -1184,13 +1184,13 @@
         <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
         <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
         <v>1.06</v>
@@ -1253,28 +1253,28 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.78</v>
+        <v>1.67</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1283,13 +1283,13 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC4" t="n">
         <v>7</v>
@@ -1298,17 +1298,17 @@
         <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.78</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
         <v>3.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -1372,10 +1372,10 @@
         <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S5" t="n">
         <v>2.14</v>
@@ -1384,7 +1384,7 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
@@ -1417,7 +1417,7 @@
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1447,7 +1447,7 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
         <v>1.73</v>
@@ -1545,7 +1545,7 @@
         <v>7.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
         <v>1.94</v>
@@ -1766,7 +1766,7 @@
         <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
         <v>1.71</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
         <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.33</v>
+        <v>2.74</v>
       </c>
       <c r="H9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>10.5</v>
       </c>
-      <c r="I9" t="n">
+      <c r="AR9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX9" t="n">
         <v>14.5</v>
       </c>
-      <c r="J9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.9</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>380</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BG9" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>12.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>4.1</v>
       </c>
       <c r="X10" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="AJ10" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AN10" t="n">
-        <v>36</v>
+        <v>5.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2494,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -2524,149 +2524,149 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG11" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AH11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>42</v>
       </c>
-      <c r="AB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>60</v>
-      </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS11" t="n">
         <v>48</v>
       </c>
-      <c r="AO11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>32</v>
-      </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="n">
         <v>10</v>
       </c>
-      <c r="AW11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
         <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.77</v>
+        <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>1.84</v>
+        <v>2.82</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2724,150 +2724,150 @@
         <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P12" t="n">
         <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
         <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>13</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AR12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="AW12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB12" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC12" t="n">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.9</v>
+        <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>25</v>
       </c>
-      <c r="AA13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>42</v>
-      </c>
       <c r="AK13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>2.44</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>2.28</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>2.34</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>2.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>2.26</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>2.12</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>2.24</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>2.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>2.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>2.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.26</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>6.4</v>
       </c>
       <c r="I16" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
@@ -3581,28 +3581,28 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AU16" t="n">
         <v>2.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AX16" t="n">
         <v>2.2</v>
@@ -3611,39 +3611,39 @@
         <v>2.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BB16" t="n">
         <v>2.22</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.22</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>1.84</v>
       </c>
       <c r="J17" t="n">
         <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>6.4</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X17" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>20</v>
-      </c>
       <c r="AR17" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX17" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AY17" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H18" t="n">
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -3891,34 +3891,34 @@
         <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
         <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,22 +3927,22 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11</v>
-      </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>38</v>
@@ -3954,7 +3954,7 @@
         <v>15.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
@@ -3963,75 +3963,75 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.44</v>
+        <v>1.81</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,153 +4079,153 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="O19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.22</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="T19" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
         <v>20</v>
       </c>
-      <c r="AC19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.85</v>
+        <v>2.58</v>
       </c>
       <c r="AS19" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.89</v>
+        <v>2.52</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="BB19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BD19" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="BE19" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="BF19" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="BG19" t="n">
-        <v>2</v>
+        <v>2.58</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X20" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT20" t="n">
         <v>1.82</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="AU20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>1.84</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X20" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BA20" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H21" t="n">
         <v>2.44</v>
       </c>
       <c r="I21" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
         <v>4.6</v>
@@ -4482,7 +4482,7 @@
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T21" t="n">
         <v>1.36</v>
@@ -4491,10 +4491,10 @@
         <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X21" t="n">
         <v>38</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H23" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K23" t="n">
         <v>3.85</v>
@@ -4861,7 +4861,7 @@
         <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
         <v>1.92</v>
@@ -4879,10 +4879,10 @@
         <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AR23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>3.55</v>
       </c>
-      <c r="AS23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BA23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
         <v>3.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>5.7</v>
       </c>
       <c r="J24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K24" t="n">
         <v>5.7</v>
@@ -5049,13 +5049,13 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q24" t="n">
         <v>1.53</v>
@@ -5064,13 +5064,13 @@
         <v>1.7</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V24" t="n">
         <v>1.21</v>
@@ -5079,25 +5079,25 @@
         <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA24" t="n">
         <v>140</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
@@ -5115,13 +5115,13 @@
         <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
         <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
         <v>80</v>
@@ -5133,10 +5133,10 @@
         <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR24" t="n">
         <v>44</v>
@@ -5148,7 +5148,7 @@
         <v>11.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV24" t="n">
         <v>19.5</v>
@@ -5163,19 +5163,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB24" t="n">
         <v>13.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
         <v>65</v>
@@ -5184,11 +5184,11 @@
         <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>1.32</v>
       </c>
       <c r="G25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H25" t="n">
         <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -5237,7 +5237,7 @@
         <v>6.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
@@ -5249,7 +5249,7 @@
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
         <v>1.69</v>
@@ -5258,13 +5258,13 @@
         <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T25" t="n">
         <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
         <v>1.08</v>
@@ -5336,10 +5336,10 @@
         <v>46</v>
       </c>
       <c r="AS25" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU25" t="n">
         <v>12</v>
@@ -5348,7 +5348,7 @@
         <v>36</v>
       </c>
       <c r="AW25" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AX25" t="n">
         <v>7.2</v>
@@ -5360,7 +5360,7 @@
         <v>28</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BB25" t="n">
         <v>9.199999999999999</v>
@@ -5369,10 +5369,10 @@
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
         <v>4.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5416,22 +5416,22 @@
         <v>2.16</v>
       </c>
       <c r="G26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
@@ -5452,7 +5452,7 @@
         <v>1.88</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T26" t="n">
         <v>1.46</v>
@@ -5464,7 +5464,7 @@
         <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -5476,10 +5476,10 @@
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5506,13 +5506,13 @@
         <v>29</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
         <v>23</v>
       </c>
       <c r="AM26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN26" t="n">
         <v>8.4</v>
@@ -5545,7 +5545,7 @@
         <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>11</v>
@@ -5554,13 +5554,13 @@
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD26" t="n">
         <v>21</v>
@@ -5572,11 +5572,11 @@
         <v>7.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G27" t="n">
         <v>4.1</v>
@@ -5616,7 +5616,7 @@
         <v>2.46</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J27" t="n">
         <v>2.62</v>
@@ -5640,13 +5640,13 @@
         <v>1.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
         <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5655,7 +5655,7 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.96</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
@@ -5816,19 +5816,19 @@
         <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.63</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
@@ -5837,25 +5837,25 @@
         <v>2.34</v>
       </c>
       <c r="R28" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
         <v>1000</v>
@@ -5864,31 +5864,31 @@
         <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
@@ -5900,7 +5900,7 @@
         <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H29" t="n">
         <v>5.7</v>
@@ -6013,16 +6013,16 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P29" t="n">
         <v>1.76</v>
@@ -6031,134 +6031,134 @@
         <v>1.96</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
@@ -6189,177 +6189,177 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G30" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="H30" t="n">
         <v>2.5</v>
       </c>
       <c r="I30" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="J30" t="n">
-        <v>1.02</v>
+        <v>2.56</v>
       </c>
       <c r="K30" t="n">
         <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>2.94</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P31" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>1.39</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="H32" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,184 +6757,766 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 18:28:31</t>
+          <t>2026-03-15 20:40:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-15 20:40:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-15 20:40:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Trujillanos</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K36" t="n">
+        <v>950</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-15 20:40:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
         <v>2.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>3.3</v>
@@ -790,13 +790,13 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.67</v>
@@ -814,7 +814,7 @@
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -823,43 +823,43 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
@@ -871,10 +871,10 @@
         <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>19</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.85</v>
@@ -969,7 +969,7 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -978,7 +978,7 @@
         <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
         <v>1.88</v>
@@ -993,7 +993,7 @@
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.9</v>
@@ -1002,10 +1002,10 @@
         <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1014,25 +1014,25 @@
         <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -1041,19 +1041,19 @@
         <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1062,59 +1062,59 @@
         <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>1.27</v>
       </c>
       <c r="H4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="I4" t="n">
         <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
         <v>8</v>
@@ -1187,7 +1187,7 @@
         <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
         <v>1.8</v>
@@ -1199,7 +1199,7 @@
         <v>4.7</v>
       </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
         <v>55</v>
@@ -1211,104 +1211,104 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AD4" t="n">
         <v>60</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ4" t="n">
         <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.79</v>
+        <v>5.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.66</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.76</v>
+        <v>5.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.66</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I5" t="n">
         <v>5</v>
       </c>
-      <c r="I5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K5" t="n">
         <v>5.3</v>
@@ -1372,13 +1372,13 @@
         <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
         <v>1.58</v>
@@ -1387,7 +1387,7 @@
         <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
         <v>2.52</v>
@@ -1405,7 +1405,7 @@
         <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
         <v>12</v>
@@ -1447,7 +1447,7 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
@@ -1462,7 +1462,7 @@
         <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
@@ -1498,11 +1498,11 @@
         <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>7.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1566,7 +1566,7 @@
         <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1578,46 +1578,46 @@
         <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
         <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
         <v>140</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>140</v>
@@ -1629,13 +1629,13 @@
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>210</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>220</v>
@@ -1644,13 +1644,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -1659,10 +1659,10 @@
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
         <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
         <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
@@ -1754,13 +1754,13 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -1778,119 +1778,119 @@
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL7" t="n">
         <v>44</v>
       </c>
-      <c r="AA7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.5</v>
+        <v>2.38</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.199999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>2.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>16</v>
+        <v>2.38</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>2.28</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>2.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
         <v>2.64</v>
@@ -1939,7 +1939,7 @@
         <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -1951,7 +1951,7 @@
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
         <v>2.14</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.07</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>3.9</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>16.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.32</v>
       </c>
-      <c r="H10" t="n">
+      <c r="P10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y10" t="n">
         <v>12.5</v>
       </c>
-      <c r="I10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>46</v>
-      </c>
       <c r="Z10" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI10" t="n">
         <v>55</v>
       </c>
-      <c r="AE10" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK10" t="n">
         <v>32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>350</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
         <v>3.7</v>
@@ -2518,13 +2518,13 @@
         <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
         <v>2.88</v>
@@ -2536,16 +2536,16 @@
         <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -2560,19 +2560,19 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>16</v>
@@ -2581,13 +2581,13 @@
         <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>70</v>
@@ -2596,31 +2596,31 @@
         <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
         <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -2632,10 +2632,10 @@
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2644,29 +2644,29 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
@@ -2727,7 +2727,7 @@
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
         <v>2.16</v>
@@ -2745,34 +2745,34 @@
         <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W12" t="n">
         <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
         <v>42</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2781,19 +2781,19 @@
         <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
         <v>42</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
         <v>140</v>
@@ -2805,10 +2805,10 @@
         <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2817,16 +2817,16 @@
         <v>32</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX12" t="n">
         <v>15.5</v>
@@ -2835,32 +2835,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC12" t="n">
         <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>44</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>34</v>
+        <v>5.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2921,22 +2921,22 @@
         <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>1.64</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.19</v>
@@ -2945,116 +2945,116 @@
         <v>2.32</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.44</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.28</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.34</v>
+        <v>4.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.26</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.12</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.24</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.38</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.22</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.22</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.3</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5</v>
       </c>
-      <c r="BG13" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
         <v>4.1</v>
@@ -3100,7 +3100,7 @@
         <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3124,37 +3124,37 @@
         <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="T14" t="n">
         <v>1.43</v>
       </c>
       <c r="U14" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y14" t="n">
         <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>970</v>
@@ -3169,13 +3169,13 @@
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
         <v>22</v>
@@ -3193,52 +3193,52 @@
         <v>23</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU14" t="n">
         <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18</v>
-      </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
         <v>1.92</v>
@@ -3288,7 +3288,7 @@
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
@@ -3303,146 +3303,146 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>2.76</v>
+        <v>1.63</v>
       </c>
       <c r="O15" t="n">
         <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>2.76</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T15" t="n">
         <v>1.35</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>2.08</v>
       </c>
       <c r="X15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z15" t="n">
         <v>46</v>
       </c>
-      <c r="Y15" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>55</v>
-      </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD15" t="n">
         <v>22</v>
       </c>
-      <c r="AC15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>26</v>
       </c>
-      <c r="AE15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="n">
         <v>30</v>
       </c>
-      <c r="AK15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>36</v>
-      </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.46</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.56</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.38</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.52</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.26</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.42</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.38</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.44</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.62</v>
+        <v>19.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G16" t="n">
         <v>1.38</v>
       </c>
       <c r="H16" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="J16" t="n">
         <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>8.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,22 +3497,22 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,13 +3521,13 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3539,104 +3539,104 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H17" t="n">
         <v>1.78</v>
@@ -3679,13 +3679,13 @@
         <v>1.84</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3697,7 +3697,7 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>2.22</v>
@@ -3712,16 +3712,16 @@
         <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W17" t="n">
         <v>1.19</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
         <v>8.199999999999999</v>
@@ -3730,16 +3730,16 @@
         <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
@@ -3748,10 +3748,10 @@
         <v>55</v>
       </c>
       <c r="AG17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
         <v>55</v>
@@ -3772,7 +3772,7 @@
         <v>170</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -3784,10 +3784,10 @@
         <v>8.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
         <v>7.4</v>
@@ -3796,41 +3796,41 @@
         <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>5.3</v>
       </c>
-      <c r="AY17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BA17" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -3861,64 +3861,64 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G18" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>140</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="X18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,37 +3927,37 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4061,28 +4061,28 @@
         <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
         <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P19" t="n">
         <v>1.84</v>
@@ -4091,37 +4091,37 @@
         <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
         <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>12</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD19" t="n">
         <v>2.28</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="BE19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BF19" t="n">
         <v>2.12</v>
       </c>
-      <c r="AU19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="H20" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4273,67 +4273,67 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="X20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H21" t="n">
         <v>2.44</v>
@@ -4455,91 +4455,91 @@
         <v>2.76</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
         <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
         <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y21" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB21" t="n">
         <v>24</v>
       </c>
-      <c r="Z21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>25</v>
-      </c>
       <c r="AC21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
         <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM21" t="n">
         <v>70</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.16</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.04</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.14</v>
+        <v>16.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.18</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.16</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.18</v>
+        <v>21</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.22</v>
+        <v>34</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
         <v>3.85</v>
@@ -4655,28 +4655,28 @@
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
         <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4688,52 +4688,52 @@
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB22" t="n">
         <v>19.5</v>
       </c>
-      <c r="AS22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ22" t="n">
+      <c r="BC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE22" t="n">
         <v>2.44</v>
       </c>
-      <c r="BA22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BF22" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -4834,55 +4834,55 @@
         <v>2.62</v>
       </c>
       <c r="G23" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J23" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4900,13 +4900,13 @@
         <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
         <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF23" t="n">
         <v>23</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA23" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
       <c r="BB23" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>1.55</v>
       </c>
       <c r="H24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I24" t="n">
         <v>5.6</v>
       </c>
-      <c r="I24" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J24" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K24" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -5049,7 +5049,7 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
@@ -5061,10 +5061,10 @@
         <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S24" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
         <v>1.68</v>
@@ -5076,7 +5076,7 @@
         <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="X24" t="n">
         <v>36</v>
@@ -5106,10 +5106,10 @@
         <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
@@ -5133,7 +5133,7 @@
         <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ24" t="n">
         <v>24</v>
@@ -5142,7 +5142,7 @@
         <v>44</v>
       </c>
       <c r="AS24" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT24" t="n">
         <v>11.5</v>
@@ -5178,7 +5178,7 @@
         <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF24" t="n">
         <v>5.4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>1.33</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I25" t="n">
         <v>12.5</v>
@@ -5255,10 +5255,10 @@
         <v>1.69</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
         <v>2.2</v>
@@ -5288,7 +5288,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
         <v>44</v>
@@ -5318,7 +5318,7 @@
         <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
         <v>5.1</v>
@@ -5333,16 +5333,16 @@
         <v>30</v>
       </c>
       <c r="AR25" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AS25" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV25" t="n">
         <v>36</v>
@@ -5357,7 +5357,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA25" t="n">
         <v>44</v>
@@ -5369,7 +5369,7 @@
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
         <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -5476,10 +5476,10 @@
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5503,7 +5503,7 @@
         <v>28</v>
       </c>
       <c r="AJ26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK26" t="n">
         <v>18.5</v>
@@ -5524,13 +5524,13 @@
         <v>30</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT26" t="n">
         <v>17</v>
@@ -5551,10 +5551,10 @@
         <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>27</v>
@@ -5572,11 +5572,11 @@
         <v>7.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>4.1</v>
@@ -5616,7 +5616,7 @@
         <v>2.46</v>
       </c>
       <c r="I27" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="J27" t="n">
         <v>2.62</v>
@@ -5625,16 +5625,16 @@
         <v>3.25</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
         <v>1.47</v>
@@ -5643,55 +5643,55 @@
         <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
         <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5715,62 +5715,62 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.96</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
@@ -5813,7 +5813,7 @@
         <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
         <v>3.6</v>
@@ -5822,7 +5822,7 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
         <v>2.86</v>
@@ -5837,28 +5837,28 @@
         <v>2.34</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="X28" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
         <v>1000</v>
@@ -5870,7 +5870,7 @@
         <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>23</v>
@@ -5909,16 +5909,16 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5927,44 +5927,44 @@
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AY28" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE28" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.7</v>
       </c>
       <c r="BF28" t="n">
         <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>1.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
         <v>4.1</v>
@@ -6016,149 +6016,149 @@
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>1.76</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T29" t="n">
         <v>1.96</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.79</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="V29" t="n">
         <v>1.18</v>
       </c>
       <c r="W29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X29" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK29" t="n">
         <v>25</v>
       </c>
-      <c r="Z29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.76</v>
+        <v>4.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="AX29" t="n">
         <v>8</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.52</v>
+        <v>16.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.76</v>
+        <v>4.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>2.94</v>
       </c>
       <c r="J31" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="K31" t="n">
         <v>950</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
         <v>1.82</v>
       </c>
       <c r="H32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -6598,7 +6598,7 @@
         <v>1.54</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N32" t="n">
         <v>2.72</v>
@@ -6610,13 +6610,13 @@
         <v>1.58</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R32" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
         <v>2.26</v>
@@ -6625,31 +6625,31 @@
         <v>1.66</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
         <v>2.2</v>
       </c>
       <c r="X32" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA32" t="n">
         <v>280</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE32" t="n">
         <v>160</v>
@@ -6658,28 +6658,28 @@
         <v>11</v>
       </c>
       <c r="AG32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI32" t="n">
         <v>180</v>
       </c>
       <c r="AJ32" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM32" t="n">
         <v>300</v>
       </c>
       <c r="AN32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO32" t="n">
         <v>300</v>
@@ -6691,10 +6691,10 @@
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
@@ -6706,7 +6706,7 @@
         <v>19</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6718,7 +6718,7 @@
         <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BB32" t="n">
         <v>16.5</v>
@@ -6727,20 +6727,20 @@
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>44</v>
+        <v>4.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BF32" t="n">
         <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>110</v>
       </c>
       <c r="H33" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="I33" t="n">
         <v>110</v>
@@ -6795,22 +6795,22 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="R33" t="n">
         <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6822,7 +6822,7 @@
         <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
         <v>5.9</v>
@@ -6986,13 +6986,13 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
         <v>1.67</v>
@@ -7001,134 +7001,134 @@
         <v>2.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V34" t="n">
         <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7177,152 +7177,152 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>
@@ -7365,158 +7365,158 @@
         <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P36" t="n">
         <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-15 20:40:25</t>
+          <t>2026-03-15 22:51:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH36"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,19 +760,19 @@
         <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -805,10 +805,10 @@
         <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>8.6</v>
@@ -838,10 +838,10 @@
         <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
         <v>50</v>
@@ -856,7 +856,7 @@
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
         <v>20</v>
@@ -874,7 +874,7 @@
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
         <v>14.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1065,7 +1065,7 @@
         <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
         <v>5.8</v>
@@ -1101,20 +1101,20 @@
         <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
         <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>11.5</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J4" t="n">
         <v>6.6</v>
@@ -1178,7 +1178,7 @@
         <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.71</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
         <v>6</v>
@@ -1265,22 +1265,22 @@
         <v>6.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
         <v>4.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>5.4</v>
@@ -1292,10 +1292,10 @@
         <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE4" t="n">
         <v>6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.9</v>
       </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
@@ -1369,7 +1369,7 @@
         <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.46</v>
@@ -1447,7 +1447,7 @@
         <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
@@ -1456,7 +1456,7 @@
         <v>40</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
@@ -1465,7 +1465,7 @@
         <v>11.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW5" t="n">
         <v>44</v>
@@ -1477,7 +1477,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
         <v>38</v>
@@ -1486,23 +1486,23 @@
         <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
         <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
         <v>1.75</v>
@@ -1548,7 +1548,7 @@
         <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.43</v>
@@ -1617,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
         <v>140</v>
@@ -1647,10 +1647,10 @@
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -1662,7 +1662,7 @@
         <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.9</v>
@@ -1745,10 +1745,10 @@
         <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
         <v>4.4</v>
@@ -1760,7 +1760,7 @@
         <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -1781,116 +1781,116 @@
         <v>2.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.38</v>
+        <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.18</v>
+        <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.38</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.36</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.46</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H9" t="n">
         <v>11.5</v>
@@ -2127,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="n">
         <v>6.4</v>
@@ -2157,16 +2157,16 @@
         <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
         <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X9" t="n">
         <v>27</v>
@@ -2220,7 +2220,7 @@
         <v>5.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AP9" t="n">
         <v>5.4</v>
@@ -2250,13 +2250,13 @@
         <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>5.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
         <v>9</v>
@@ -2274,11 +2274,11 @@
         <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         <v>2.76</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>13.5</v>
@@ -2853,14 +2853,14 @@
         <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BG12" t="n">
         <v>5.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.63</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.28</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>1.97</v>
       </c>
       <c r="T13" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>26</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY13" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
         <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H14" t="n">
         <v>3.5</v>
@@ -3124,7 +3124,7 @@
         <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
         <v>1.43</v>
@@ -3136,7 +3136,7 @@
         <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
@@ -3193,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
         <v>4.9</v>
@@ -3217,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY14" t="n">
         <v>9.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VVV Venlo</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>1.97</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AB15" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
         <v>12</v>
       </c>
-      <c r="AD15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
         <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC15" t="n">
         <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
         <v>1.38</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="O16" t="n">
         <v>1.09</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
         <v>3.35</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>140</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>140</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S19" t="n">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
         <v>2.44</v>
       </c>
       <c r="I21" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
         <v>4.6</v>
@@ -4476,7 +4476,7 @@
         <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.64</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>3.15</v>
@@ -4661,34 +4661,34 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
         <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4724,7 +4724,7 @@
         <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="n">
         <v>36</v>
@@ -4760,13 +4760,13 @@
         <v>1.98</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AV22" t="n">
         <v>2.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AX22" t="n">
         <v>9.6</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J24" t="n">
         <v>5.8</v>
@@ -5049,7 +5049,7 @@
         <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
@@ -5058,13 +5058,13 @@
         <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R24" t="n">
         <v>1.71</v>
       </c>
       <c r="S24" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
         <v>1.68</v>
@@ -5103,7 +5103,7 @@
         <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
         <v>9.800000000000001</v>
@@ -5172,23 +5172,23 @@
         <v>13.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
         <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
         <v>11.5</v>
       </c>
       <c r="I25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.32</v>
@@ -5252,7 +5252,7 @@
         <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.54</v>
@@ -5261,13 +5261,13 @@
         <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
         <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W25" t="n">
         <v>4</v>
@@ -5279,7 +5279,7 @@
         <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA25" t="n">
         <v>580</v>
@@ -5288,7 +5288,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
         <v>44</v>
@@ -5315,13 +5315,13 @@
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>190</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO25" t="n">
         <v>270</v>
@@ -5333,10 +5333,10 @@
         <v>30</v>
       </c>
       <c r="AR25" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AS25" t="n">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="AT25" t="n">
         <v>8.199999999999999</v>
@@ -5363,7 +5363,7 @@
         <v>44</v>
       </c>
       <c r="BB25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC25" t="n">
         <v>13.5</v>
@@ -5372,7 +5372,7 @@
         <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF25" t="n">
         <v>4.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -5527,10 +5527,10 @@
         <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT26" t="n">
         <v>17</v>
@@ -5542,7 +5542,7 @@
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>18</v>
@@ -5554,7 +5554,7 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>27</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G27" t="n">
         <v>4.1</v>
@@ -5619,7 +5619,7 @@
         <v>2.86</v>
       </c>
       <c r="J27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K27" t="n">
         <v>3.25</v>
@@ -5628,25 +5628,25 @@
         <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="P27" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
@@ -5655,10 +5655,10 @@
         <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X27" t="n">
         <v>9.199999999999999</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -5816,13 +5816,13 @@
         <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
         <v>2.86</v>
@@ -5837,10 +5837,10 @@
         <v>2.34</v>
       </c>
       <c r="R28" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
         <v>2.04</v>
@@ -5849,10 +5849,10 @@
         <v>1.81</v>
       </c>
       <c r="V28" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W28" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>S. San Lorenzo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>2 Mayo de PJ</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="G29" t="n">
-        <v>1.87</v>
+        <v>500</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>500</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="X29" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,28 +6180,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>S. San Lorenzo</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2 Mayo de PJ</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="I30" t="n">
-        <v>500</v>
+        <v>2.94</v>
       </c>
       <c r="J30" t="n">
-        <v>2.56</v>
+        <v>1.56</v>
       </c>
       <c r="K30" t="n">
         <v>950</v>
@@ -6216,19 +6216,19 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6237,10 +6237,10 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H31" t="n">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="J31" t="n">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>1.39</v>
+        <v>3.8</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6598,7 @@
         <v>1.54</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
         <v>2.72</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -6989,7 +6989,7 @@
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>1.41</v>
@@ -7013,31 +7013,31 @@
         <v>1.77</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="X34" t="n">
         <v>12.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA34" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC34" t="n">
         <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE34" t="n">
         <v>85</v>
@@ -7052,37 +7052,37 @@
         <v>23</v>
       </c>
       <c r="AI34" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ34" t="n">
         <v>30</v>
       </c>
       <c r="AK34" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL34" t="n">
         <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN34" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AO34" t="n">
         <v>130</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ34" t="n">
         <v>9.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT34" t="n">
         <v>6.6</v>
@@ -7091,10 +7091,10 @@
         <v>6.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX34" t="n">
         <v>9.800000000000001</v>
@@ -7103,32 +7103,32 @@
         <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BA34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB34" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC34" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF34" t="n">
         <v>14</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
         <v>1.24</v>
@@ -7516,7 +7516,783 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-15 22:51:24</t>
+          <t>2026-03-16 01:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CD Leones del Norte</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LDU</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-16 01:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-16 01:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G39" t="n">
+        <v>110</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I39" t="n">
+        <v>110</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K39" t="n">
+        <v>950</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-16 01:03:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-16 01:03:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -766,7 +766,7 @@
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -775,25 +775,25 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -802,13 +802,13 @@
         <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
@@ -916,11 +916,11 @@
         <v>14.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -957,46 +957,46 @@
         <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
         <v>7.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.92</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.16</v>
@@ -1014,16 +1014,16 @@
         <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
@@ -1035,22 +1035,22 @@
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
         <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
         <v>11.5</v>
@@ -1065,13 +1065,13 @@
         <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>8.199999999999999</v>
@@ -1092,29 +1092,29 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H4" t="n">
         <v>11.5</v>
@@ -1157,7 +1157,7 @@
         <v>15.5</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>8</v>
@@ -1178,25 +1178,25 @@
         <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
         <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1205,34 +1205,34 @@
         <v>55</v>
       </c>
       <c r="Z4" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AF4" t="n">
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ4" t="n">
         <v>970</v>
@@ -1244,71 +1244,71 @@
         <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
         <v>4.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
       </c>
       <c r="AY4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.4</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
         <v>4.8</v>
@@ -1396,7 +1396,7 @@
         <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z5" t="n">
         <v>48</v>
@@ -1480,7 +1480,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1578,7 +1578,7 @@
         <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1599,7 +1599,7 @@
         <v>270</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
@@ -1617,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>140</v>
@@ -1632,13 +1632,13 @@
         <v>55</v>
       </c>
       <c r="AM6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO6" t="n">
         <v>210</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>220</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1647,10 +1647,10 @@
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
@@ -1662,19 +1662,19 @@
         <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1686,17 +1686,17 @@
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
         <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H7" t="n">
         <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.34</v>
@@ -1760,7 +1760,7 @@
         <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
         <v>16.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
@@ -1936,7 +1936,7 @@
         <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H9" t="n">
         <v>11.5</v>
@@ -2127,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
         <v>6.4</v>
@@ -2139,25 +2139,25 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
         <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
         <v>1.79</v>
@@ -2166,10 +2166,10 @@
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>46</v>
@@ -2226,13 +2226,13 @@
         <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.199999999999999</v>
@@ -2265,7 +2265,7 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
         <v>6.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2309,40 +2309,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -2354,16 +2354,16 @@
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
@@ -2372,16 +2372,16 @@
         <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
         <v>40</v>
@@ -2411,7 +2411,7 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
         <v>38</v>
@@ -2426,10 +2426,10 @@
         <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2438,10 +2438,10 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
@@ -2450,29 +2450,29 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
         <v>16.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3.3</v>
@@ -2524,22 +2524,22 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
         <v>4.3</v>
@@ -2551,22 +2551,22 @@
         <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
         <v>10</v>
@@ -2575,22 +2575,22 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
         <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
         <v>42</v>
@@ -2605,13 +2605,13 @@
         <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
@@ -2644,29 +2644,29 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2721,19 +2721,19 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>3.9</v>
@@ -2742,10 +2742,10 @@
         <v>1.83</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
         <v>1.42</v>
@@ -2772,7 +2772,7 @@
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2793,10 +2793,10 @@
         <v>42</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
         <v>44</v>
@@ -2829,38 +2829,38 @@
         <v>5.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC12" t="n">
         <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
         <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H13" t="n">
         <v>3.95</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -2915,40 +2915,40 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.63</v>
+        <v>2.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="S13" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V13" t="n">
         <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
       </c>
       <c r="Y13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z13" t="n">
         <v>46</v>
@@ -2975,7 +2975,7 @@
         <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>48</v>
@@ -2990,7 +2990,7 @@
         <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
         <v>7.2</v>
@@ -2999,16 +2999,16 @@
         <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT13" t="n">
         <v>13</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>13</v>
@@ -3032,10 +3032,10 @@
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
@@ -3044,7 +3044,7 @@
         <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF13" t="n">
         <v>5.3</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G14" t="n">
         <v>2.22</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,31 +3109,31 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
         <v>1.82</v>
@@ -3145,7 +3145,7 @@
         <v>32</v>
       </c>
       <c r="Z14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
         <v>75</v>
@@ -3166,79 +3166,79 @@
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
         <v>25</v>
       </c>
       <c r="AM14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BA14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5.4</v>
       </c>
-      <c r="AT14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
         <v>4.1</v>
@@ -3300,7 +3300,7 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>4.7</v>
@@ -3309,22 +3309,22 @@
         <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
         <v>1.19</v>
@@ -3333,7 +3333,7 @@
         <v>2.32</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
         <v>27</v>
@@ -3393,10 +3393,10 @@
         <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
@@ -3420,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>14.5</v>
@@ -3432,7 +3432,7 @@
         <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
         <v>6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>6.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I17" t="n">
         <v>1.84</v>
@@ -3685,7 +3685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3697,22 +3697,22 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
         <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
         <v>2.18</v>
@@ -3757,16 +3757,16 @@
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AK17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL17" t="n">
         <v>120</v>
       </c>
       <c r="AM17" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
         <v>170</v>
@@ -3823,14 +3823,14 @@
         <v>6.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>1.82</v>
       </c>
       <c r="G18" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>6.2</v>
@@ -3897,10 +3897,10 @@
         <v>1.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T18" t="n">
         <v>1.86</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4055,40 +4055,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="H19" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>140</v>
+        <v>13.5</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R19" t="n">
         <v>1.08</v>
@@ -4103,10 +4103,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4318,7 +4318,7 @@
         <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.52</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H21" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>4.6</v>
@@ -4473,10 +4473,10 @@
         <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
         <v>1.64</v>
@@ -4485,10 +4485,10 @@
         <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U21" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V21" t="n">
         <v>1.56</v>
@@ -4497,10 +4497,10 @@
         <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
         <v>29</v>
@@ -4509,7 +4509,7 @@
         <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
         <v>13.5</v>
@@ -4521,10 +4521,10 @@
         <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
@@ -4554,25 +4554,25 @@
         <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AX21" t="n">
         <v>16.5</v>
@@ -4587,26 +4587,26 @@
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BC21" t="n">
         <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>21</v>
+        <v>2.36</v>
       </c>
       <c r="BE21" t="n">
-        <v>34</v>
+        <v>2.44</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>2.26</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4676,7 +4676,7 @@
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
         <v>1.89</v>
@@ -4724,13 +4724,13 @@
         <v>28</v>
       </c>
       <c r="AI22" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
         <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
         <v>60</v>
@@ -4757,28 +4757,28 @@
         <v>2.44</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AU22" t="n">
         <v>1.97</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AW22" t="n">
         <v>2.38</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BB22" t="n">
         <v>19.5</v>
@@ -4787,7 +4787,7 @@
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>2.36</v>
       </c>
       <c r="BE22" t="n">
         <v>2.44</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
@@ -4855,19 +4855,19 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
         <v>3.35</v>
@@ -4876,7 +4876,7 @@
         <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H24" t="n">
         <v>5.5</v>
@@ -5037,10 +5037,10 @@
         <v>5.7</v>
       </c>
       <c r="J24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K24" t="n">
         <v>5.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.27</v>
@@ -5064,10 +5064,10 @@
         <v>1.71</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U24" t="n">
         <v>2.38</v>
@@ -5076,16 +5076,16 @@
         <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y24" t="n">
         <v>28</v>
       </c>
       <c r="Z24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
         <v>140</v>
@@ -5097,19 +5097,19 @@
         <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>55</v>
@@ -5127,16 +5127,16 @@
         <v>80</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
         <v>44</v>
@@ -5154,7 +5154,7 @@
         <v>19.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
@@ -5163,10 +5163,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB24" t="n">
         <v>13.5</v>
@@ -5178,17 +5178,17 @@
         <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
         <v>44</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
         <v>11.5</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J25" t="n">
         <v>6.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.32</v>
@@ -5243,13 +5243,13 @@
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
         <v>1.7</v>
@@ -5258,7 +5258,7 @@
         <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T25" t="n">
         <v>2.18</v>
@@ -5267,7 +5267,7 @@
         <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
         <v>4</v>
@@ -5279,7 +5279,7 @@
         <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA25" t="n">
         <v>580</v>
@@ -5294,10 +5294,10 @@
         <v>44</v>
       </c>
       <c r="AE25" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
@@ -5315,13 +5315,13 @@
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
         <v>190</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO25" t="n">
         <v>270</v>
@@ -5330,16 +5330,16 @@
         <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR25" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AS25" t="n">
         <v>130</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU25" t="n">
         <v>12.5</v>
@@ -5369,20 +5369,20 @@
         <v>13.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
         <v>48</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5422,13 +5422,13 @@
         <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
         <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -5464,7 +5464,7 @@
         <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X26" t="n">
         <v>34</v>
@@ -5491,7 +5491,7 @@
         <v>28</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
@@ -5500,7 +5500,7 @@
         <v>14.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ26" t="n">
         <v>30</v>
@@ -5539,7 +5539,7 @@
         <v>10.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5551,7 +5551,7 @@
         <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>26</v>
@@ -5572,11 +5572,11 @@
         <v>7.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>4.1</v>
@@ -5619,7 +5619,7 @@
         <v>2.86</v>
       </c>
       <c r="J27" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="K27" t="n">
         <v>3.25</v>
@@ -5631,22 +5631,22 @@
         <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
@@ -5655,10 +5655,10 @@
         <v>1.71</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
         <v>9.199999999999999</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5801,64 +5801,64 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G28" t="n">
         <v>2.18</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V28" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
         <v>1000</v>
@@ -5867,19 +5867,19 @@
         <v>140</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
@@ -5888,7 +5888,7 @@
         <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
         <v>1000</v>
@@ -5900,7 +5900,7 @@
         <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
         <v>1000</v>
@@ -5909,16 +5909,16 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5927,44 +5927,44 @@
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY28" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>2.48</v>
       </c>
       <c r="G29" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="H29" t="n">
         <v>2.5</v>
       </c>
       <c r="I29" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="J29" t="n">
         <v>2.56</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>1.87</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I31" t="n">
         <v>6.2</v>
@@ -6398,7 +6398,7 @@
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,28 +6407,28 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U31" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V31" t="n">
         <v>1.19</v>
@@ -6437,7 +6437,7 @@
         <v>2.14</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y31" t="n">
         <v>970</v>
@@ -6449,25 +6449,25 @@
         <v>190</v>
       </c>
       <c r="AB31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG31" t="n">
         <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>110</v>
@@ -6485,68 +6485,68 @@
         <v>170</v>
       </c>
       <c r="AN31" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.85</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT31" t="n">
         <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF31" t="n">
         <v>4.4</v>
       </c>
-      <c r="BE31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG31" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
         <v>1.82</v>
@@ -6586,13 +6586,13 @@
         <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.54</v>
@@ -6613,7 +6613,7 @@
         <v>2.46</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -6637,16 +6637,16 @@
         <v>18.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB32" t="n">
         <v>7.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
         <v>32</v>
@@ -6661,40 +6661,40 @@
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ32" t="n">
         <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL32" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO32" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
@@ -6706,7 +6706,7 @@
         <v>19</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6718,7 +6718,7 @@
         <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB32" t="n">
         <v>16.5</v>
@@ -6727,20 +6727,20 @@
         <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
         <v>13.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H33" t="n">
         <v>2.66</v>
       </c>
       <c r="I33" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J33" t="n">
         <v>2.58</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
@@ -6977,7 +6977,7 @@
         <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K34" t="n">
         <v>3.4</v>
@@ -6989,40 +6989,40 @@
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U34" t="n">
         <v>1.77</v>
       </c>
       <c r="V34" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="X34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z34" t="n">
         <v>40</v>
@@ -7031,13 +7031,13 @@
         <v>150</v>
       </c>
       <c r="AB34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
         <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
         <v>85</v>
@@ -7055,7 +7055,7 @@
         <v>110</v>
       </c>
       <c r="AJ34" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
         <v>25</v>
@@ -7067,22 +7067,22 @@
         <v>150</v>
       </c>
       <c r="AN34" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AO34" t="n">
         <v>130</v>
       </c>
       <c r="AP34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT34" t="n">
         <v>6.6</v>
@@ -7091,44 +7091,44 @@
         <v>6.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF34" t="n">
         <v>14</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G37" t="n">
         <v>6.6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="I37" t="n">
         <v>2.18</v>
@@ -7589,10 +7589,10 @@
         <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V37" t="n">
         <v>1.85</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G38" t="n">
         <v>4.2</v>
@@ -7750,28 +7750,28 @@
         <v>2.42</v>
       </c>
       <c r="I38" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J38" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O38" t="n">
         <v>1.72</v>
       </c>
       <c r="P38" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q38" t="n">
         <v>3.35</v>
@@ -7780,16 +7780,16 @@
         <v>1.13</v>
       </c>
       <c r="S38" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="U38" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="V38" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W38" t="n">
         <v>1.31</v>
@@ -7807,7 +7807,7 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC38" t="n">
         <v>8.4</v>
@@ -7825,7 +7825,7 @@
         <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
         <v>110</v>
@@ -7849,16 +7849,16 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>5.8</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT38" t="n">
         <v>7.4</v>
@@ -7867,44 +7867,44 @@
         <v>6.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ38" t="n">
         <v>6</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB38" t="n">
         <v>50</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF38" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF38" t="n">
-        <v>7</v>
-      </c>
       <c r="BG38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>1.04</v>
       </c>
       <c r="G39" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H39" t="n">
         <v>1.04</v>
       </c>
       <c r="I39" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J39" t="n">
         <v>1.09</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G40" t="n">
         <v>3.3</v>
@@ -8153,7 +8153,7 @@
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O40" t="n">
         <v>1.42</v>
@@ -8171,16 +8171,16 @@
         <v>3.85</v>
       </c>
       <c r="T40" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U40" t="n">
         <v>1.7</v>
       </c>
       <c r="V40" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W40" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AX40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY40" t="n">
         <v>1.82</v>
       </c>
-      <c r="AY40" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AZ40" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BC40" t="n">
         <v>1.95</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH40"/>
+  <dimension ref="A1:BH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -775,34 +775,34 @@
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T2" t="n">
         <v>1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
@@ -817,7 +817,7 @@
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
@@ -847,34 +847,34 @@
         <v>48</v>
       </c>
       <c r="AJ2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="n">
         <v>40</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO2" t="n">
         <v>30</v>
       </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32</v>
-      </c>
       <c r="AP2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
         <v>1.72</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.32</v>
@@ -987,13 +987,13 @@
         <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>1.92</v>
@@ -1011,7 +1011,7 @@
         <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>220</v>
@@ -1053,7 +1053,7 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1065,13 +1065,13 @@
         <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>42</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
         <v>8.199999999999999</v>
@@ -1092,29 +1092,29 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
         <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
         <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG3" t="n">
         <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H4" t="n">
         <v>11.5</v>
       </c>
       <c r="I4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
@@ -1175,10 +1175,10 @@
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
         <v>1.72</v>
@@ -1187,22 +1187,22 @@
         <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Z4" t="n">
         <v>150</v>
@@ -1220,16 +1220,16 @@
         <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF4" t="n">
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
         <v>170</v>
@@ -1241,74 +1241,74 @@
         <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
         <v>4.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
         <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1351,10 +1351,10 @@
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>5.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
@@ -1417,7 +1417,7 @@
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1480,7 +1480,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
         <v>16.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -1551,16 +1551,16 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
         <v>1.77</v>
@@ -1578,16 +1578,16 @@
         <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
@@ -1596,7 +1596,7 @@
         <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB6" t="n">
         <v>7.4</v>
@@ -1647,7 +1647,7 @@
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
         <v>6.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
         <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -1954,13 +1954,13 @@
         <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.31</v>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H9" t="n">
         <v>11.5</v>
@@ -2127,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K9" t="n">
         <v>6.4</v>
@@ -2139,40 +2139,40 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z9" t="n">
         <v>140</v>
@@ -2190,7 +2190,7 @@
         <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF9" t="n">
         <v>8.199999999999999</v>
@@ -2226,13 +2226,13 @@
         <v>5.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS9" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.199999999999999</v>
@@ -2241,7 +2241,7 @@
         <v>4.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AW9" t="n">
         <v>6.6</v>
@@ -2253,7 +2253,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
         <v>6.6</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
         <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
         <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
         <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.35</v>
@@ -2333,16 +2333,16 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -2354,16 +2354,16 @@
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
@@ -2375,7 +2375,7 @@
         <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2387,7 +2387,7 @@
         <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2399,7 +2399,7 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>32</v>
@@ -2411,7 +2411,7 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>38</v>
@@ -2426,7 +2426,7 @@
         <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
         <v>9.199999999999999</v>
@@ -2453,26 +2453,26 @@
         <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
         <v>16.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
         <v>3.6</v>
@@ -2518,25 +2518,25 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -2545,7 +2545,7 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -2554,7 +2554,7 @@
         <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2569,10 +2569,10 @@
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -2611,10 +2611,10 @@
         <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
         <v>19</v>
@@ -2647,26 +2647,26 @@
         <v>50</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
         <v>2.52</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,25 +2721,25 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
         <v>2.02</v>
@@ -2748,7 +2748,7 @@
         <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
         <v>13.5</v>
@@ -2766,7 +2766,7 @@
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
@@ -2817,7 +2817,7 @@
         <v>32</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2835,32 +2835,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
         <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
         <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2882,127 +2882,127 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VVV Venlo</t>
+          <t>FC Dordrecht</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.76</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.93</v>
-      </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.76</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.12</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
         <v>12</v>
       </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
         <v>5</v>
@@ -3011,50 +3011,50 @@
         <v>5.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
         <v>5.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>19.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -3109,46 +3109,46 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
       </c>
       <c r="Y14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3160,19 +3160,19 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
         <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
         <v>28</v>
@@ -3184,71 +3184,71 @@
         <v>25</v>
       </c>
       <c r="AM14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AP14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
         <v>6</v>
       </c>
-      <c r="AR14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS14" t="n">
+      <c r="BE14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Dordrecht</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N15" t="n">
         <v>6.2</v>
       </c>
-      <c r="J15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AK15" t="n">
         <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
         <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
         <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3515,10 +3515,10 @@
         <v>1.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.03</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>1.77</v>
       </c>
       <c r="I17" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
@@ -3685,7 +3685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3700,7 +3700,7 @@
         <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -3709,13 +3709,13 @@
         <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
         <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="W17" t="n">
         <v>1.19</v>
@@ -3793,7 +3793,7 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW17" t="n">
         <v>5.3</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottish League Two</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spartans</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Forfar</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="H18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AV18" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.28</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.32</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="S19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>6.4</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4252,167 +4252,167 @@
         <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
         <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE20" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB20" t="n">
+      <c r="BF20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG20" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="H21" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR21" t="n">
         <v>4.6</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X21" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AS21" t="n">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>5</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC22" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC22" t="n">
-        <v>10</v>
-      </c>
       <c r="AD22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE22" t="n">
         <v>23</v>
       </c>
-      <c r="AE22" t="n">
-        <v>80</v>
-      </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AG22" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
         <v>60</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.44</v>
+        <v>4.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.99</v>
+        <v>4.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.38</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>18.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.44</v>
+        <v>5.3</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.44</v>
+        <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="G23" t="n">
         <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="I23" t="n">
         <v>2.94</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="U23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU23" t="n">
         <v>2.12</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AV23" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.3</v>
+        <v>2.32</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.27</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AW24" t="n">
         <v>2.38</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="AX24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB24" t="n">
         <v>19.5</v>
       </c>
-      <c r="AW24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>65</v>
+        <v>2.44</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.3</v>
+        <v>2.44</v>
       </c>
       <c r="BG24" t="n">
-        <v>44</v>
+        <v>2.44</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="G25" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="H25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
         <v>11.5</v>
       </c>
-      <c r="I25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4</v>
-      </c>
-      <c r="X25" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>580</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>270</v>
+        <v>55</v>
       </c>
       <c r="AP25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV25" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>36</v>
-      </c>
       <c r="AW25" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG25" t="n">
         <v>44</v>
       </c>
-      <c r="BB25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>55</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.16</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="U26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX26" t="n">
         <v>7.2</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X26" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z26" t="n">
+      <c r="AY26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>29</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="BA26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG26" t="n">
         <v>55</v>
       </c>
-      <c r="AB26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>14</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.71</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="X27" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="Z27" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AA27" t="n">
         <v>55</v>
       </c>
       <c r="AB27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC27" t="n">
         <v>11</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF27" t="n">
         <v>8</v>
       </c>
-      <c r="AD27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG27" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>2.96</v>
       </c>
       <c r="G28" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>2.86</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="K28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT28" t="n">
         <v>3.5</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="AU28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV28" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AW28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX28" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AZ28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD28" t="n">
         <v>4.9</v>
       </c>
-      <c r="BA28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB28" t="n">
+      <c r="BE28" t="n">
         <v>5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
         <v>4.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,90 +5981,90 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>S. San Lorenzo</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2 Mayo de PJ</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="G29" t="n">
-        <v>970</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>970</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O29" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="P29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6073,16 +6073,16 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
@@ -6094,7 +6094,7 @@
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
@@ -6228,7 +6228,7 @@
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,115 +6374,115 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>S. San Lorenzo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>2 Mayo de PJ</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87</v>
+        <v>970</v>
       </c>
       <c r="H31" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
         <v>1000</v>
@@ -6491,69 +6491,69 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="P32" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="U32" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y32" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD32" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
         <v>170</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>290</v>
-      </c>
       <c r="AN32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AU32" t="n">
         <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB32" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BD32" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="G33" t="n">
-        <v>970</v>
+        <v>1.82</v>
       </c>
       <c r="H33" t="n">
-        <v>2.66</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.38</v>
+        <v>2.46</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>970</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="J34" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P34" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T34" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W34" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="X34" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,31 +7344,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7380,19 +7380,19 @@
         <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="P36" t="n">
         <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7404,7 +7404,7 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,36 +7533,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.7</v>
+        <v>1.59</v>
       </c>
       <c r="G37" t="n">
-        <v>6.6</v>
+        <v>2.86</v>
       </c>
       <c r="H37" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="K37" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,67 +7571,67 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="O37" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="T37" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.54</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X37" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7655,69 +7655,69 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,184 +7727,184 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G38" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="H38" t="n">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="I38" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="J38" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR38" t="n">
         <v>2.18</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>370</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>5</v>
-      </c>
       <c r="AS38" t="n">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.4</v>
+        <v>2.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.2</v>
+        <v>2.08</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="AX38" t="n">
-        <v>5.9</v>
+        <v>2.46</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.4</v>
+        <v>2.38</v>
       </c>
       <c r="AZ38" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="BA38" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="BB38" t="n">
-        <v>50</v>
+        <v>2.58</v>
       </c>
       <c r="BC38" t="n">
-        <v>7</v>
+        <v>2.58</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="BE38" t="n">
-        <v>7.4</v>
+        <v>2.58</v>
       </c>
       <c r="BF38" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.6</v>
+        <v>2.58</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G39" t="n">
         <v>970</v>
@@ -7947,7 +7947,7 @@
         <v>970</v>
       </c>
       <c r="J39" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K39" t="n">
         <v>950</v>
@@ -8098,14 +8098,14 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,184 +8115,378 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
       <c r="G40" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H40" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I40" t="n">
         <v>2.64</v>
-      </c>
-      <c r="I40" t="n">
-        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>2.74</v>
       </c>
       <c r="K40" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="N40" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="P40" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-16 05:27:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2.34</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>1.18</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>3.85</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>1.81</v>
       </c>
-      <c r="U40" t="n">
+      <c r="U41" t="n">
         <v>1.7</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="V41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.43</v>
       </c>
-      <c r="X40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="X41" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y41" t="n">
         <v>970</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="Z41" t="n">
         <v>24</v>
       </c>
-      <c r="AA40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
         <v>970</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AC41" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AD41" t="n">
         <v>970</v>
       </c>
-      <c r="AE40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF40" t="n">
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
         <v>28</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AG41" t="n">
         <v>970</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AH41" t="n">
         <v>29</v>
       </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC40" t="n">
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU41" t="n">
         <v>1.95</v>
       </c>
-      <c r="BD40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH40" t="inlineStr">
-        <is>
-          <t>2026-03-16 03:15:16</t>
+      <c r="AV41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
         <v>3.35</v>
@@ -796,10 +796,10 @@
         <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
         <v>2.38</v>
@@ -808,7 +808,7 @@
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -820,7 +820,7 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -835,7 +835,7 @@
         <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -862,7 +862,7 @@
         <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
@@ -871,10 +871,10 @@
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -898,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
         <v>9.4</v>
@@ -910,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H4" t="n">
         <v>11.5</v>
@@ -1157,7 +1157,7 @@
         <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>7.6</v>
@@ -1175,7 +1175,7 @@
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
         <v>1.48</v>
@@ -1190,13 +1190,13 @@
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1268,10 +1268,10 @@
         <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AW4" t="n">
         <v>7.6</v>
@@ -1289,7 +1289,7 @@
         <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>5.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>1.65</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
@@ -1375,7 +1375,7 @@
         <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S5" t="n">
         <v>2.16</v>
@@ -1384,13 +1384,13 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
         <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X5" t="n">
         <v>34</v>
@@ -1399,7 +1399,7 @@
         <v>28</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
         <v>110</v>
@@ -1408,7 +1408,7 @@
         <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1417,7 +1417,7 @@
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1429,7 +1429,7 @@
         <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK5" t="n">
         <v>14.5</v>
@@ -1495,14 +1495,14 @@
         <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
         <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G6" t="n">
         <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
@@ -1548,16 +1548,16 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
@@ -1578,7 +1578,7 @@
         <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G7" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.95</v>
@@ -1757,10 +1757,10 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.47</v>
@@ -1769,7 +1769,7 @@
         <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
         <v>2.3</v>
@@ -1778,13 +1778,13 @@
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="n">
         <v>44</v>
@@ -1793,7 +1793,7 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
         <v>11</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -1829,22 +1829,22 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
         <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>9.199999999999999</v>
@@ -1856,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -1868,29 +1868,29 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
         <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.72</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H8" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
@@ -1939,7 +1939,7 @@
         <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
         <v>1.34</v>
       </c>
       <c r="H9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
         <v>14</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2142,22 +2142,22 @@
         <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
         <v>1.8</v>
@@ -2166,7 +2166,7 @@
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
@@ -2178,7 +2178,7 @@
         <v>140</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
@@ -2190,13 +2190,13 @@
         <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AF9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>32</v>
@@ -2220,43 +2220,43 @@
         <v>5.3</v>
       </c>
       <c r="AO9" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX9" t="n">
         <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
         <v>9</v>
@@ -2265,20 +2265,20 @@
         <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2309,73 +2309,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
         <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
         <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2387,7 +2387,7 @@
         <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>13.5</v>
@@ -2399,19 +2399,19 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>38</v>
@@ -2423,10 +2423,10 @@
         <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
         <v>9.199999999999999</v>
@@ -2435,7 +2435,7 @@
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
         <v>30</v>
@@ -2453,26 +2453,26 @@
         <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
         <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
         <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
         <v>2.66</v>
@@ -2527,19 +2527,19 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
         <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
         <v>4.3</v>
@@ -2557,7 +2557,7 @@
         <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
         <v>12</v>
@@ -2569,7 +2569,7 @@
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -2581,7 +2581,7 @@
         <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -2635,7 +2635,7 @@
         <v>38</v>
       </c>
       <c r="AX11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2647,26 +2647,26 @@
         <v>50</v>
       </c>
       <c r="BB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE11" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BF11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG11" t="n">
         <v>6.8</v>
       </c>
-      <c r="BD11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
         <v>2.52</v>
@@ -2712,7 +2712,7 @@
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2724,10 +2724,10 @@
         <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
         <v>2.16</v>
@@ -2739,7 +2739,7 @@
         <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
         <v>2.02</v>
@@ -2826,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2835,7 +2835,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA12" t="n">
         <v>6.4</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
         <v>6.8</v>
@@ -2856,11 +2856,11 @@
         <v>30</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
         <v>1.48</v>
@@ -2933,10 +2933,10 @@
         <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.19</v>
@@ -3005,10 +3005,10 @@
         <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3020,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
         <v>9.6</v>
@@ -3032,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3044,17 +3044,17 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>3.65</v>
@@ -3121,22 +3121,22 @@
         <v>1.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T14" t="n">
         <v>1.44</v>
       </c>
       <c r="U14" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="X14" t="n">
         <v>34</v>
@@ -3169,10 +3169,10 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
         <v>28</v>
@@ -3184,16 +3184,16 @@
         <v>25</v>
       </c>
       <c r="AM14" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
         <v>970</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>6.2</v>
@@ -3202,13 +3202,13 @@
         <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
         <v>5.5</v>
@@ -3217,7 +3217,7 @@
         <v>6.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -3229,16 +3229,16 @@
         <v>6.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3500,31 +3500,31 @@
         <v>1.03</v>
       </c>
       <c r="O16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
         <v>2.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.81</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,68 +3575,68 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>1.77</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
@@ -3685,7 +3685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3709,13 +3709,13 @@
         <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
         <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.19</v>
@@ -3739,7 +3739,7 @@
         <v>9.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
@@ -3784,7 +3784,7 @@
         <v>8.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3796,16 +3796,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX17" t="n">
         <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -3817,7 +3817,7 @@
         <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
         <v>6.6</v>
@@ -3826,11 +3826,11 @@
         <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.26</v>
@@ -3885,7 +3885,7 @@
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.2</v>
@@ -3909,7 +3909,7 @@
         <v>1.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
         <v>3.2</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>3.1</v>
@@ -4088,7 +4088,7 @@
         <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
@@ -4103,122 +4103,122 @@
         <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
         <v>1.86</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>2.76</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
         <v>2.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -4288,7 +4288,7 @@
         <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
@@ -4297,10 +4297,10 @@
         <v>2.24</v>
       </c>
       <c r="V20" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G21" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4494,7 +4494,7 @@
         <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" t="n">
         <v>3.85</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.75</v>
       </c>
       <c r="AV21" t="n">
         <v>4.1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BB21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC21" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BD21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BF21" t="n">
         <v>5</v>
       </c>
-      <c r="BD21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4646,16 +4646,16 @@
         <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
         <v>4.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
@@ -4670,22 +4670,22 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R22" t="n">
         <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W22" t="n">
         <v>1.25</v>
@@ -4709,22 +4709,22 @@
         <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>23</v>
       </c>
       <c r="AF22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG22" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ22" t="n">
         <v>100</v>
@@ -4745,62 +4745,62 @@
         <v>13.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AR22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT22" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AW22" t="n">
         <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AY22" t="n">
         <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC22" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG22" t="n">
         <v>9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4840,10 +4840,10 @@
         <v>2.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
         <v>4.6</v>
@@ -4873,128 +4873,128 @@
         <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U23" t="n">
         <v>2.66</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X23" t="n">
         <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ23" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.26</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.32</v>
+        <v>16.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.26</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.34</v>
+        <v>18.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.32</v>
+        <v>17.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF23" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BG23" t="n">
-        <v>2.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G24" t="n">
         <v>2.28</v>
@@ -5034,7 +5034,7 @@
         <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
@@ -5061,134 +5061,134 @@
         <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
         <v>3.75</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
         <v>1.78</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>10</v>
       </c>
-      <c r="AD24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC24" t="n">
         <v>19</v>
       </c>
-      <c r="AS24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD24" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.44</v>
+        <v>16</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.44</v>
+        <v>4.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G25" t="n">
         <v>1.56</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>5.6</v>
       </c>
       <c r="K25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L25" t="n">
         <v>1.27</v>
@@ -5249,13 +5249,13 @@
         <v>1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q25" t="n">
         <v>1.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S25" t="n">
         <v>2.3</v>
@@ -5264,19 +5264,19 @@
         <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V25" t="n">
         <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X25" t="n">
         <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z25" t="n">
         <v>55</v>
@@ -5291,13 +5291,13 @@
         <v>13</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>65</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
         <v>10</v>
@@ -5309,7 +5309,7 @@
         <v>55</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK25" t="n">
         <v>14</v>
@@ -5327,16 +5327,16 @@
         <v>55</v>
       </c>
       <c r="AP25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR25" t="n">
         <v>44</v>
       </c>
       <c r="AS25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AT25" t="n">
         <v>11.5</v>
@@ -5354,13 +5354,13 @@
         <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB25" t="n">
         <v>14</v>
@@ -5369,7 +5369,7 @@
         <v>13</v>
       </c>
       <c r="BD25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE25" t="n">
         <v>70</v>
@@ -5378,11 +5378,11 @@
         <v>5.3</v>
       </c>
       <c r="BG25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5437,25 +5437,25 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R26" t="n">
         <v>1.54</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
         <v>1.8</v>
@@ -5467,16 +5467,16 @@
         <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
         <v>38</v>
       </c>
       <c r="Z26" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA26" t="n">
-        <v>580</v>
+        <v>530</v>
       </c>
       <c r="AB26" t="n">
         <v>8.800000000000001</v>
@@ -5488,7 +5488,7 @@
         <v>44</v>
       </c>
       <c r="AE26" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AF26" t="n">
         <v>7.6</v>
@@ -5500,7 +5500,7 @@
         <v>34</v>
       </c>
       <c r="AI26" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ26" t="n">
         <v>10</v>
@@ -5527,7 +5527,7 @@
         <v>32</v>
       </c>
       <c r="AR26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AS26" t="n">
         <v>130</v>
@@ -5542,7 +5542,7 @@
         <v>36</v>
       </c>
       <c r="AW26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX26" t="n">
         <v>7.2</v>
@@ -5554,7 +5554,7 @@
         <v>29</v>
       </c>
       <c r="BA26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB26" t="n">
         <v>9.6</v>
@@ -5566,7 +5566,7 @@
         <v>36</v>
       </c>
       <c r="BE26" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="BF26" t="n">
         <v>4.8</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
         <v>3.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R27" t="n">
         <v>1.86</v>
@@ -5649,7 +5649,7 @@
         <v>2.12</v>
       </c>
       <c r="T27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U27" t="n">
         <v>3</v>
@@ -5658,7 +5658,7 @@
         <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
@@ -5685,7 +5685,7 @@
         <v>28</v>
       </c>
       <c r="AF27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
@@ -5697,7 +5697,7 @@
         <v>29</v>
       </c>
       <c r="AJ27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK27" t="n">
         <v>18.5</v>
@@ -5709,7 +5709,7 @@
         <v>44</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO27" t="n">
         <v>15</v>
@@ -5745,7 +5745,7 @@
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
         <v>26</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I28" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="K28" t="n">
         <v>3.25</v>
@@ -5825,7 +5825,7 @@
         <v>1.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O28" t="n">
         <v>1.56</v>
@@ -5834,7 +5834,7 @@
         <v>1.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R28" t="n">
         <v>1.16</v>
@@ -5849,7 +5849,7 @@
         <v>1.71</v>
       </c>
       <c r="V28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W28" t="n">
         <v>1.32</v>
@@ -5858,13 +5858,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB28" t="n">
         <v>11</v>
@@ -5873,10 +5873,10 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF28" t="n">
         <v>26</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AR28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG28" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5995,31 +5995,31 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.47</v>
@@ -6040,13 +6040,13 @@
         <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6082,7 +6082,7 @@
         <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
@@ -6103,16 +6103,16 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
@@ -6121,44 +6121,44 @@
         <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX29" t="n">
         <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE29" t="n">
         <v>6</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6189,100 +6189,100 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="I30" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="J30" t="n">
-        <v>1.56</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ30" t="n">
         <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -6294,65 +6294,65 @@
         <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="G31" t="n">
-        <v>970</v>
+        <v>3.85</v>
       </c>
       <c r="H31" t="n">
         <v>2.5</v>
       </c>
       <c r="I31" t="n">
-        <v>970</v>
+        <v>3.15</v>
       </c>
       <c r="J31" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="O31" t="n">
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6431,10 +6431,10 @@
         <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W31" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6580,22 +6580,22 @@
         <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H32" t="n">
         <v>5.7</v>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
         <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -6604,13 +6604,13 @@
         <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R32" t="n">
         <v>1.29</v>
@@ -6628,7 +6628,7 @@
         <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X32" t="n">
         <v>970</v>
@@ -6646,7 +6646,7 @@
         <v>970</v>
       </c>
       <c r="AC32" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
         <v>23</v>
@@ -6691,7 +6691,7 @@
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS32" t="n">
         <v>6.4</v>
@@ -6712,7 +6712,7 @@
         <v>4.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
         <v>5.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
         <v>3.45</v>
@@ -6795,13 +6795,13 @@
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O33" t="n">
         <v>1.51</v>
       </c>
       <c r="P33" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
         <v>2.46</v>
@@ -6816,7 +6816,7 @@
         <v>2.26</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
         <v>1.17</v>
@@ -6861,7 +6861,7 @@
         <v>170</v>
       </c>
       <c r="AJ33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK33" t="n">
         <v>29</v>
@@ -6891,16 +6891,16 @@
         <v>4.9</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU33" t="n">
         <v>7.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX33" t="n">
         <v>7.8</v>
@@ -6909,10 +6909,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB33" t="n">
         <v>16.5</v>
@@ -6921,7 +6921,7 @@
         <v>20</v>
       </c>
       <c r="BD33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
         <v>4.9</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>970</v>
+        <v>2.94</v>
       </c>
       <c r="H34" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>2.58</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M34" t="n">
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="O34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.38</v>
+        <v>2.16</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7013,10 +7013,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W34" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="G35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I35" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,146 +7183,146 @@
         <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P35" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="T35" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U35" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="V35" t="n">
         <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="X35" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="Z35" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC35" t="n">
         <v>8.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AE35" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI35" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AK35" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AL35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM35" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>8.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.6</v>
+        <v>1.62</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.3</v>
+        <v>1.69</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.8</v>
+        <v>1.74</v>
       </c>
       <c r="AT35" t="n">
-        <v>6.6</v>
+        <v>1.48</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.2</v>
+        <v>1.44</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.8</v>
+        <v>1.65</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.7</v>
+        <v>1.74</v>
       </c>
       <c r="AX35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.8</v>
+        <v>1.63</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.7</v>
+        <v>1.74</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.5</v>
+        <v>1.69</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.8</v>
+        <v>1.74</v>
       </c>
       <c r="BF35" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.8</v>
+        <v>1.74</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7547,58 +7547,58 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.86</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="K37" t="n">
-        <v>950</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.25</v>
       </c>
       <c r="O37" t="n">
         <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>6.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I38" t="n">
         <v>2.18</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AX38" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BA38" t="n">
         <v>2.58</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
         <v>1.2</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="O39" t="n">
         <v>1.21</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8132,16 +8132,16 @@
         <v>3.75</v>
       </c>
       <c r="G40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H40" t="n">
         <v>2.42</v>
       </c>
       <c r="I40" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
@@ -8177,10 +8177,10 @@
         <v>1.61</v>
       </c>
       <c r="V40" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W40" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X40" t="n">
         <v>6.8</v>
@@ -8237,7 +8237,7 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ40" t="n">
         <v>5.8</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.88</v>
       </c>
       <c r="G41" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H41" t="n">
         <v>2.66</v>
@@ -8341,19 +8341,19 @@
         <v>3.45</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="O41" t="n">
         <v>1.45</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
         <v>2.34</v>
@@ -8365,16 +8365,16 @@
         <v>3.85</v>
       </c>
       <c r="T41" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U41" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V41" t="n">
         <v>1.48</v>
       </c>
       <c r="W41" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="X41" t="n">
         <v>12</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH44"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
@@ -811,10 +811,10 @@
         <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>28</v>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
         <v>19.5</v>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>36</v>
@@ -862,7 +862,7 @@
         <v>16.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
@@ -874,7 +874,7 @@
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2" t="n">
         <v>9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>27</v>
       </c>
       <c r="BC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.48</v>
@@ -975,67 +975,67 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="O3" t="n">
         <v>1.53</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>950</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1056,65 +1056,65 @@
         <v>38</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BA3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="BB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.1</v>
       </c>
-      <c r="AV3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="BE3" t="n">
         <v>2.56</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BF3" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
         <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>5.9</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1357,7 +1357,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1381,67 +1381,67 @@
         <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AB5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>29</v>
       </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>26</v>
-      </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1468,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1480,7 +1480,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1489,20 +1489,20 @@
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>1.25</v>
@@ -1563,7 +1563,7 @@
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
         <v>1.48</v>
@@ -1605,7 +1605,7 @@
         <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE6" t="n">
         <v>230</v>
@@ -1629,74 +1629,74 @@
         <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
         <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AO6" t="n">
         <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
         <v>3.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.25</v>
@@ -1751,67 +1751,67 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
         <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
         <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
         <v>44</v>
@@ -1820,7 +1820,7 @@
         <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>23</v>
@@ -1829,28 +1829,28 @@
         <v>60</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AO7" t="n">
         <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AT7" t="n">
         <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
         <v>18.5</v>
@@ -1865,7 +1865,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
         <v>38</v>
@@ -1874,7 +1874,7 @@
         <v>16.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
         <v>21</v>
@@ -1883,14 +1883,14 @@
         <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
         <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
         <v>7.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
         <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>28</v>
@@ -2002,7 +2002,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
@@ -2014,43 +2014,43 @@
         <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
         <v>210</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
         <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
@@ -2062,29 +2062,29 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
         <v>1.46</v>
@@ -2157,7 +2157,7 @@
         <v>2.86</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
@@ -2229,13 +2229,13 @@
         <v>17</v>
       </c>
       <c r="AR9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS9" t="n">
         <v>10</v>
       </c>
-      <c r="AS9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AT9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
         <v>8.4</v>
@@ -2244,10 +2244,10 @@
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>8.800000000000001</v>
@@ -2256,7 +2256,7 @@
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB9" t="n">
         <v>17</v>
@@ -2265,20 +2265,20 @@
         <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
         <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
         <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="I10" t="n">
         <v>3.2</v>
@@ -2327,22 +2327,22 @@
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
         <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
@@ -2402,7 +2402,7 @@
         <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
@@ -2420,16 +2420,16 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
         <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
@@ -2438,16 +2438,16 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
         <v>4.8</v>
@@ -2456,23 +2456,23 @@
         <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD10" t="n">
         <v>4.8</v>
       </c>
       <c r="BE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG10" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>5.7</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2605,7 +2605,7 @@
         <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO11" t="n">
         <v>300</v>
@@ -2614,13 +2614,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2629,10 +2629,10 @@
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>7.2</v>
@@ -2641,10 +2641,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
         <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
         <v>2.48</v>
@@ -2706,16 +2706,16 @@
         <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2727,106 +2727,106 @@
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
         <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
         <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
         <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
         <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
@@ -2835,32 +2835,32 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
         <v>18.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
         <v>2.64</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -2915,7 +2915,7 @@
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>1.43</v>
@@ -2927,19 +2927,19 @@
         <v>2.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
         <v>1.6</v>
@@ -2957,7 +2957,7 @@
         <v>65</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
@@ -2981,10 +2981,10 @@
         <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -2993,7 +2993,7 @@
         <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
@@ -3008,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3020,7 +3020,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,29 +3032,29 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7.6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>25</v>
-      </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>2.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="J14" t="n">
         <v>3.25</v>
@@ -3103,7 +3103,7 @@
         <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
@@ -3118,7 +3118,7 @@
         <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
@@ -3127,13 +3127,13 @@
         <v>3.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
         <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
         <v>1.43</v>
@@ -3145,10 +3145,10 @@
         <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
@@ -3157,43 +3157,43 @@
         <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
         <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
         <v>44</v>
       </c>
       <c r="AO14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.4</v>
@@ -3202,10 +3202,10 @@
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
@@ -3214,41 +3214,41 @@
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA14" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>4.9</v>
@@ -3312,7 +3312,7 @@
         <v>2.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R15" t="n">
         <v>1.72</v>
@@ -3393,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS15" t="n">
         <v>4.1</v>
@@ -3408,7 +3408,7 @@
         <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3438,11 +3438,11 @@
         <v>5.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G16" t="n">
         <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -3503,16 +3503,16 @@
         <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.77</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
         <v>1.44</v>
@@ -3527,13 +3527,13 @@
         <v>1.86</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
         <v>65</v>
@@ -3545,22 +3545,22 @@
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF16" t="n">
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
@@ -3569,10 +3569,10 @@
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN16" t="n">
         <v>9.4</v>
@@ -3581,16 +3581,16 @@
         <v>970</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>14.5</v>
@@ -3599,44 +3599,44 @@
         <v>8.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H17" t="n">
         <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
@@ -3709,22 +3709,22 @@
         <v>2.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
         <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W17" t="n">
         <v>2.32</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,58 +3733,58 @@
         <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
         <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
         <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
         <v>9.6</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
         <v>14.5</v>
@@ -3820,17 +3820,17 @@
         <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BF17" t="n">
         <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3900,16 +3900,16 @@
         <v>1.86</v>
       </c>
       <c r="S18" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="T18" t="n">
         <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
         <v>3.75</v>
@@ -3954,7 +3954,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR18" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AS18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW18" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AY18" t="n">
         <v>3.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
         <v>2.92</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>5.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H19" t="n">
         <v>1.77</v>
       </c>
       <c r="I19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4103,7 +4103,7 @@
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W19" t="n">
         <v>1.19</v>
@@ -4112,10 +4112,10 @@
         <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
         <v>22</v>
@@ -4172,10 +4172,10 @@
         <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
@@ -4184,41 +4184,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG19" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4249,34 +4249,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G20" t="n">
         <v>1.4</v>
       </c>
       <c r="H20" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
         <v>2.36</v>
@@ -4285,16 +4285,16 @@
         <v>1.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
         <v>1.09</v>
@@ -4303,10 +4303,10 @@
         <v>3.4</v>
       </c>
       <c r="X20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z20" t="n">
         <v>120</v>
@@ -4315,104 +4315,104 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="AZ20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BB20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE20" t="n">
         <v>5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF20" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4449,28 +4449,28 @@
         <v>1.98</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
         <v>1.84</v>
@@ -4482,7 +4482,7 @@
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
         <v>1.86</v>
@@ -4491,19 +4491,19 @@
         <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
         <v>2.02</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4512,101 +4512,101 @@
         <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>85</v>
       </c>
       <c r="AF21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
         <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
         <v>100</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE21" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8</v>
-      </c>
       <c r="BF21" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>2.76</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I22" t="n">
         <v>2.74</v>
@@ -4679,7 +4679,7 @@
         <v>2.96</v>
       </c>
       <c r="T22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
         <v>2.24</v>
@@ -4688,7 +4688,7 @@
         <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4745,52 +4745,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS22" t="n">
         <v>3.05</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>4.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AY22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ22" t="n">
         <v>5.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BC22" t="n">
         <v>3.05</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BF22" t="n">
         <v>4.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
@@ -4900,13 +4900,13 @@
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD23" t="n">
         <v>970</v>
       </c>
       <c r="AE23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>23</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE23" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF23" t="n">
         <v>18.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
@@ -5058,19 +5058,19 @@
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
         <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
         <v>1.9</v>
@@ -5091,7 +5091,7 @@
         <v>26</v>
       </c>
       <c r="AB24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10.5</v>
@@ -5109,7 +5109,7 @@
         <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI24" t="n">
         <v>38</v>
@@ -5133,62 +5133,62 @@
         <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AS24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT24" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>13</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA24" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
         <v>4.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
         <v>4.7</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>2.72</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H25" t="n">
         <v>2.24</v>
       </c>
       <c r="I25" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.8</v>
@@ -5252,7 +5252,7 @@
         <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R25" t="n">
         <v>1.66</v>
@@ -5261,70 +5261,70 @@
         <v>2.2</v>
       </c>
       <c r="T25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.47</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.46</v>
       </c>
       <c r="X25" t="n">
         <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN25" t="n">
         <v>18</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -5336,10 +5336,10 @@
         <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU25" t="n">
         <v>8.800000000000001</v>
@@ -5351,38 +5351,38 @@
         <v>18.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>40</v>
+        <v>4.5</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
         <v>3.15</v>
@@ -5431,7 +5431,7 @@
         <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5455,13 +5455,13 @@
         <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
         <v>1.78</v>
@@ -5524,16 +5524,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT26" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
@@ -5545,38 +5545,38 @@
         <v>4.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD26" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG26" t="n">
         <v>5</v>
       </c>
-      <c r="BF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G27" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J27" t="n">
         <v>5.7</v>
       </c>
-      <c r="J27" t="n">
-        <v>5.6</v>
-      </c>
       <c r="K27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.27</v>
@@ -5631,52 +5631,52 @@
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T27" t="n">
         <v>1.67</v>
       </c>
       <c r="U27" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD27" t="n">
         <v>22</v>
@@ -5691,7 +5691,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>55</v>
@@ -5709,13 +5709,13 @@
         <v>80</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ27" t="n">
         <v>25</v>
@@ -5727,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="AT27" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU27" t="n">
         <v>12</v>
@@ -5754,7 +5754,7 @@
         <v>14.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD27" t="n">
         <v>24</v>
@@ -5763,14 +5763,14 @@
         <v>65</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BG27" t="n">
         <v>44</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5810,43 +5810,43 @@
         <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V28" t="n">
         <v>1.08</v>
@@ -5855,7 +5855,7 @@
         <v>4.1</v>
       </c>
       <c r="X28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y28" t="n">
         <v>38</v>
@@ -5867,16 +5867,16 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE28" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AF28" t="n">
         <v>7.6</v>
@@ -5888,61 +5888,61 @@
         <v>34</v>
       </c>
       <c r="AI28" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ28" t="n">
         <v>10</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AO28" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>34</v>
       </c>
       <c r="AR28" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AS28" t="n">
         <v>120</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW28" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA28" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB28" t="n">
         <v>9.4</v>
@@ -5951,20 +5951,20 @@
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
         <v>55</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.16</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.18</v>
       </c>
       <c r="H29" t="n">
         <v>3.1</v>
@@ -6010,43 +6010,43 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O29" t="n">
         <v>1.14</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R29" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T29" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
         <v>1.46</v>
       </c>
       <c r="W29" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>34</v>
@@ -6055,25 +6055,25 @@
         <v>22</v>
       </c>
       <c r="Z29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA29" t="n">
         <v>55</v>
       </c>
       <c r="AB29" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
         <v>11.5</v>
@@ -6100,10 +6100,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ29" t="n">
         <v>20</v>
@@ -6112,13 +6112,13 @@
         <v>26</v>
       </c>
       <c r="AS29" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>13.5</v>
@@ -6127,7 +6127,7 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6151,14 +6151,14 @@
         <v>40</v>
       </c>
       <c r="BF29" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="G30" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,100 +6374,100 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tacuarembo</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>La Luz FC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1.21</v>
       </c>
       <c r="G31" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>11.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.34</v>
+        <v>1.02</v>
       </c>
       <c r="O31" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.52</v>
+        <v>1.74</v>
       </c>
       <c r="R31" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>3.45</v>
+        <v>1.74</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
@@ -6488,72 +6488,72 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>La Luz FC</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS32" t="n">
         <v>4.8</v>
       </c>
-      <c r="J32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>10</v>
-      </c>
       <c r="AT32" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX32" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BB32" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BE32" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BG32" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,108 +6757,108 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>2.14</v>
       </c>
       <c r="H33" t="n">
-        <v>1.79</v>
+        <v>4.3</v>
       </c>
       <c r="I33" t="n">
-        <v>1.98</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L33" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="O33" t="n">
         <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S33" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="V33" t="n">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="X33" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB33" t="n">
         <v>7.6</v>
       </c>
-      <c r="Z33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>17</v>
-      </c>
       <c r="AC33" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ33" t="n">
         <v>1000</v>
@@ -6870,78 +6870,78 @@
         <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.15</v>
+        <v>11</v>
       </c>
       <c r="AR33" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,31 +6956,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>S. San Lorenzo</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2 Mayo de PJ</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="G34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K34" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.48</v>
@@ -6989,146 +6989,146 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="O34" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR34" t="n">
         <v>4.2</v>
       </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
+      <c r="AS34" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AV34" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>1.84</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -7177,13 +7177,13 @@
         <v>4.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.35</v>
@@ -7192,19 +7192,19 @@
         <v>1.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="R35" t="n">
         <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
         <v>1.96</v>
       </c>
       <c r="U35" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V35" t="n">
         <v>1.18</v>
@@ -7216,43 +7216,43 @@
         <v>15.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z35" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB35" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG35" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI35" t="n">
         <v>120</v>
       </c>
       <c r="AJ35" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AK35" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7261,75 +7261,75 @@
         <v>180</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AR35" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="AS35" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AT35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW35" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AX35" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="BE35" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Club 2 de Mayo de Pedro Ju</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>2.92</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="K36" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P36" t="n">
         <v>1.55</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.59</v>
       </c>
       <c r="Q36" t="n">
         <v>2.46</v>
       </c>
       <c r="R36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="V36" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AE36" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AH36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI36" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="AN36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX36" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB36" t="n">
-        <v>16.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC36" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF36" t="n">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,191 +7533,191 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Universidad de Venezuela</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="G37" t="n">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="L37" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N37" t="n">
-        <v>2.06</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P37" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="W37" t="n">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,191 +7727,191 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Universidad de Venezuela</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="I38" t="n">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="J38" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
         <v>3</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T38" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>1.96</v>
+        <v>1.46</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,191 +7921,191 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R39" t="n">
         <v>1.25</v>
       </c>
-      <c r="O39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8120,67 +8120,67 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="R40" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="T40" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8237,69 +8237,69 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,120 +8309,120 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K41" t="n">
         <v>4.4</v>
       </c>
-      <c r="G41" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O41" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S41" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="T41" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U41" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="W41" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="X41" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL41" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
         <v>1000</v>
@@ -8431,69 +8431,69 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AX41" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV41" t="n">
+      <c r="AY41" t="n">
         <v>4</v>
       </c>
-      <c r="AW41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AZ41" t="n">
-        <v>4.9</v>
+        <v>1.79</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.3</v>
+        <v>1.51</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.7</v>
+        <v>1.89</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.6</v>
+        <v>1.75</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.6</v>
+        <v>1.49</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.7</v>
+        <v>1.51</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.7</v>
+        <v>1.62</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.6</v>
+        <v>1.51</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,120 +8503,120 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="G42" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="H42" t="n">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="I42" t="n">
-        <v>970</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="N42" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="O42" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="P42" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="R42" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V42" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -8720,13 +8720,13 @@
         <v>2.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J43" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L43" t="n">
         <v>1.71</v>
@@ -8753,13 +8753,13 @@
         <v>7.2</v>
       </c>
       <c r="T43" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
         <v>1.61</v>
       </c>
       <c r="V43" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W43" t="n">
         <v>1.33</v>
@@ -8777,7 +8777,7 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
         <v>8.4</v>
@@ -8825,7 +8825,7 @@
         <v>5.8</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS43" t="n">
         <v>7</v>
@@ -8837,238 +8837,432 @@
         <v>6.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW43" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX43" t="n">
         <v>6.2</v>
       </c>
       <c r="AY43" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AZ43" t="n">
-        <v>25</v>
+        <v>6.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB43" t="n">
         <v>50</v>
       </c>
       <c r="BC43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD43" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
         <v>7.8</v>
       </c>
-      <c r="BE43" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF43" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-16 12:03:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Millonarios</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F45" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N45" t="n">
         <v>2.9</v>
       </c>
-      <c r="G44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q44" t="n">
+      <c r="O45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS45" t="n">
         <v>2.34</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BH44" t="inlineStr">
-        <is>
-          <t>2026-03-16 09:51:18</t>
+      <c r="AT45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -760,16 +760,16 @@
         <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -781,7 +781,7 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
@@ -805,55 +805,55 @@
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
         <v>24</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>75</v>
@@ -868,28 +868,28 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
         <v>3.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X3" t="n">
         <v>950</v>
@@ -1011,16 +1011,16 @@
         <v>950</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>950</v>
@@ -1029,7 +1029,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>950</v>
@@ -1038,83 +1038,83 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
         <v>110</v>
       </c>
       <c r="AP3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.56</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="P4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.29</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
         <v>5.9</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1357,7 +1357,7 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1366,10 +1366,10 @@
         <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
         <v>2.06</v>
@@ -1384,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
@@ -1405,7 +1405,7 @@
         <v>240</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
@@ -1441,22 +1441,22 @@
         <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1468,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1480,7 +1480,7 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1489,20 +1489,20 @@
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,13 @@
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.25</v>
@@ -1560,31 +1560,31 @@
         <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
         <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.72</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
         <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="X6" t="n">
         <v>38</v>
@@ -1605,7 +1605,7 @@
         <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE6" t="n">
         <v>230</v>
@@ -1614,10 +1614,10 @@
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
         <v>170</v>
@@ -1629,74 +1629,74 @@
         <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
         <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
         <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
         <v>3.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -1736,37 +1736,37 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K7" t="n">
         <v>5.4</v>
       </c>
-      <c r="K7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
@@ -1781,19 +1781,19 @@
         <v>2.6</v>
       </c>
       <c r="X7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA7" t="n">
         <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
         <v>13.5</v>
@@ -1802,16 +1802,16 @@
         <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
         <v>44</v>
@@ -1820,7 +1820,7 @@
         <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL7" t="n">
         <v>23</v>
@@ -1844,10 +1844,10 @@
         <v>42</v>
       </c>
       <c r="AS7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
@@ -1856,13 +1856,13 @@
         <v>18.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
         <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>17</v>
@@ -1886,11 +1886,11 @@
         <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
         <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1948,16 +1948,16 @@
         <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
         <v>3.9</v>
@@ -1969,16 +1969,16 @@
         <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD8" t="n">
         <v>28</v>
@@ -2011,19 +2011,19 @@
         <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
         <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
         <v>210</v>
@@ -2032,13 +2032,13 @@
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
         <v>6.2</v>
@@ -2050,41 +2050,41 @@
         <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
         <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
         <v>4.6</v>
@@ -2154,19 +2154,19 @@
         <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
         <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
         <v>23</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
         <v>2.6</v>
@@ -2321,10 +2321,10 @@
         <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.37</v>
@@ -2378,7 +2378,7 @@
         <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>14.5</v>
@@ -2402,7 +2402,7 @@
         <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
@@ -2426,7 +2426,7 @@
         <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -2438,7 +2438,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2450,29 +2450,29 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
         <v>1.35</v>
@@ -2605,7 +2605,7 @@
         <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO11" t="n">
         <v>300</v>
@@ -2614,13 +2614,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2629,10 +2629,10 @@
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>7.2</v>
@@ -2641,10 +2641,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>9.4</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
         <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2745,10 +2745,10 @@
         <v>2.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -2757,10 +2757,10 @@
         <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>12</v>
@@ -2778,31 +2778,31 @@
         <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>40</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -2811,13 +2811,13 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>13.5</v>
@@ -2838,19 +2838,19 @@
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
         <v>15.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2900,13 +2900,13 @@
         <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2939,7 +2939,7 @@
         <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
         <v>1.6</v>
@@ -2969,7 +2969,7 @@
         <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
@@ -3008,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>7.8</v>
@@ -3020,7 +3020,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,29 +3032,29 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC13" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G14" t="n">
         <v>3.05</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="X14" t="n">
         <v>13.5</v>
@@ -3151,61 +3151,61 @@
         <v>46</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>34</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>55</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>60</v>
-      </c>
       <c r="AK14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
@@ -3214,41 +3214,41 @@
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="AX14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
         <v>4.9</v>
@@ -3312,7 +3312,7 @@
         <v>2.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.72</v>
@@ -3327,7 +3327,7 @@
         <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
         <v>2.08</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3518,10 +3518,10 @@
         <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
         <v>1.86</v>
@@ -3545,13 +3545,13 @@
         <v>11.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
@@ -3563,7 +3563,7 @@
         <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
@@ -3581,62 +3581,62 @@
         <v>970</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>8.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX16" t="n">
         <v>4.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB16" t="n">
         <v>6.8</v>
       </c>
       <c r="BC16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD16" t="n">
         <v>5</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
@@ -3709,13 +3709,13 @@
         <v>2.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
         <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
         <v>2.32</v>
@@ -3733,16 +3733,16 @@
         <v>160</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
         <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
         <v>13.5</v>
@@ -3760,7 +3760,7 @@
         <v>21</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>38</v>
@@ -3778,13 +3778,13 @@
         <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
         <v>9.6</v>
@@ -3817,20 +3817,20 @@
         <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
         <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3900,16 +3900,16 @@
         <v>1.86</v>
       </c>
       <c r="S18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="T18" t="n">
         <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
         <v>3.75</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
         <v>1.77</v>
       </c>
       <c r="I19" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,7 +4079,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.41</v>
@@ -4091,7 +4091,7 @@
         <v>2.22</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
         <v>4.2</v>
@@ -4103,7 +4103,7 @@
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W19" t="n">
         <v>1.19</v>
@@ -4115,34 +4115,34 @@
         <v>7.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AB19" t="n">
         <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ19" t="n">
         <v>200</v>
@@ -4172,10 +4172,10 @@
         <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
@@ -4184,41 +4184,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
         <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4291,10 +4291,10 @@
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
         <v>1.09</v>
@@ -4357,7 +4357,7 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
         <v>4.6</v>
@@ -4369,7 +4369,7 @@
         <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4381,10 +4381,10 @@
         <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
@@ -4393,7 +4393,7 @@
         <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC20" t="n">
         <v>11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC21" t="n">
-        <v>10</v>
-      </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
       </c>
       <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK21" t="n">
         <v>24</v>
       </c>
-      <c r="AI21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>26</v>
-      </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
         <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
         <v>4.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
         <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
         <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.76</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H22" t="n">
         <v>2.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
@@ -4688,7 +4688,7 @@
         <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4763,7 +4763,7 @@
         <v>4.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW22" t="n">
         <v>4.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -4864,7 +4864,7 @@
         <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
         <v>9.6</v>
@@ -4948,7 +4948,7 @@
         <v>14</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT23" t="n">
         <v>3.35</v>
@@ -4957,44 +4957,44 @@
         <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
         <v>13.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AZ23" t="n">
         <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF23" t="n">
         <v>18.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G24" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
         <v>4.2</v>
@@ -5055,28 +5055,28 @@
         <v>1.26</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5088,7 +5088,7 @@
         <v>15.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB24" t="n">
         <v>19.5</v>
@@ -5100,13 +5100,13 @@
         <v>12.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG24" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>970</v>
@@ -5130,49 +5130,49 @@
         <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ24" t="n">
         <v>3.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
         <v>4.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="AY24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ24" t="n">
-        <v>13</v>
-      </c>
       <c r="BA24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
         <v>4.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD24" t="n">
         <v>4.6</v>
@@ -5184,11 +5184,11 @@
         <v>4.7</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5225,10 +5225,10 @@
         <v>3.15</v>
       </c>
       <c r="H25" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J25" t="n">
         <v>3.8</v>
@@ -5252,7 +5252,7 @@
         <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.66</v>
@@ -5261,13 +5261,13 @@
         <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U25" t="n">
         <v>2.66</v>
       </c>
       <c r="V25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W25" t="n">
         <v>1.47</v>
@@ -5327,7 +5327,7 @@
         <v>13</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AQ25" t="n">
         <v>14</v>
@@ -5345,7 +5345,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW25" t="n">
         <v>18.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
         <v>3.15</v>
@@ -5431,7 +5431,7 @@
         <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5455,10 +5455,10 @@
         <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="G27" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J27" t="n">
         <v>5.7</v>
@@ -5625,152 +5625,152 @@
         <v>5.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
         <v>1.03</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R27" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="S27" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="T27" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W27" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="X27" t="n">
         <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA27" t="n">
         <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC27" t="n">
         <v>13.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AM27" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AO27" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP27" t="n">
         <v>32</v>
       </c>
       <c r="AQ27" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR27" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AS27" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
         <v>12.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE27" t="n">
         <v>65</v>
       </c>
       <c r="BF27" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5801,25 +5801,25 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.31</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.32</v>
       </c>
       <c r="H28" t="n">
         <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
@@ -5831,7 +5831,7 @@
         <v>1.21</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q28" t="n">
         <v>1.63</v>
@@ -5840,19 +5840,19 @@
         <v>1.59</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
         <v>2.14</v>
       </c>
       <c r="U28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V28" t="n">
         <v>1.08</v>
       </c>
       <c r="W28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X28" t="n">
         <v>25</v>
@@ -5876,7 +5876,7 @@
         <v>42</v>
       </c>
       <c r="AE28" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF28" t="n">
         <v>7.6</v>
@@ -5885,7 +5885,7 @@
         <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI28" t="n">
         <v>150</v>
@@ -5915,13 +5915,13 @@
         <v>34</v>
       </c>
       <c r="AR28" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS28" t="n">
         <v>120</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>13.5</v>
@@ -5939,7 +5939,7 @@
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA28" t="n">
         <v>55</v>
@@ -5954,7 +5954,7 @@
         <v>34</v>
       </c>
       <c r="BE28" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BF28" t="n">
         <v>4.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H29" t="n">
         <v>3.1</v>
@@ -6010,7 +6010,7 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.24</v>
@@ -6031,7 +6031,7 @@
         <v>1.43</v>
       </c>
       <c r="R29" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S29" t="n">
         <v>2.08</v>
@@ -6046,16 +6046,16 @@
         <v>1.46</v>
       </c>
       <c r="W29" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y29" t="n">
         <v>22</v>
       </c>
       <c r="Z29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA29" t="n">
         <v>55</v>
@@ -6106,13 +6106,13 @@
         <v>32</v>
       </c>
       <c r="AQ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR29" t="n">
         <v>26</v>
       </c>
       <c r="AS29" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT29" t="n">
         <v>18.5</v>
@@ -6142,7 +6142,7 @@
         <v>27</v>
       </c>
       <c r="BC29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD29" t="n">
         <v>21</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -6189,64 +6189,64 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="H30" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
         <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K30" t="n">
         <v>4.2</v>
       </c>
       <c r="L30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.5</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.49</v>
-      </c>
       <c r="Q30" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R30" t="n">
         <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
         <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
         <v>1.09</v>
       </c>
       <c r="W30" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="X30" t="n">
         <v>9.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
         <v>100</v>
@@ -6255,34 +6255,34 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC30" t="n">
         <v>10.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG30" t="n">
         <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
         <v>90</v>
@@ -6291,16 +6291,16 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR30" t="n">
         <v>5.9</v>
@@ -6309,25 +6309,25 @@
         <v>6.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
       </c>
       <c r="AX30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AY30" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -6342,17 +6342,17 @@
         <v>5.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
         <v>6.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G31" t="n">
         <v>2.62</v>
@@ -6398,7 +6398,7 @@
         <v>1.66</v>
       </c>
       <c r="K31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="L31" t="n">
         <v>1.4</v>
@@ -6413,16 +6413,16 @@
         <v>1.02</v>
       </c>
       <c r="P31" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R31" t="n">
         <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -6586,10 +6586,10 @@
         <v>2.42</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J32" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
         <v>3.25</v>
@@ -6610,7 +6610,7 @@
         <v>1.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.16</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -6774,25 +6774,25 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H33" t="n">
         <v>4.3</v>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
         <v>2.92</v>
@@ -6801,7 +6801,7 @@
         <v>1.46</v>
       </c>
       <c r="P33" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q33" t="n">
         <v>2.36</v>
@@ -6813,7 +6813,7 @@
         <v>4.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
         <v>1.83</v>
@@ -6822,7 +6822,7 @@
         <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6840,7 +6840,7 @@
         <v>7.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
@@ -6879,16 +6879,16 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>11</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT33" t="n">
         <v>6.6</v>
@@ -6897,10 +6897,10 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX33" t="n">
         <v>10</v>
@@ -6909,32 +6909,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB33" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BC33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE33" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>10</v>
-      </c>
       <c r="BF33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H34" t="n">
         <v>2.02</v>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -6989,7 +6989,7 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
@@ -6998,13 +6998,13 @@
         <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R34" t="n">
         <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
         <v>2.06</v>
@@ -7013,10 +7013,10 @@
         <v>1.74</v>
       </c>
       <c r="V34" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="W34" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
         <v>10.5</v>
@@ -7031,13 +7031,13 @@
         <v>34</v>
       </c>
       <c r="AB34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC34" t="n">
         <v>7.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
         <v>34</v>
@@ -7073,62 +7073,62 @@
         <v>32</v>
       </c>
       <c r="AP34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX34" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY34" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC34" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC34" t="n">
-        <v>6</v>
-      </c>
       <c r="BD34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
         <v>1.84</v>
       </c>
       <c r="H35" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.42</v>
@@ -7204,16 +7204,16 @@
         <v>1.96</v>
       </c>
       <c r="U35" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V35" t="n">
         <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y35" t="n">
         <v>22</v>
@@ -7228,7 +7228,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD35" t="n">
         <v>29</v>
@@ -7240,10 +7240,10 @@
         <v>12</v>
       </c>
       <c r="AG35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH35" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI35" t="n">
         <v>120</v>
@@ -7258,7 +7258,7 @@
         <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="n">
         <v>16</v>
@@ -7270,25 +7270,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT35" t="n">
         <v>6.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX35" t="n">
         <v>8.4</v>
@@ -7297,32 +7297,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB35" t="n">
         <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -7356,19 +7356,19 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H36" t="n">
         <v>2.54</v>
       </c>
       <c r="I36" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.48</v>
@@ -7377,13 +7377,13 @@
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P36" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q36" t="n">
         <v>2.46</v>
@@ -7398,25 +7398,25 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V36" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z36" t="n">
         <v>19</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB36" t="n">
         <v>11</v>
@@ -7431,7 +7431,7 @@
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG36" t="n">
         <v>17</v>
@@ -7470,7 +7470,7 @@
         <v>13.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT36" t="n">
         <v>8.199999999999999</v>
@@ -7479,44 +7479,44 @@
         <v>6.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC36" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA36" t="n">
+      <c r="BD36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE36" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC36" t="n">
+      <c r="BF36" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG36" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H37" t="n">
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
         <v>3.5</v>
@@ -7592,19 +7592,19 @@
         <v>2.26</v>
       </c>
       <c r="U37" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V37" t="n">
         <v>1.17</v>
       </c>
       <c r="W37" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X37" t="n">
         <v>11.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="n">
         <v>55</v>
@@ -7661,10 +7661,10 @@
         <v>13</v>
       </c>
       <c r="AR37" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT37" t="n">
         <v>5.6</v>
@@ -7676,7 +7676,7 @@
         <v>18.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX37" t="n">
         <v>7.8</v>
@@ -7688,7 +7688,7 @@
         <v>22</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB37" t="n">
         <v>16.5</v>
@@ -7697,20 +7697,20 @@
         <v>20</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF37" t="n">
         <v>13.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="H38" t="n">
         <v>3.2</v>
       </c>
       <c r="I38" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J38" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="K38" t="n">
         <v>8.4</v>
@@ -7765,7 +7765,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.02</v>
@@ -7783,16 +7783,16 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V38" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -7935,170 +7935,170 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
         <v>1.94</v>
       </c>
       <c r="U39" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V39" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA39" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD39" t="n">
         <v>27</v>
       </c>
       <c r="AE39" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF39" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG39" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI39" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ39" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AK39" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL39" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM39" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN39" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AO39" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF39" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -8323,58 +8323,58 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G41" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I41" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="O41" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P41" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U41" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V41" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W41" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU41" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY41" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>4.9</v>
       </c>
       <c r="G42" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J42" t="n">
         <v>3.4</v>
@@ -8547,7 +8547,7 @@
         <v>1.48</v>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
         <v>2.42</v>
@@ -8556,7 +8556,7 @@
         <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T42" t="n">
         <v>2.12</v>
@@ -8568,10 +8568,10 @@
         <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y42" t="n">
         <v>7.4</v>
@@ -8628,59 +8628,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AR42" t="n">
         <v>8.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT42" t="n">
         <v>11.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AV42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC42" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG42" t="n">
         <v>16</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -8717,13 +8717,13 @@
         <v>4.1</v>
       </c>
       <c r="H43" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I43" t="n">
         <v>2.58</v>
       </c>
       <c r="J43" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K43" t="n">
         <v>3.05</v>
@@ -8774,7 +8774,7 @@
         <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB43" t="n">
         <v>1000</v>
@@ -8849,10 +8849,10 @@
         <v>5.7</v>
       </c>
       <c r="AZ43" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB43" t="n">
         <v>50</v>
@@ -8864,17 +8864,17 @@
         <v>7.6</v>
       </c>
       <c r="BE43" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF43" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>7.6</v>
       </c>
       <c r="BG43" t="n">
         <v>7</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -8905,34 +8905,34 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="G44" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I44" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K44" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="N44" t="n">
         <v>1.91</v>
       </c>
       <c r="O44" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="P44" t="n">
         <v>1.26</v>
@@ -8947,22 +8947,22 @@
         <v>3.95</v>
       </c>
       <c r="T44" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U44" t="n">
         <v>1.45</v>
       </c>
       <c r="V44" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W44" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="X44" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z44" t="n">
         <v>22</v>
@@ -8971,22 +8971,22 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -9013,40 +9013,40 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ44" t="n">
         <v>6.2</v>
       </c>
       <c r="AR44" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS44" t="n">
         <v>32</v>
       </c>
       <c r="AT44" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW44" t="n">
         <v>34</v>
       </c>
       <c r="AX44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ44" t="n">
         <v>24</v>
       </c>
       <c r="BA44" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BB44" t="n">
         <v>30</v>
@@ -9055,20 +9055,20 @@
         <v>32</v>
       </c>
       <c r="BD44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE44" t="n">
-        <v>55</v>
+        <v>4.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG44" t="n">
         <v>40</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2.86</v>
       </c>
       <c r="G45" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H45" t="n">
         <v>2.66</v>
@@ -9147,7 +9147,7 @@
         <v>1.89</v>
       </c>
       <c r="V45" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W45" t="n">
         <v>1.42</v>
@@ -9159,7 +9159,7 @@
         <v>12.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA45" t="n">
         <v>1000</v>
@@ -9216,16 +9216,16 @@
         <v>2.22</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AU45" t="n">
         <v>1.95</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AW45" t="n">
         <v>2.32</v>
@@ -9237,19 +9237,19 @@
         <v>2.16</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BA45" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BB45" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BC45" t="n">
         <v>2.34</v>
       </c>
       <c r="BD45" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BE45" t="n">
         <v>2.44</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -763,16 +763,16 @@
         <v>2.44</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.36</v>
@@ -784,16 +784,16 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.92</v>
@@ -805,16 +805,16 @@
         <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
         <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="n">
         <v>24</v>
@@ -832,7 +832,7 @@
         <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>17.5</v>
@@ -859,13 +859,13 @@
         <v>70</v>
       </c>
       <c r="AN2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP2" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>13.5</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -916,11 +916,11 @@
         <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1071,7 +1071,7 @@
         <v>4.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AU3" t="n">
         <v>5.8</v>
@@ -1095,7 +1095,7 @@
         <v>3.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="BC3" t="n">
         <v>4.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,7 +1363,7 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>7.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1578,7 +1578,7 @@
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V6" t="n">
         <v>1.16</v>
@@ -1590,7 +1590,7 @@
         <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
         <v>65</v>
@@ -1602,10 +1602,10 @@
         <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>130</v>
@@ -1614,7 +1614,7 @@
         <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>29</v>
@@ -1623,10 +1623,10 @@
         <v>130</v>
       </c>
       <c r="AJ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK6" t="n">
         <v>21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
@@ -1647,10 +1647,10 @@
         <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1662,7 +1662,7 @@
         <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1683,20 +1683,20 @@
         <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,22 +1751,22 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
         <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,22 +1945,22 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -1969,10 +1969,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
         <v>1.28</v>
@@ -2127,7 +2127,7 @@
         <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
         <v>7.6</v>
@@ -2160,7 +2160,7 @@
         <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>1.07</v>
@@ -2169,7 +2169,7 @@
         <v>4.5</v>
       </c>
       <c r="X9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y9" t="n">
         <v>48</v>
@@ -2196,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>36</v>
@@ -2217,34 +2217,34 @@
         <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AO9" t="n">
         <v>270</v>
       </c>
       <c r="AP9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
         <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
         <v>34</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
@@ -2253,32 +2253,32 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
         <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
         <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2309,64 +2309,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
         <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X10" t="n">
         <v>42</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2378,13 +2378,13 @@
         <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
         <v>13.5</v>
@@ -2396,22 +2396,22 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
         <v>13.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
         <v>60</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO10" t="n">
         <v>34</v>
@@ -2423,10 +2423,10 @@
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AS10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT10" t="n">
         <v>15.5</v>
@@ -2438,7 +2438,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
@@ -2453,7 +2453,7 @@
         <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
@@ -2465,14 +2465,14 @@
         <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
         <v>30</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
         <v>6.6</v>
@@ -2515,34 +2515,34 @@
         <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>2.12</v>
@@ -2554,13 +2554,13 @@
         <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
         <v>60</v>
@@ -2572,7 +2572,7 @@
         <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>28</v>
@@ -2605,7 +2605,7 @@
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO11" t="n">
         <v>210</v>
@@ -2620,7 +2620,7 @@
         <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -2635,7 +2635,7 @@
         <v>10.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
         <v>9</v>
@@ -2644,29 +2644,29 @@
         <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
         <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
@@ -2721,22 +2721,22 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -2915,19 +2915,19 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
         <v>2.88</v>
@@ -2969,7 +2969,7 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>9.800000000000001</v>
@@ -2999,19 +2999,19 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
         <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>8.4</v>
@@ -3020,7 +3020,7 @@
         <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13" t="n">
         <v>17</v>
@@ -3041,20 +3041,20 @@
         <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
         <v>3.25</v>
@@ -3100,34 +3100,34 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
         <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
         <v>2.04</v>
@@ -3169,10 +3169,10 @@
         <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>55</v>
@@ -3199,22 +3199,22 @@
         <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -3223,32 +3223,32 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="BD14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG14" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H15" t="n">
         <v>9.199999999999999</v>
@@ -3294,7 +3294,7 @@
         <v>6.2</v>
       </c>
       <c r="K15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.18</v>
@@ -3381,68 +3381,68 @@
         <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
         <v>2.92</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3500,7 +3500,7 @@
         <v>6.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
         <v>2.8</v>
@@ -3515,7 +3515,7 @@
         <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U16" t="n">
         <v>2.6</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H17" t="n">
         <v>5.3</v>
@@ -3682,7 +3682,7 @@
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
         <v>25</v>
@@ -3739,7 +3739,7 @@
         <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>85</v>
@@ -3784,7 +3784,7 @@
         <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
@@ -3891,7 +3891,7 @@
         <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q18" t="n">
         <v>1.45</v>
@@ -3903,34 +3903,34 @@
         <v>2.02</v>
       </c>
       <c r="T18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X18" t="n">
         <v>32</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="n">
         <v>20</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -3945,13 +3945,13 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3960,71 +3960,71 @@
         <v>25</v>
       </c>
       <c r="AM18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO18" t="n">
         <v>970</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>11</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
         <v>6.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4103,7 +4103,7 @@
         <v>1.84</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W19" t="n">
         <v>1.18</v>
@@ -4121,7 +4121,7 @@
         <v>970</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
         <v>8.199999999999999</v>
@@ -4133,16 +4133,16 @@
         <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ19" t="n">
         <v>200</v>
@@ -4160,7 +4160,7 @@
         <v>170</v>
       </c>
       <c r="AO19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AP19" t="n">
         <v>10</v>
@@ -4172,7 +4172,7 @@
         <v>8.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
@@ -4184,7 +4184,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE19" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD19" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>12</v>
-      </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I20" t="n">
         <v>2.78</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4276,7 +4276,7 @@
         <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
         <v>1.78</v>
@@ -4288,7 +4288,7 @@
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
         <v>1.84</v>
@@ -4300,7 +4300,7 @@
         <v>1.56</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
         <v>13.5</v>
@@ -4309,10 +4309,10 @@
         <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="n">
         <v>11</v>
@@ -4342,7 +4342,7 @@
         <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL20" t="n">
         <v>55</v>
@@ -4354,7 +4354,7 @@
         <v>42</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
         <v>9.800000000000001</v>
@@ -4369,16 +4369,16 @@
         <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU20" t="n">
         <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -4390,29 +4390,29 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE20" t="n">
         <v>10</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G21" t="n">
         <v>2.64</v>
@@ -4452,10 +4452,10 @@
         <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
@@ -4473,10 +4473,10 @@
         <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
@@ -4485,16 +4485,16 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
@@ -4593,20 +4593,20 @@
         <v>9</v>
       </c>
       <c r="BD21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>10</v>
       </c>
       <c r="BF21" t="n">
         <v>25</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
         <v>2.58</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J22" t="n">
         <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -4664,13 +4664,13 @@
         <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.35</v>
@@ -4685,122 +4685,122 @@
         <v>2.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
         <v>1.63</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
         <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>42</v>
       </c>
       <c r="AM22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
         <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,146 +4855,146 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="X23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z23" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA23" t="n">
-        <v>500</v>
+        <v>670</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE23" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AO23" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AR23" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AX23" t="n">
         <v>7.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
         <v>12.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG23" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="I24" t="n">
         <v>4</v>
@@ -5046,16 +5046,16 @@
         <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
         <v>3.35</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
@@ -5064,13 +5064,13 @@
         <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
@@ -5079,16 +5079,16 @@
         <v>1.76</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
         <v>30</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB24" t="n">
         <v>10</v>
@@ -5103,7 +5103,7 @@
         <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG24" t="n">
         <v>12.5</v>
@@ -5130,7 +5130,7 @@
         <v>23</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -5139,13 +5139,13 @@
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>6.8</v>
@@ -5154,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
@@ -5175,20 +5175,20 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF24" t="n">
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H25" t="n">
         <v>9.800000000000001</v>
@@ -5231,7 +5231,7 @@
         <v>11.5</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
@@ -5270,7 +5270,7 @@
         <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="X25" t="n">
         <v>27</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="H26" t="n">
         <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.32</v>
@@ -5455,16 +5455,16 @@
         <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
         <v>2.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5607,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G27" t="n">
         <v>2.78</v>
       </c>
       <c r="H27" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I27" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
         <v>4.5</v>
@@ -5652,10 +5652,10 @@
         <v>1.47</v>
       </c>
       <c r="U27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V27" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
         <v>1.56</v>
@@ -5673,10 +5673,10 @@
         <v>38</v>
       </c>
       <c r="AB27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD27" t="n">
         <v>14</v>
@@ -5685,13 +5685,13 @@
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>13.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
         <v>32</v>
@@ -5709,13 +5709,13 @@
         <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO27" t="n">
         <v>14</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27" t="n">
         <v>15.5</v>
@@ -5757,10 +5757,10 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF27" t="n">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
         <v>4.3</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I28" t="n">
         <v>2.16</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
         <v>4.1</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6001,19 +6001,19 @@
         <v>2.18</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
         <v>4.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
         <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
@@ -6028,7 +6028,7 @@
         <v>1.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R29" t="n">
         <v>1.26</v>
@@ -6037,16 +6037,16 @@
         <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V29" t="n">
         <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X29" t="n">
         <v>13.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6198,13 +6198,13 @@
         <v>2.66</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.32</v>
@@ -6216,7 +6216,7 @@
         <v>3.55</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
         <v>1.87</v>
@@ -6234,10 +6234,10 @@
         <v>1.72</v>
       </c>
       <c r="U30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W30" t="n">
         <v>1.53</v>
@@ -6267,7 +6267,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>970</v>
@@ -6303,56 +6303,56 @@
         <v>8.6</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AW30" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
-        <v>13.5</v>
+        <v>3.95</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AZ30" t="n">
         <v>12.5</v>
       </c>
       <c r="BA30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF30" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.49</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.5</v>
-      </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
         <v>6.4</v>
       </c>
       <c r="J31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>1.25</v>
@@ -6413,22 +6413,22 @@
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q31" t="n">
         <v>1.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T31" t="n">
         <v>1.68</v>
       </c>
       <c r="U31" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.18</v>
@@ -6437,22 +6437,22 @@
         <v>3</v>
       </c>
       <c r="X31" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y31" t="n">
         <v>32</v>
       </c>
       <c r="Z31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA31" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB31" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD31" t="n">
         <v>24</v>
@@ -6461,25 +6461,25 @@
         <v>75</v>
       </c>
       <c r="AF31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>11</v>
       </c>
-      <c r="AG31" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
         <v>80</v>
@@ -6488,7 +6488,7 @@
         <v>4.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP31" t="n">
         <v>32</v>
@@ -6500,10 +6500,10 @@
         <v>50</v>
       </c>
       <c r="AS31" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU31" t="n">
         <v>12.5</v>
@@ -6527,13 +6527,13 @@
         <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
       </c>
       <c r="BD31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE31" t="n">
         <v>65</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G32" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I32" t="n">
         <v>12</v>
-      </c>
-      <c r="I32" t="n">
-        <v>12.5</v>
       </c>
       <c r="J32" t="n">
         <v>6.6</v>
@@ -6601,16 +6601,16 @@
         <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
         <v>1.57</v>
@@ -6619,22 +6619,22 @@
         <v>2.68</v>
       </c>
       <c r="T32" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W32" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z32" t="n">
         <v>120</v>
@@ -6649,13 +6649,13 @@
         <v>14.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE32" t="n">
         <v>220</v>
       </c>
       <c r="AF32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
@@ -6667,13 +6667,13 @@
         <v>170</v>
       </c>
       <c r="AJ32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK32" t="n">
         <v>13.5</v>
       </c>
       <c r="AL32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM32" t="n">
         <v>190</v>
@@ -6685,19 +6685,19 @@
         <v>260</v>
       </c>
       <c r="AP32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ32" t="n">
         <v>30</v>
       </c>
       <c r="AR32" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AS32" t="n">
         <v>130</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU32" t="n">
         <v>13.5</v>
@@ -6706,10 +6706,10 @@
         <v>38</v>
       </c>
       <c r="AW32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY32" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
         <v>30</v>
       </c>
       <c r="BA32" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB32" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC32" t="n">
         <v>12.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>2.14</v>
       </c>
       <c r="G33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I33" t="n">
         <v>3.2</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L33" t="n">
         <v>1.24</v>
@@ -6795,7 +6795,7 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O33" t="n">
         <v>1.14</v>
@@ -6804,25 +6804,25 @@
         <v>3.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R33" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S33" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V33" t="n">
         <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X33" t="n">
         <v>36</v>
@@ -6831,13 +6831,13 @@
         <v>22</v>
       </c>
       <c r="Z33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA33" t="n">
         <v>55</v>
       </c>
       <c r="AB33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC33" t="n">
         <v>11.5</v>
@@ -6846,10 +6846,10 @@
         <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF33" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG33" t="n">
         <v>11.5</v>
@@ -6864,7 +6864,7 @@
         <v>29</v>
       </c>
       <c r="AK33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL33" t="n">
         <v>23</v>
@@ -6876,7 +6876,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP33" t="n">
         <v>32</v>
@@ -6885,7 +6885,7 @@
         <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS33" t="n">
         <v>48</v>
@@ -6897,13 +6897,13 @@
         <v>11</v>
       </c>
       <c r="AV33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY33" t="n">
         <v>11</v>
@@ -6927,14 +6927,14 @@
         <v>40</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R34" t="n">
         <v>1.17</v>
@@ -7019,7 +7019,7 @@
         <v>2.58</v>
       </c>
       <c r="X34" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" t="n">
         <v>1000</v>
@@ -7076,13 +7076,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT34" t="n">
         <v>4.6</v>
@@ -7091,10 +7091,10 @@
         <v>4.3</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX34" t="n">
         <v>3.85</v>
@@ -7103,32 +7103,32 @@
         <v>4.7</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB34" t="n">
         <v>5</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF34" t="n">
         <v>11</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="H35" t="n">
         <v>11</v>
@@ -7171,10 +7171,10 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>1.4</v>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="O35" t="n">
         <v>1.02</v>
@@ -7210,7 +7210,7 @@
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -7353,92 +7353,92 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="G36" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="H36" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="I36" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="J36" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K36" t="n">
         <v>3.25</v>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M36" t="n">
         <v>1.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O36" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P36" t="n">
         <v>1.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
         <v>3.45</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U36" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="X36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>11</v>
       </c>
       <c r="AC36" t="n">
         <v>8</v>
       </c>
       <c r="AD36" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE36" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH36" t="n">
         <v>27</v>
       </c>
-      <c r="AG36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>28</v>
-      </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
@@ -7458,65 +7458,65 @@
         <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AU36" t="n">
         <v>3.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB36" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC36" t="n">
         <v>4.9</v>
       </c>
       <c r="BD36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF36" t="n">
         <v>5</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G37" t="n">
         <v>2.08</v>
@@ -7595,7 +7595,7 @@
         <v>1.83</v>
       </c>
       <c r="V37" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
         <v>1.92</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -7744,55 +7744,55 @@
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I38" t="n">
         <v>2.28</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K38" t="n">
         <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
         <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P38" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W38" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X38" t="n">
         <v>10</v>
@@ -7804,7 +7804,7 @@
         <v>12.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AB38" t="n">
         <v>12.5</v>
@@ -7822,7 +7822,7 @@
         <v>36</v>
       </c>
       <c r="AG38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH38" t="n">
         <v>26</v>
@@ -7834,7 +7834,7 @@
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -7849,7 +7849,7 @@
         <v>28</v>
       </c>
       <c r="AP38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>6</v>
@@ -7858,7 +7858,7 @@
         <v>10</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT38" t="n">
         <v>9.6</v>
@@ -7870,10 +7870,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY38" t="n">
         <v>15.5</v>
@@ -7882,29 +7882,29 @@
         <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG38" t="n">
         <v>15</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G39" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H39" t="n">
         <v>5.3</v>
@@ -7950,10 +7950,10 @@
         <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L39" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
         <v>1.08</v>
@@ -7986,7 +7986,7 @@
         <v>1.19</v>
       </c>
       <c r="W39" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X39" t="n">
         <v>14.5</v>
@@ -8058,7 +8058,7 @@
         <v>6.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV39" t="n">
         <v>4.9</v>
@@ -8079,7 +8079,7 @@
         <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC39" t="n">
         <v>5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -8153,16 +8153,16 @@
         <v>1.11</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O40" t="n">
         <v>1.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R40" t="n">
         <v>1.18</v>
@@ -8171,10 +8171,10 @@
         <v>4.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V40" t="n">
         <v>1.57</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G41" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H41" t="n">
         <v>6.2</v>
@@ -8338,10 +8338,10 @@
         <v>3.5</v>
       </c>
       <c r="K41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L41" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
         <v>1.12</v>
@@ -8371,19 +8371,19 @@
         <v>1.69</v>
       </c>
       <c r="V41" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X41" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y41" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA41" t="n">
         <v>260</v>
@@ -8401,10 +8401,10 @@
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG41" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH41" t="n">
         <v>55</v>
@@ -8440,7 +8440,7 @@
         <v>25</v>
       </c>
       <c r="AS41" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AT41" t="n">
         <v>5.6</v>
@@ -8449,7 +8449,7 @@
         <v>7.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AW41" t="n">
         <v>40</v>
@@ -8458,25 +8458,25 @@
         <v>7.8</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA41" t="n">
         <v>44</v>
       </c>
       <c r="BB41" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BD41" t="n">
         <v>32</v>
       </c>
       <c r="BE41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF41" t="n">
         <v>15</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G42" t="n">
-        <v>3.05</v>
+        <v>990</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="K42" t="n">
-        <v>8.4</v>
+        <v>500</v>
       </c>
       <c r="L42" t="n">
         <v>1.41</v>
@@ -8541,7 +8541,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>1.02</v>
@@ -8550,7 +8550,7 @@
         <v>1.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
@@ -8565,10 +8565,10 @@
         <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W42" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -8720,10 +8720,10 @@
         <v>5.1</v>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
         <v>3.5</v>
@@ -8741,7 +8741,7 @@
         <v>1.4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q43" t="n">
         <v>2.18</v>
@@ -8759,7 +8759,7 @@
         <v>1.88</v>
       </c>
       <c r="V43" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
         <v>2</v>
@@ -8777,7 +8777,7 @@
         <v>180</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
@@ -8825,10 +8825,10 @@
         <v>10</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS43" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT43" t="n">
         <v>6.4</v>
@@ -8837,10 +8837,10 @@
         <v>6.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AW43" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX43" t="n">
         <v>9</v>
@@ -8849,10 +8849,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BA43" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB43" t="n">
         <v>18</v>
@@ -8861,20 +8861,20 @@
         <v>18.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG43" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>2.82</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L47" t="n">
         <v>1.7</v>
@@ -9532,7 +9532,7 @@
         <v>2.4</v>
       </c>
       <c r="U47" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
         <v>1.61</v>
@@ -9628,7 +9628,7 @@
         <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB47" t="n">
         <v>50</v>
@@ -9643,14 +9643,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF47" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG47" t="n">
         <v>7.2</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G48" t="n">
         <v>3.15</v>
@@ -9696,7 +9696,7 @@
         <v>2.68</v>
       </c>
       <c r="K48" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,10 +9705,10 @@
         <v>1.21</v>
       </c>
       <c r="N48" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O48" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="P48" t="n">
         <v>1.25</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BF48" t="n">
         <v>38</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -9914,13 +9914,13 @@
         <v>1.23</v>
       </c>
       <c r="S49" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T49" t="n">
         <v>1.89</v>
       </c>
       <c r="U49" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V49" t="n">
         <v>1.49</v>
@@ -9998,7 +9998,7 @@
         <v>2.06</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="AV49" t="n">
         <v>2.14</v>
@@ -10007,7 +10007,7 @@
         <v>2.32</v>
       </c>
       <c r="AX49" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY49" t="n">
         <v>2.16</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -769,7 +769,7 @@
         <v>3.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -781,37 +781,37 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
         <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
         <v>15</v>
@@ -820,22 +820,22 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -850,43 +850,43 @@
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
         <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
         <v>15.5</v>
@@ -895,32 +895,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
         <v>34</v>
       </c>
       <c r="BB2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -975,61 +975,61 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB3" t="n">
         <v>950</v>
       </c>
-      <c r="Z3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF3" t="n">
         <v>75</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>950</v>
@@ -1038,83 +1038,83 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>340</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="P4" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.04</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>1.47</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.94</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.96</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.16</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.24</v>
+        <v>1.48</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.32</v>
+        <v>1.48</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.44</v>
+        <v>1.48</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1360,31 +1360,31 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
         <v>1.16</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.09</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
         <v>1.72</v>
@@ -1548,10 +1548,10 @@
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1566,7 +1566,7 @@
         <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1578,49 +1578,49 @@
         <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.16</v>
       </c>
       <c r="W6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AB6" t="n">
         <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1629,13 +1629,13 @@
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,13 +1644,13 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1692,11 +1692,11 @@
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1751,13 +1751,13 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
@@ -1769,10 +1769,10 @@
         <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.12</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
         <v>4.5</v>
@@ -1972,7 +1972,7 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J9" t="n">
         <v>6.8</v>
@@ -2142,22 +2142,22 @@
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
         <v>1.86</v>
@@ -2169,49 +2169,49 @@
         <v>4.7</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z9" t="n">
         <v>160</v>
       </c>
-      <c r="Z9" t="n">
-        <v>150</v>
-      </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>780</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AE9" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
         <v>460</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>380</v>
@@ -2220,65 +2220,65 @@
         <v>3.95</v>
       </c>
       <c r="AO9" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AP9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>14</v>
-      </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF9" t="n">
         <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.56</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.57</v>
       </c>
       <c r="H10" t="n">
         <v>5.5</v>
@@ -2321,7 +2321,7 @@
         <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
         <v>5.7</v>
@@ -2336,31 +2336,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X10" t="n">
         <v>38</v>
@@ -2372,13 +2372,13 @@
         <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
         <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2393,10 +2393,10 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
         <v>16</v>
@@ -2405,16 +2405,16 @@
         <v>13.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN10" t="n">
         <v>4.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
         <v>36</v>
@@ -2423,7 +2423,7 @@
         <v>30</v>
       </c>
       <c r="AR10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS10" t="n">
         <v>100</v>
@@ -2435,10 +2435,10 @@
         <v>13</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
@@ -2453,13 +2453,13 @@
         <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE10" t="n">
         <v>50</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
         <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V11" t="n">
         <v>1.25</v>
@@ -2557,31 +2557,31 @@
         <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
         <v>100</v>
       </c>
       <c r="AA11" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE11" t="n">
         <v>320</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>9.800000000000001</v>
@@ -2593,16 +2593,16 @@
         <v>250</v>
       </c>
       <c r="AJ11" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AL11" t="n">
         <v>75</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>9.800000000000001</v>
@@ -2611,22 +2611,22 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
         <v>16.5</v>
@@ -2635,7 +2635,7 @@
         <v>10.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -2650,23 +2650,23 @@
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>14.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2745,10 +2745,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
         <v>1.7</v>
@@ -2909,7 +2909,7 @@
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2918,25 +2918,25 @@
         <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
         <v>1.16</v>
@@ -2945,22 +2945,22 @@
         <v>2.42</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
         <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AA13" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
         <v>28</v>
@@ -2984,16 +2984,16 @@
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
         <v>220</v>
@@ -3002,28 +3002,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
         <v>9</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3088,13 +3088,13 @@
         <v>1.05</v>
       </c>
       <c r="G14" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
         <v>3.65</v>
@@ -3109,7 +3109,7 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.21</v>
@@ -3118,19 +3118,19 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.39</v>
@@ -3309,10 +3309,10 @@
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
@@ -3324,7 +3324,7 @@
         <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3342,7 +3342,7 @@
         <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>11.5</v>
@@ -3360,34 +3360,34 @@
         <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AK15" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>55</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
@@ -3396,13 +3396,13 @@
         <v>15.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
         <v>10.5</v>
@@ -3414,35 +3414,35 @@
         <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>14.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
         <v>1.33</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
         <v>14</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
@@ -3506,22 +3506,22 @@
         <v>3.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R16" t="n">
         <v>1.86</v>
       </c>
       <c r="S16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
         <v>4</v>
@@ -3533,13 +3533,13 @@
         <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
         <v>1000</v>
@@ -3548,10 +3548,10 @@
         <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
         <v>1000</v>
@@ -3575,37 +3575,37 @@
         <v>320</v>
       </c>
       <c r="AN16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>4.2</v>
       </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7</v>
-      </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AY16" t="n">
         <v>6.4</v>
@@ -3614,29 +3614,29 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>1.87</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>2.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>4.3</v>
@@ -3685,7 +3685,7 @@
         <v>4.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -3697,140 +3697,140 @@
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S17" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Z17" t="n">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AA17" t="n">
-        <v>95</v>
+        <v>470</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13</v>
-      </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>1.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="AW17" t="n">
-        <v>34</v>
+        <v>1.41</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>1.38</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>1.41</v>
       </c>
       <c r="BB17" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>11.5</v>
+        <v>1.39</v>
       </c>
       <c r="BE17" t="n">
         <v>16</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>1.97</v>
       </c>
       <c r="BG17" t="n">
-        <v>19.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3864,25 +3864,25 @@
         <v>1.65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
         <v>4.5</v>
@@ -3891,16 +3891,16 @@
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
         <v>1.71</v>
@@ -3909,122 +3909,122 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>14</v>
-      </c>
       <c r="BD18" t="n">
-        <v>22</v>
+        <v>1.74</v>
       </c>
       <c r="BE18" t="n">
-        <v>24</v>
+        <v>3.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>2.64</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>1.57</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4085,7 +4085,7 @@
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q19" t="n">
         <v>1.45</v>
@@ -4094,10 +4094,10 @@
         <v>1.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
@@ -4106,7 +4106,7 @@
         <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>80</v>
@@ -4115,13 +4115,13 @@
         <v>65</v>
       </c>
       <c r="Z19" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
@@ -4130,10 +4130,10 @@
         <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG19" t="n">
         <v>16.5</v>
@@ -4145,13 +4145,13 @@
         <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
@@ -4172,7 +4172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -4181,22 +4181,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -4208,17 +4208,17 @@
         <v>11.5</v>
       </c>
       <c r="BE19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF19" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF19" t="n">
-        <v>7</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4258,10 @@
         <v>1.74</v>
       </c>
       <c r="I20" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>3.8</v>
@@ -4276,7 +4276,7 @@
         <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
         <v>1.76</v>
@@ -4297,7 +4297,7 @@
         <v>1.85</v>
       </c>
       <c r="V20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W20" t="n">
         <v>1.18</v>
@@ -4312,49 +4312,49 @@
         <v>9.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG20" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AH20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI20" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AJ20" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AK20" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AL20" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AM20" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AN20" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
         <v>6.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
         <v>15.5</v>
@@ -4378,41 +4378,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AY20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE20" t="n">
         <v>11</v>
       </c>
-      <c r="BD20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
         <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I21" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4467,7 +4467,7 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>1.39</v>
@@ -4476,31 +4476,31 @@
         <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W21" t="n">
         <v>1.47</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
         <v>18.5</v>
@@ -4509,55 +4509,55 @@
         <v>44</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ21" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="AK21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO21" t="n">
         <v>32</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
         <v>32</v>
@@ -4569,13 +4569,13 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
@@ -4584,29 +4584,29 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD21" t="n">
         <v>42</v>
       </c>
-      <c r="BC21" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>10</v>
-      </c>
       <c r="BE21" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BF21" t="n">
         <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
         <v>2.62</v>
       </c>
       <c r="H22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
         <v>3.55</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,16 +4661,16 @@
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
@@ -4688,16 +4688,16 @@
         <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
         <v>65</v>
@@ -4706,7 +4706,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
         <v>15</v>
@@ -4715,10 +4715,10 @@
         <v>46</v>
       </c>
       <c r="AF22" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -4739,68 +4739,68 @@
         <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>38</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="n">
         <v>3.1</v>
@@ -4843,34 +4843,34 @@
         <v>3.25</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.45</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
         <v>1.79</v>
@@ -4882,10 +4882,10 @@
         <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -4894,31 +4894,31 @@
         <v>22</v>
       </c>
       <c r="AA23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
         <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
         <v>36</v>
@@ -4936,25 +4936,25 @@
         <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP23" t="n">
         <v>12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS23" t="n">
         <v>46</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4978,23 +4978,23 @@
         <v>32</v>
       </c>
       <c r="BC23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BD23" t="n">
         <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF23" t="n">
         <v>20</v>
       </c>
       <c r="BG23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>1.3</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>6.2</v>
@@ -5055,7 +5055,7 @@
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
         <v>1.64</v>
@@ -5070,16 +5070,16 @@
         <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X24" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="n">
         <v>40</v>
@@ -5088,7 +5088,7 @@
         <v>130</v>
       </c>
       <c r="AA24" t="n">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="AB24" t="n">
         <v>9.6</v>
@@ -5118,7 +5118,7 @@
         <v>10</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL24" t="n">
         <v>80</v>
@@ -5130,31 +5130,31 @@
         <v>4.7</v>
       </c>
       <c r="AO24" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AP24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
         <v>32</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
         <v>20</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>12.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX24" t="n">
         <v>7.2</v>
@@ -5163,22 +5163,22 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BF24" t="n">
         <v>4.3</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5228,10 +5228,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
@@ -5270,119 +5270,119 @@
         <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="X25" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="Z25" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC25" t="n">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="AD25" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
         <v>29</v>
       </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>1.57</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="AW25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BC25" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>11</v>
-      </c>
       <c r="BD25" t="n">
-        <v>18</v>
+        <v>1.63</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.5</v>
+        <v>1.66</v>
       </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
         <v>2.3</v>
@@ -5428,16 +5428,16 @@
         <v>3.3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.35</v>
@@ -5449,7 +5449,7 @@
         <v>2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
         <v>3.5</v>
@@ -5467,116 +5467,116 @@
         <v>1.76</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
         <v>14</v>
       </c>
       <c r="Z26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>30</v>
       </c>
-      <c r="AA26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>32</v>
-      </c>
       <c r="AK26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G27" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H27" t="n">
         <v>2.54</v>
       </c>
       <c r="I27" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.32</v>
@@ -5655,10 +5655,10 @@
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="X27" t="n">
         <v>90</v>
@@ -5706,7 +5706,7 @@
         <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>1000</v>
@@ -5715,16 +5715,16 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27" t="n">
         <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5733,44 +5733,44 @@
         <v>4.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AW27" t="n">
         <v>7.8</v>
       </c>
       <c r="AX27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY27" t="n">
         <v>7</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AZ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BF27" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BG27" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
         <v>1.67</v>
       </c>
       <c r="S28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T28" t="n">
         <v>1.47</v>
@@ -5858,16 +5858,16 @@
         <v>70</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
         <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="n">
         <v>11</v>
@@ -5876,10 +5876,10 @@
         <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG28" t="n">
         <v>13.5</v>
@@ -5888,10 +5888,10 @@
         <v>15</v>
       </c>
       <c r="AI28" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AJ28" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK28" t="n">
         <v>42</v>
@@ -5900,7 +5900,7 @@
         <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
         <v>13.5</v>
@@ -5909,7 +5909,7 @@
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>15.5</v>
@@ -5918,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AT28" t="n">
         <v>15</v>
@@ -5927,25 +5927,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
         <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BC28" t="n">
         <v>20</v>
@@ -5954,17 +5954,17 @@
         <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
         <v>11</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>3.6</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H29" t="n">
         <v>2.02</v>
       </c>
       <c r="I29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J29" t="n">
         <v>3.65</v>
@@ -6019,22 +6019,22 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>2.18</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
         <v>1.69</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="T29" t="n">
         <v>1.7</v>
@@ -6046,46 +6046,46 @@
         <v>1.87</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>970</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="AF29" t="n">
         <v>90</v>
       </c>
       <c r="AG29" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI29" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ29" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
         <v>190</v>
@@ -6094,16 +6094,16 @@
         <v>250</v>
       </c>
       <c r="AM29" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
         <v>250</v>
       </c>
       <c r="AO29" t="n">
-        <v>14.5</v>
+        <v>85</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>2.54</v>
       </c>
       <c r="AQ29" t="n">
         <v>5.8</v>
@@ -6112,53 +6112,53 @@
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>9</v>
+        <v>2.54</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV29" t="n">
         <v>5.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>2.52</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9</v>
+        <v>2.52</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.6</v>
+        <v>2.68</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="BF29" t="n">
         <v>5.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.7</v>
+        <v>2.72</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>2.04</v>
       </c>
       <c r="G30" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I30" t="n">
         <v>4.5</v>
@@ -6246,55 +6246,55 @@
         <v>13.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF30" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK30" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AP30" t="n">
         <v>9.800000000000001</v>
@@ -6303,10 +6303,10 @@
         <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT30" t="n">
         <v>7</v>
@@ -6318,7 +6318,7 @@
         <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX30" t="n">
         <v>10.5</v>
@@ -6330,29 +6330,29 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC30" t="n">
         <v>21</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF30" t="n">
         <v>17.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6383,100 +6383,100 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G31" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H31" t="n">
         <v>2.66</v>
       </c>
       <c r="I31" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q31" t="n">
         <v>1.94</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="T31" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W31" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X31" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="Y31" t="n">
         <v>14</v>
       </c>
       <c r="Z31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF31" t="n">
         <v>970</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>22</v>
       </c>
       <c r="AG31" t="n">
         <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6580,13 +6580,13 @@
         <v>1.48</v>
       </c>
       <c r="G32" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="n">
         <v>6.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>5.9</v>
@@ -6601,7 +6601,7 @@
         <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.14</v>
@@ -6610,10 +6610,10 @@
         <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R32" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S32" t="n">
         <v>2.12</v>
@@ -6625,16 +6625,16 @@
         <v>2.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W32" t="n">
         <v>3</v>
       </c>
       <c r="X32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z32" t="n">
         <v>55</v>
@@ -6661,7 +6661,7 @@
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
         <v>55</v>
@@ -6670,13 +6670,13 @@
         <v>14</v>
       </c>
       <c r="AK32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM32" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN32" t="n">
         <v>4.5</v>
@@ -6694,13 +6694,13 @@
         <v>48</v>
       </c>
       <c r="AS32" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU32" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>13</v>
       </c>
       <c r="AV32" t="n">
         <v>22</v>
@@ -6715,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA32" t="n">
         <v>46</v>
@@ -6736,11 +6736,11 @@
         <v>4.3</v>
       </c>
       <c r="BG32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6801,16 +6801,16 @@
         <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R33" t="n">
         <v>1.58</v>
       </c>
       <c r="S33" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
         <v>2.18</v>
@@ -6861,7 +6861,7 @@
         <v>160</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK33" t="n">
         <v>13.5</v>
@@ -6870,22 +6870,22 @@
         <v>40</v>
       </c>
       <c r="AM33" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO33" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AP33" t="n">
         <v>22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AS33" t="n">
         <v>130</v>
@@ -6900,10 +6900,10 @@
         <v>38</v>
       </c>
       <c r="AW33" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -6927,14 +6927,14 @@
         <v>160</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G34" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H34" t="n">
         <v>3.1</v>
@@ -7010,13 +7010,13 @@
         <v>1.45</v>
       </c>
       <c r="U34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W34" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X34" t="n">
         <v>36</v>
@@ -7025,10 +7025,10 @@
         <v>23</v>
       </c>
       <c r="Z34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA34" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
         <v>19</v>
@@ -7043,7 +7043,7 @@
         <v>27</v>
       </c>
       <c r="AF34" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG34" t="n">
         <v>11.5</v>
@@ -7055,7 +7055,7 @@
         <v>28</v>
       </c>
       <c r="AJ34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK34" t="n">
         <v>18</v>
@@ -7067,7 +7067,7 @@
         <v>44</v>
       </c>
       <c r="AN34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO34" t="n">
         <v>14.5</v>
@@ -7121,14 +7121,14 @@
         <v>40</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -7210,22 +7210,22 @@
         <v>1.09</v>
       </c>
       <c r="W35" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X35" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>100</v>
+        <v>490</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
         <v>10.5</v>
@@ -7237,10 +7237,10 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AG35" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AH35" t="n">
         <v>1000</v>
@@ -7249,19 +7249,19 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AK35" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="AL35" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
@@ -7270,59 +7270,59 @@
         <v>6.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS35" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT35" t="n">
         <v>4.6</v>
       </c>
       <c r="AU35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX35" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW35" t="n">
+      <c r="AY35" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB35" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC35" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>1.35</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I36" t="n">
         <v>1000</v>
@@ -7368,16 +7368,16 @@
         <v>4.2</v>
       </c>
       <c r="K36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.02</v>
@@ -7389,16 +7389,16 @@
         <v>1.76</v>
       </c>
       <c r="R36" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.02</v>
@@ -7443,7 +7443,7 @@
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK36" t="n">
         <v>1000</v>
@@ -7455,7 +7455,7 @@
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
@@ -7464,13 +7464,13 @@
         <v>1.69</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="AT36" t="n">
         <v>1.42</v>
@@ -7479,10 +7479,10 @@
         <v>1.69</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="AX36" t="n">
         <v>3.25</v>
@@ -7494,7 +7494,7 @@
         <v>1.69</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="BB36" t="n">
         <v>1.53</v>
@@ -7512,11 +7512,11 @@
         <v>2.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -7553,13 +7553,13 @@
         <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I37" t="n">
         <v>3.45</v>
       </c>
       <c r="J37" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K37" t="n">
         <v>3.25</v>
@@ -7571,7 +7571,7 @@
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
         <v>1.55</v>
@@ -7586,7 +7586,7 @@
         <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="T37" t="n">
         <v>2.08</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>1.95</v>
       </c>
       <c r="G38" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H38" t="n">
         <v>4.7</v>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.4</v>
@@ -7774,7 +7774,7 @@
         <v>1.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R38" t="n">
         <v>1.24</v>
@@ -7795,16 +7795,16 @@
         <v>1.96</v>
       </c>
       <c r="X38" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="Y38" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB38" t="n">
         <v>7.2</v>
@@ -7813,7 +7813,7 @@
         <v>7.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE38" t="n">
         <v>1000</v>
@@ -7825,43 +7825,43 @@
         <v>11</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI38" t="n">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM38" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR38" t="n">
         <v>14.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -7870,41 +7870,41 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY38" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA38" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>10.5</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BE38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF38" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG38" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>2.28</v>
       </c>
       <c r="J39" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K39" t="n">
         <v>3.5</v>
@@ -7995,7 +7995,7 @@
         <v>7.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA39" t="n">
         <v>30</v>
@@ -8004,7 +8004,7 @@
         <v>12.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
         <v>12</v>
@@ -8016,7 +8016,7 @@
         <v>32</v>
       </c>
       <c r="AG39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
@@ -8025,7 +8025,7 @@
         <v>60</v>
       </c>
       <c r="AJ39" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK39" t="n">
         <v>160</v>
@@ -8043,10 +8043,10 @@
         <v>28</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR39" t="n">
         <v>10</v>
@@ -8055,13 +8055,13 @@
         <v>10.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU39" t="n">
         <v>6.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW39" t="n">
         <v>14.5</v>
@@ -8070,10 +8070,10 @@
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA39" t="n">
         <v>7.8</v>
@@ -8082,13 +8082,13 @@
         <v>8.4</v>
       </c>
       <c r="BC39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BD39" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BE39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF39" t="n">
         <v>8.4</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G40" t="n">
         <v>1.88</v>
@@ -8159,7 +8159,7 @@
         <v>1.36</v>
       </c>
       <c r="P40" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
         <v>2.08</v>
@@ -8168,7 +8168,7 @@
         <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T40" t="n">
         <v>1.96</v>
@@ -8183,31 +8183,31 @@
         <v>2.12</v>
       </c>
       <c r="X40" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z40" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA40" t="n">
         <v>900</v>
       </c>
       <c r="AB40" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AG40" t="n">
         <v>17.5</v>
@@ -8219,19 +8219,19 @@
         <v>450</v>
       </c>
       <c r="AJ40" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AK40" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AL40" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
         <v>580</v>
       </c>
       <c r="AN40" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -8240,13 +8240,13 @@
         <v>10</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AT40" t="n">
         <v>6.6</v>
@@ -8258,10 +8258,10 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY40" t="n">
         <v>8.800000000000001</v>
@@ -8270,29 +8270,29 @@
         <v>11.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC40" t="n">
         <v>10.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H41" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I41" t="n">
         <v>2.72</v>
@@ -8338,7 +8338,7 @@
         <v>2.98</v>
       </c>
       <c r="K41" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="L41" t="n">
         <v>1.48</v>
@@ -8353,16 +8353,16 @@
         <v>1.48</v>
       </c>
       <c r="P41" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="R41" t="n">
         <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T41" t="n">
         <v>2.02</v>
@@ -8374,7 +8374,7 @@
         <v>1.58</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X41" t="n">
         <v>11</v>
@@ -8398,10 +8398,10 @@
         <v>13.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF41" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG41" t="n">
         <v>17</v>
@@ -8413,7 +8413,7 @@
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK41" t="n">
         <v>1000</v>
@@ -8440,7 +8440,7 @@
         <v>13.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT41" t="n">
         <v>8.4</v>
@@ -8452,7 +8452,7 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX41" t="n">
         <v>17.5</v>
@@ -8461,32 +8461,32 @@
         <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG41" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -8523,13 +8523,13 @@
         <v>1.79</v>
       </c>
       <c r="H42" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
         <v>3.65</v>
@@ -8547,16 +8547,16 @@
         <v>1.51</v>
       </c>
       <c r="P42" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R42" t="n">
         <v>1.21</v>
       </c>
       <c r="S42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T42" t="n">
         <v>2.36</v>
@@ -8571,19 +8571,19 @@
         <v>2.26</v>
       </c>
       <c r="X42" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Z42" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AA42" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC42" t="n">
         <v>8.199999999999999</v>
@@ -8592,10 +8592,10 @@
         <v>46</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF42" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG42" t="n">
         <v>11.5</v>
@@ -8604,31 +8604,31 @@
         <v>50</v>
       </c>
       <c r="AI42" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ42" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK42" t="n">
         <v>25</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM42" t="n">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AN42" t="n">
         <v>18</v>
       </c>
       <c r="AO42" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AP42" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR42" t="n">
         <v>26</v>
@@ -8637,13 +8637,13 @@
         <v>46</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU42" t="n">
         <v>7.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AW42" t="n">
         <v>40</v>
@@ -8661,10 +8661,10 @@
         <v>44</v>
       </c>
       <c r="BB42" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC42" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD42" t="n">
         <v>46</v>
@@ -8673,14 +8673,14 @@
         <v>110</v>
       </c>
       <c r="BF42" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG42" t="n">
         <v>48</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G43" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="K43" t="n">
         <v>8.4</v>
@@ -8735,16 +8735,16 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="O43" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
@@ -8762,7 +8762,7 @@
         <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8819,62 +8819,62 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -8905,19 +8905,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G44" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H44" t="n">
         <v>5.2</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J44" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K44" t="n">
         <v>3.5</v>
@@ -8929,40 +8929,40 @@
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.4</v>
       </c>
       <c r="P44" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S44" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U44" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X44" t="n">
         <v>11</v>
       </c>
       <c r="Y44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z44" t="n">
         <v>120</v>
@@ -8986,7 +8986,7 @@
         <v>12</v>
       </c>
       <c r="AG44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH44" t="n">
         <v>55</v>
@@ -8998,10 +8998,10 @@
         <v>90</v>
       </c>
       <c r="AK44" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AL44" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM44" t="n">
         <v>580</v>
@@ -9013,7 +9013,7 @@
         <v>150</v>
       </c>
       <c r="AP44" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ44" t="n">
         <v>10</v>
@@ -9022,10 +9022,10 @@
         <v>16</v>
       </c>
       <c r="AS44" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU44" t="n">
         <v>6.4</v>
@@ -9034,7 +9034,7 @@
         <v>12.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AX44" t="n">
         <v>9.800000000000001</v>
@@ -9043,32 +9043,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB44" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BC44" t="n">
         <v>18.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE44" t="n">
         <v>28</v>
       </c>
       <c r="BF44" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -9099,31 +9099,31 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G45" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="H45" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="I45" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>1.35</v>
@@ -9135,28 +9135,28 @@
         <v>1.89</v>
       </c>
       <c r="R45" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V45" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="n">
         <v>1000</v>
@@ -9165,31 +9165,31 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC45" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE45" t="n">
         <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH45" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI45" t="n">
         <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK45" t="n">
         <v>1000</v>
@@ -9207,62 +9207,62 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -9359,10 +9359,10 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AC46" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD46" t="n">
         <v>85</v>
@@ -9374,7 +9374,7 @@
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9407,10 +9407,10 @@
         <v>8.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AT46" t="n">
         <v>3.85</v>
@@ -9419,44 +9419,44 @@
         <v>5.1</v>
       </c>
       <c r="AV46" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="BB46" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H47" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="K47" t="n">
-        <v>3.65</v>
+        <v>500</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9517,7 +9517,7 @@
         <v>1.48</v>
       </c>
       <c r="P47" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q47" t="n">
         <v>2.42</v>
@@ -9535,58 +9535,58 @@
         <v>1.7</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W47" t="n">
         <v>1.2</v>
       </c>
       <c r="X47" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
         <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -9684,13 +9684,13 @@
         <v>3.7</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J48" t="n">
         <v>2.82</v>
@@ -9699,7 +9699,7 @@
         <v>2.9</v>
       </c>
       <c r="L48" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M48" t="n">
         <v>1.17</v>
@@ -9708,13 +9708,13 @@
         <v>2.2</v>
       </c>
       <c r="O48" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P48" t="n">
         <v>1.39</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R48" t="n">
         <v>1.13</v>
@@ -9723,22 +9723,22 @@
         <v>7.2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U48" t="n">
         <v>1.61</v>
       </c>
       <c r="V48" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W48" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X48" t="n">
         <v>6.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z48" t="n">
         <v>1000</v>
@@ -9747,10 +9747,10 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD48" t="n">
         <v>1000</v>
@@ -9789,7 +9789,7 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ48" t="n">
         <v>5.8</v>
@@ -9798,53 +9798,53 @@
         <v>12</v>
       </c>
       <c r="AS48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT48" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU48" t="n">
         <v>6.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AW48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY48" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>5.8</v>
       </c>
       <c r="AZ48" t="n">
         <v>25</v>
       </c>
       <c r="BA48" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB48" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC48" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD48" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE48" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G49" t="n">
         <v>3.2</v>
@@ -9890,7 +9890,7 @@
         <v>2.6</v>
       </c>
       <c r="K49" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,25 +9899,25 @@
         <v>1.21</v>
       </c>
       <c r="N49" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O49" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="P49" t="n">
         <v>1.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R49" t="n">
         <v>1.1</v>
       </c>
       <c r="S49" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="T49" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U49" t="n">
         <v>1.44</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -10069,91 +10069,91 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H50" t="n">
         <v>2.56</v>
       </c>
       <c r="I50" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J50" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K50" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L50" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M50" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N50" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O50" t="n">
         <v>1.43</v>
       </c>
       <c r="P50" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R50" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T50" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U50" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V50" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W50" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
       </c>
       <c r="Y50" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
         <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
         <v>1000</v>
@@ -10177,62 +10177,62 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG50" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH50"/>
+  <dimension ref="A1:BH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,76 +757,76 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -835,13 +835,13 @@
         <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
@@ -856,37 +856,37 @@
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>15.5</v>
@@ -898,10 +898,10 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -913,14 +913,14 @@
         <v>60</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -975,16 +975,16 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -993,22 +993,22 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>70</v>
+        <v>17.5</v>
       </c>
       <c r="Z3" t="n">
         <v>110</v>
@@ -1020,7 +1020,7 @@
         <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
@@ -1053,22 +1053,22 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1077,44 +1077,44 @@
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N4" t="n">
         <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.55</v>
       </c>
-      <c r="V4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1238,7 +1238,7 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.48</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.45</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.48</v>
+        <v>2.48</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.48</v>
+        <v>2.52</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.48</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.48</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.2</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.06</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.06</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.06</v>
+        <v>5.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.06</v>
+        <v>5.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.06</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.06</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.06</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.84</v>
+        <v>3.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1548,10 +1548,10 @@
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1560,7 +1560,7 @@
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
         <v>1.79</v>
@@ -1581,7 +1581,7 @@
         <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W6" t="n">
         <v>2.38</v>
@@ -1650,7 +1650,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1662,7 +1662,7 @@
         <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>44</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>1000</v>
@@ -1850,7 +1850,7 @@
         <v>1.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AV7" t="n">
         <v>1.18</v>
@@ -1874,7 +1874,7 @@
         <v>1.16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BD7" t="n">
         <v>1.17</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>1.23</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>44</v>
@@ -1972,7 +1972,7 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2115,85 +2115,85 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
         <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="n">
         <v>55</v>
       </c>
       <c r="Z9" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>780</v>
+        <v>750</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="AD9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE9" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2202,52 +2202,52 @@
         <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>460</v>
+        <v>170</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="n">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AV9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
         <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
@@ -2268,17 +2268,17 @@
         <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BG9" t="n">
         <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>1.56</v>
       </c>
       <c r="H10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I10" t="n">
         <v>5.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>5.6</v>
@@ -2339,13 +2339,13 @@
         <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -2357,16 +2357,16 @@
         <v>2.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>2.78</v>
       </c>
       <c r="X10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z10" t="n">
         <v>50</v>
@@ -2378,7 +2378,7 @@
         <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2396,13 +2396,13 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>24</v>
@@ -2417,10 +2417,10 @@
         <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR10" t="n">
         <v>46</v>
@@ -2447,13 +2447,13 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
@@ -2468,11 +2468,11 @@
         <v>4.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G11" t="n">
         <v>1.84</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -2521,28 +2521,28 @@
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
         <v>1.72</v>
@@ -2572,7 +2572,7 @@
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
         <v>32</v>
@@ -2593,7 +2593,7 @@
         <v>250</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
         <v>18.5</v>
@@ -2620,7 +2620,7 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -2644,7 +2644,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2656,17 +2656,17 @@
         <v>14.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
         <v>8.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.99</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.8</v>
@@ -2909,7 +2909,7 @@
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2930,31 +2930,31 @@
         <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>2.42</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y13" t="n">
         <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AA13" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AB13" t="n">
         <v>7.2</v>
@@ -2966,7 +2966,7 @@
         <v>28</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
         <v>9.199999999999999</v>
@@ -2978,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AJ13" t="n">
         <v>17</v>
@@ -2990,13 +2990,13 @@
         <v>160</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN13" t="n">
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP13" t="n">
         <v>11.5</v>
@@ -3008,7 +3008,7 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
         <v>6.2</v>
@@ -3020,7 +3020,7 @@
         <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3029,19 +3029,19 @@
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>17</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BE13" t="n">
         <v>28</v>
@@ -3050,11 +3050,11 @@
         <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3279,52 +3279,52 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G15" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
         <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
         <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
         <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3420,7 +3420,7 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G16" t="n">
         <v>1.33</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>14</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
         <v>1.18</v>
@@ -3509,16 +3509,16 @@
         <v>1.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S16" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T16" t="n">
         <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
         <v>1.09</v>
@@ -3617,16 +3617,16 @@
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="BD16" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="BF16" t="n">
         <v>3.05</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>4.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -3697,10 +3697,10 @@
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="R17" t="n">
         <v>1.64</v>
@@ -3715,10 +3715,10 @@
         <v>2.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X17" t="n">
         <v>90</v>
@@ -3775,16 +3775,16 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AT17" t="n">
         <v>8.4</v>
@@ -3793,22 +3793,22 @@
         <v>1.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AX17" t="n">
         <v>7.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AZ17" t="n">
         <v>8.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BB17" t="n">
         <v>6.8</v>
@@ -3817,7 +3817,7 @@
         <v>8.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BE17" t="n">
         <v>16</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3861,34 +3861,34 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
@@ -3897,19 +3897,19 @@
         <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
         <v>2.3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4061,22 +4061,22 @@
         <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I19" t="n">
         <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
         <v>6.8</v>
@@ -4091,19 +4091,19 @@
         <v>1.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U19" t="n">
         <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
         <v>1.87</v>
@@ -4133,7 +4133,7 @@
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
         <v>16.5</v>
@@ -4148,10 +4148,10 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
@@ -4172,7 +4172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -4184,7 +4184,7 @@
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4196,7 +4196,7 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -4208,17 +4208,17 @@
         <v>11.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H20" t="n">
         <v>1.74</v>
@@ -4261,13 +4261,13 @@
         <v>1.78</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
         <v>3.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4282,13 +4282,13 @@
         <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
         <v>2.1</v>
@@ -4300,7 +4300,7 @@
         <v>2.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
         <v>13.5</v>
@@ -4309,10 +4309,10 @@
         <v>7.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
         <v>19.5</v>
@@ -4336,7 +4336,7 @@
         <v>55</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
         <v>700</v>
@@ -4354,7 +4354,7 @@
         <v>700</v>
       </c>
       <c r="AO20" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
@@ -4375,7 +4375,7 @@
         <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
         <v>17.5</v>
@@ -4390,29 +4390,29 @@
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC20" t="n">
         <v>11</v>
       </c>
-      <c r="BC20" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
         <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G21" t="n">
         <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I21" t="n">
         <v>2.72</v>
@@ -4458,7 +4458,7 @@
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4467,7 +4467,7 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.39</v>
@@ -4548,7 +4548,7 @@
         <v>42</v>
       </c>
       <c r="AO21" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
         <v>3.4</v>
@@ -4652,16 +4652,16 @@
         <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.44</v>
@@ -4670,16 +4670,16 @@
         <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
@@ -4691,7 +4691,7 @@
         <v>1.62</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
         <v>11.5</v>
@@ -4706,7 +4706,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
         <v>15</v>
@@ -4736,13 +4736,13 @@
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
         <v>29</v>
       </c>
       <c r="AO22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
@@ -4754,10 +4754,10 @@
         <v>19.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4775,32 +4775,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
         <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BG22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
         <v>3.1</v>
@@ -4855,19 +4855,19 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
         <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
         <v>3.6</v>
@@ -4882,7 +4882,7 @@
         <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
         <v>13</v>
@@ -4891,7 +4891,7 @@
         <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
         <v>55</v>
@@ -4912,7 +4912,7 @@
         <v>16</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>17.5</v>
@@ -4930,13 +4930,13 @@
         <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN23" t="n">
         <v>23</v>
       </c>
       <c r="AO23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP23" t="n">
         <v>12</v>
@@ -4972,19 +4972,19 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
         <v>32</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF23" t="n">
         <v>20</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J24" t="n">
         <v>6.2</v>
@@ -5043,13 +5043,13 @@
         <v>6.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.21</v>
@@ -5064,7 +5064,7 @@
         <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
         <v>2.18</v>
@@ -5151,7 +5151,7 @@
         <v>12.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AW24" t="n">
         <v>19.5</v>
@@ -5175,20 +5175,20 @@
         <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
         <v>18</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G25" t="n">
         <v>1.35</v>
       </c>
       <c r="H25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
         <v>12</v>
@@ -5237,40 +5237,40 @@
         <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R25" t="n">
         <v>1.56</v>
       </c>
       <c r="S25" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T25" t="n">
         <v>1.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V25" t="n">
         <v>1.09</v>
       </c>
       <c r="W25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X25" t="n">
         <v>42</v>
@@ -5309,13 +5309,13 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
         <v>970</v>
       </c>
       <c r="AL25" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5413,73 +5413,73 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
         <v>2.3</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P26" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
         <v>1.76</v>
       </c>
       <c r="X26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y26" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>14</v>
       </c>
       <c r="Z26" t="n">
         <v>27</v>
       </c>
       <c r="AA26" t="n">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>8.199999999999999</v>
@@ -5488,10 +5488,10 @@
         <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
@@ -5500,7 +5500,7 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
         <v>30</v>
@@ -5509,13 +5509,13 @@
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
         <v>60</v>
@@ -5524,13 +5524,13 @@
         <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT26" t="n">
         <v>7.8</v>
@@ -5539,10 +5539,10 @@
         <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5554,7 +5554,7 @@
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
@@ -5563,20 +5563,20 @@
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5607,55 +5607,55 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G27" t="n">
         <v>2.94</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I27" t="n">
         <v>2.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.27</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
         <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W27" t="n">
         <v>1.51</v>
@@ -5721,10 +5721,10 @@
         <v>6.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5748,10 +5748,10 @@
         <v>9</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC27" t="n">
         <v>8</v>
@@ -5766,11 +5766,11 @@
         <v>4</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
-        <v>2.78</v>
+        <v>2.16</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="I28" t="n">
-        <v>2.72</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.64</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="U28" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="V28" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="X28" t="n">
-        <v>70</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>11</v>
       </c>
-      <c r="AD28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G29" t="n">
         <v>4.1</v>
@@ -6004,7 +6004,7 @@
         <v>2.02</v>
       </c>
       <c r="I29" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J29" t="n">
         <v>3.65</v>
@@ -6013,28 +6013,28 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>2.18</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>1.7</v>
@@ -6103,7 +6103,7 @@
         <v>85</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="AQ29" t="n">
         <v>5.8</v>
@@ -6112,10 +6112,10 @@
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.54</v>
+        <v>1.9</v>
       </c>
       <c r="AU29" t="n">
         <v>4.9</v>
@@ -6124,31 +6124,31 @@
         <v>5.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="AX29" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.68</v>
+        <v>1.97</v>
       </c>
       <c r="BB29" t="n">
         <v>2.02</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BF29" t="n">
         <v>5.8</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.78</v>
       </c>
       <c r="H30" t="n">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.69</v>
       </c>
       <c r="S30" t="n">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="T30" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="X30" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG30" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AH30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN30" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AO30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU30" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ30" t="n">
+      <c r="AV30" t="n">
         <v>11</v>
       </c>
-      <c r="AR30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA30" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB30" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6383,46 +6383,46 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G31" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H31" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -6431,19 +6431,19 @@
         <v>1.94</v>
       </c>
       <c r="V31" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W31" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X31" t="n">
         <v>26</v>
       </c>
       <c r="Y31" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6452,7 +6452,7 @@
         <v>20</v>
       </c>
       <c r="AC31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD31" t="n">
         <v>18.5</v>
@@ -6464,7 +6464,7 @@
         <v>970</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AH31" t="n">
         <v>29</v>
@@ -6473,7 +6473,7 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
         <v>85</v>
@@ -6497,10 +6497,10 @@
         <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6512,10 +6512,10 @@
         <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6524,29 +6524,29 @@
         <v>9</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF31" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>19</v>
       </c>
       <c r="BG31" t="n">
         <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -6589,10 +6589,10 @@
         <v>6.2</v>
       </c>
       <c r="J32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K32" t="n">
         <v>5.9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6</v>
       </c>
       <c r="L32" t="n">
         <v>1.25</v>
@@ -6601,7 +6601,7 @@
         <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.14</v>
@@ -6610,40 +6610,40 @@
         <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R32" t="n">
         <v>1.86</v>
       </c>
       <c r="S32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U32" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V32" t="n">
         <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z32" t="n">
         <v>55</v>
       </c>
       <c r="AA32" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC32" t="n">
         <v>14</v>
@@ -6661,7 +6661,7 @@
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
         <v>55</v>
@@ -6673,13 +6673,13 @@
         <v>13</v>
       </c>
       <c r="AL32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM32" t="n">
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO32" t="n">
         <v>55</v>
@@ -6688,19 +6688,19 @@
         <v>32</v>
       </c>
       <c r="AQ32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR32" t="n">
         <v>48</v>
       </c>
       <c r="AS32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AT32" t="n">
         <v>14.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV32" t="n">
         <v>22</v>
@@ -6712,7 +6712,7 @@
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
         <v>20</v>
@@ -6727,20 +6727,20 @@
         <v>12</v>
       </c>
       <c r="BD32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE32" t="n">
         <v>65</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
         <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q33" t="n">
         <v>1.66</v>
@@ -6813,7 +6813,7 @@
         <v>2.66</v>
       </c>
       <c r="T33" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
         <v>1.8</v>
@@ -6828,7 +6828,7 @@
         <v>24</v>
       </c>
       <c r="Y33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z33" t="n">
         <v>120</v>
@@ -6843,10 +6843,10 @@
         <v>14.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE33" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AF33" t="n">
         <v>7.6</v>
@@ -6870,16 +6870,16 @@
         <v>40</v>
       </c>
       <c r="AM33" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="n">
         <v>4.7</v>
       </c>
       <c r="AO33" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="AP33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ33" t="n">
         <v>32</v>
@@ -6897,13 +6897,13 @@
         <v>13.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AW33" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -6912,7 +6912,7 @@
         <v>30</v>
       </c>
       <c r="BA33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BB33" t="n">
         <v>9.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>3.1</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J34" t="n">
         <v>4.5</v>
@@ -6995,7 +6995,7 @@
         <v>1.14</v>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q34" t="n">
         <v>1.43</v>
@@ -7079,10 +7079,10 @@
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT34" t="n">
         <v>18</v>
@@ -7100,7 +7100,7 @@
         <v>18.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ34" t="n">
         <v>13.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>1.02</v>
@@ -7386,10 +7386,10 @@
         <v>1.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S36" t="n">
         <v>2.78</v>
@@ -7497,13 +7497,13 @@
         <v>4.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BE36" t="n">
         <v>1.69</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.66</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
@@ -7571,7 +7571,7 @@
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>1.55</v>
@@ -7610,7 +7610,7 @@
         <v>21</v>
       </c>
       <c r="AA37" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB37" t="n">
         <v>8.6</v>
@@ -7622,7 +7622,7 @@
         <v>15.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="n">
         <v>18.5</v>
@@ -7655,7 +7655,7 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ37" t="n">
         <v>4.4</v>
@@ -7664,7 +7664,7 @@
         <v>7</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37" t="n">
         <v>5.1</v>
@@ -7673,19 +7673,19 @@
         <v>4.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AW37" t="n">
         <v>7.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY37" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA37" t="n">
         <v>7.8</v>
@@ -7697,20 +7697,20 @@
         <v>7.2</v>
       </c>
       <c r="BD37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF37" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG37" t="n">
         <v>7.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G38" t="n">
         <v>2.04</v>
@@ -7756,7 +7756,7 @@
         <v>3.25</v>
       </c>
       <c r="K38" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L38" t="n">
         <v>1.44</v>
@@ -7780,7 +7780,7 @@
         <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T38" t="n">
         <v>2.06</v>
@@ -7789,7 +7789,7 @@
         <v>1.86</v>
       </c>
       <c r="V38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
         <v>1.96</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G39" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>2.04</v>
       </c>
       <c r="I39" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="J39" t="n">
         <v>3.2</v>
@@ -7953,22 +7953,22 @@
         <v>3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="M39" t="n">
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P39" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
         <v>1.21</v>
@@ -7983,7 +7983,7 @@
         <v>1.78</v>
       </c>
       <c r="V39" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W39" t="n">
         <v>1.27</v>
@@ -7992,31 +7992,31 @@
         <v>10</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB39" t="n">
         <v>13</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>12.5</v>
       </c>
       <c r="AC39" t="n">
         <v>7.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
@@ -8025,7 +8025,7 @@
         <v>60</v>
       </c>
       <c r="AJ39" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AK39" t="n">
         <v>160</v>
@@ -8040,7 +8040,7 @@
         <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP39" t="n">
         <v>8.199999999999999</v>
@@ -8058,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV39" t="n">
         <v>9.4</v>
@@ -8076,29 +8076,29 @@
         <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB39" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF39" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G40" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H40" t="n">
         <v>5.7</v>
@@ -8147,7 +8147,7 @@
         <v>3.65</v>
       </c>
       <c r="L40" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
@@ -8159,13 +8159,13 @@
         <v>1.36</v>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
         <v>3.8</v>
@@ -8177,10 +8177,10 @@
         <v>1.89</v>
       </c>
       <c r="V40" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W40" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
@@ -8189,7 +8189,7 @@
         <v>970</v>
       </c>
       <c r="Z40" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA40" t="n">
         <v>900</v>
@@ -8216,7 +8216,7 @@
         <v>60</v>
       </c>
       <c r="AI40" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ40" t="n">
         <v>900</v>
@@ -8258,7 +8258,7 @@
         <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX40" t="n">
         <v>8.800000000000001</v>
@@ -8279,7 +8279,7 @@
         <v>10.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE40" t="n">
         <v>10</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="n">
         <v>3.45</v>
@@ -8338,7 +8338,7 @@
         <v>2.98</v>
       </c>
       <c r="K41" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
         <v>1.48</v>
@@ -8347,10 +8347,10 @@
         <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O41" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P41" t="n">
         <v>1.5</v>
@@ -8368,7 +8368,7 @@
         <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V41" t="n">
         <v>1.58</v>
@@ -8380,10 +8380,10 @@
         <v>11</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
         <v>55</v>
@@ -8422,7 +8422,7 @@
         <v>1000</v>
       </c>
       <c r="AM41" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN41" t="n">
         <v>1000</v>
@@ -8431,7 +8431,7 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ41" t="n">
         <v>7.2</v>
@@ -8440,7 +8440,7 @@
         <v>13.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT41" t="n">
         <v>8.4</v>
@@ -8452,7 +8452,7 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX41" t="n">
         <v>17.5</v>
@@ -8461,32 +8461,32 @@
         <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG41" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB41" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -8523,13 +8523,13 @@
         <v>1.79</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K42" t="n">
         <v>3.65</v>
@@ -8550,7 +8550,7 @@
         <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R42" t="n">
         <v>1.21</v>
@@ -8583,7 +8583,7 @@
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC42" t="n">
         <v>8.199999999999999</v>
@@ -8601,7 +8601,7 @@
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AI42" t="n">
         <v>700</v>
@@ -8631,19 +8631,19 @@
         <v>13.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AS42" t="n">
         <v>46</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU42" t="n">
         <v>7.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AW42" t="n">
         <v>40</v>
@@ -8655,7 +8655,7 @@
         <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA42" t="n">
         <v>44</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -8711,58 +8711,58 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="G43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N43" t="n">
         <v>3</v>
       </c>
-      <c r="H43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="K43" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.38</v>
-      </c>
       <c r="O43" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P43" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T43" t="n">
         <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8819,52 +8819,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AU43" t="n">
         <v>1.14</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF43" t="n">
         <v>1.55</v>
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F44" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.88</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.96</v>
-      </c>
       <c r="H44" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J44" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K44" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P44" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T44" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="U44" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X44" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AE44" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG44" t="n">
         <v>12</v>
       </c>
-      <c r="AG44" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH44" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AI44" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.199999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="AQ44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR44" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AS44" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT44" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY44" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14</v>
+        <v>2.32</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>18.5</v>
+        <v>2.56</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.6</v>
+        <v>2.42</v>
       </c>
       <c r="BE44" t="n">
-        <v>28</v>
+        <v>2.56</v>
       </c>
       <c r="BF44" t="n">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9090,186 +9090,186 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G45" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H45" t="n">
+        <v>6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR45" t="n">
         <v>4.9</v>
       </c>
-      <c r="I45" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>26</v>
-      </c>
       <c r="AS45" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AT45" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AU45" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AX45" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.96</v>
+        <v>4.2</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="BA45" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="BB45" t="n">
-        <v>15.5</v>
+        <v>2.7</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="BE45" t="n">
         <v>2.34</v>
       </c>
       <c r="BF45" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,72 +9279,72 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.75</v>
+        <v>3.65</v>
       </c>
       <c r="G46" t="n">
-        <v>1.84</v>
+        <v>6.6</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="K46" t="n">
-        <v>3.5</v>
+        <v>500</v>
       </c>
       <c r="L46" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="O46" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P46" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S46" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U46" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V46" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="W46" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9359,13 +9359,13 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
@@ -9374,7 +9374,7 @@
         <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9395,75 +9395,75 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,78 +9473,78 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>3.7</v>
       </c>
       <c r="G47" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="J47" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="K47" t="n">
-        <v>500</v>
+        <v>2.9</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="M47" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="P47" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T47" t="n">
         <v>2.42</v>
       </c>
-      <c r="R47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U47" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="V47" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="W47" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -9553,10 +9553,10 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -9574,7 +9574,7 @@
         <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ47" t="n">
         <v>1000</v>
@@ -9583,10 +9583,10 @@
         <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -9672,103 +9672,103 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="H48" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="I48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J48" t="n">
         <v>2.62</v>
       </c>
-      <c r="J48" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K48" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="L48" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="N48" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="P48" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="R48" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="S48" t="n">
-        <v>7.2</v>
+        <v>1.05</v>
       </c>
       <c r="T48" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="U48" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="W48" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="X48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB48" t="n">
         <v>6.8</v>
       </c>
-      <c r="Y48" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>9</v>
-      </c>
       <c r="AC48" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH48" t="n">
         <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
         <v>1000</v>
@@ -9777,10 +9777,10 @@
         <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
         <v>1000</v>
@@ -9789,69 +9789,69 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ48" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT48" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="AU48" t="n">
         <v>6.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AW48" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AX48" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AY48" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="AZ48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA48" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BB48" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BC48" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BD48" t="n">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF48" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BG48" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9861,378 +9861,184 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>3.2</v>
       </c>
       <c r="H49" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="I49" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K49" t="n">
         <v>3.45</v>
       </c>
-      <c r="J49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K49" t="n">
-        <v>2.74</v>
-      </c>
       <c r="L49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP49" t="n">
         <v>1.01</v>
       </c>
-      <c r="M49" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X49" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AQ49" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Millonarios</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medellin</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>3</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH50" t="inlineStr">
-        <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -769,10 +769,10 @@
         <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.35</v>
@@ -790,25 +790,25 @@
         <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -820,13 +820,13 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -835,7 +835,7 @@
         <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -844,25 +844,25 @@
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>32</v>
       </c>
       <c r="AK2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
         <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP2" t="n">
         <v>19</v>
@@ -871,25 +871,25 @@
         <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -901,7 +901,7 @@
         <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -951,40 +951,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P3" t="n">
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -993,34 +993,34 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>17.5</v>
+        <v>60</v>
       </c>
       <c r="Z3" t="n">
         <v>110</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
@@ -1035,16 +1035,16 @@
         <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI3" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>250</v>
@@ -1059,62 +1059,62 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.62</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1238,7 +1238,7 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.12</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.48</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
         <v>1.75</v>
@@ -1384,7 +1384,7 @@
         <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.2</v>
@@ -1417,7 +1417,7 @@
         <v>150</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1447,62 +1447,62 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BA5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5.8</v>
       </c>
-      <c r="AW5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ5" t="n">
+      <c r="BC5" t="n">
         <v>5.7</v>
       </c>
-      <c r="BA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7</v>
       </c>
-      <c r="BF5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="G6" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>1.45</v>
@@ -1557,85 +1557,85 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
         <v>700</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>700</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,59 +1644,59 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8</v>
-      </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE6" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>28</v>
-      </c>
       <c r="BF6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="G7" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>1.27</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.13</v>
+        <v>1.97</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.18</v>
+        <v>2.04</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.16</v>
+        <v>1.81</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.16</v>
+        <v>1.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.18</v>
+        <v>1.79</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>5.3</v>
       </c>
-      <c r="I8" t="n">
-        <v>44</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>44</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,92 +1999,92 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.06</v>
+        <v>3.95</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.06</v>
+        <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.06</v>
+        <v>3.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.06</v>
+        <v>3.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.06</v>
+        <v>4.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.06</v>
+        <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.06</v>
+        <v>3.95</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.06</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J9" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2139,7 +2139,7 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.17</v>
@@ -2154,131 +2154,131 @@
         <v>1.71</v>
       </c>
       <c r="S9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="Z9" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
-        <v>750</v>
+        <v>470</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>38</v>
+        <v>15.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AE9" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>170</v>
+        <v>460</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
         <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BG9" t="n">
         <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>1.23</v>
@@ -2333,146 +2333,146 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
         <v>1.58</v>
       </c>
       <c r="U10" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB10" t="n">
         <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK10" t="n">
         <v>13</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AQ10" t="n">
         <v>32</v>
       </c>
       <c r="AR10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -2536,34 +2536,34 @@
         <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
         <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
         <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X11" t="n">
         <v>38</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>700</v>
@@ -2578,7 +2578,7 @@
         <v>32</v>
       </c>
       <c r="AE11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2590,13 +2590,13 @@
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>75</v>
@@ -2605,16 +2605,16 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2626,13 +2626,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -2641,32 +2641,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB11" t="n">
         <v>11</v>
       </c>
-      <c r="BB11" t="n">
-        <v>17</v>
-      </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11" t="n">
         <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.18</v>
@@ -2712,7 +2712,7 @@
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -2721,146 +2721,146 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2897,46 +2897,46 @@
         <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
@@ -2945,10 +2945,10 @@
         <v>2.42</v>
       </c>
       <c r="X13" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
         <v>60</v>
@@ -2957,10 +2957,10 @@
         <v>700</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>28</v>
@@ -2969,13 +2969,13 @@
         <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
         <v>700</v>
@@ -2993,13 +2993,13 @@
         <v>700</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>16</v>
@@ -3008,10 +3008,10 @@
         <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>7.6</v>
@@ -3020,7 +3020,7 @@
         <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -3032,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3041,20 +3041,20 @@
         <v>17</v>
       </c>
       <c r="BD13" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3085,61 +3085,61 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.05</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>2.42</v>
       </c>
       <c r="H14" t="n">
-        <v>1.05</v>
+        <v>2.96</v>
       </c>
       <c r="I14" t="n">
-        <v>990</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>2.76</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
         <v>2.66</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
         <v>1.45</v>
@@ -3303,28 +3303,28 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3339,7 +3339,7 @@
         <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
         <v>130</v>
@@ -3351,10 +3351,10 @@
         <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
         <v>20</v>
@@ -3372,7 +3372,7 @@
         <v>230</v>
       </c>
       <c r="AK15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL15" t="n">
         <v>250</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
         <v>48</v>
@@ -3396,7 +3396,7 @@
         <v>15.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AT15" t="n">
         <v>9.199999999999999</v>
@@ -3408,7 +3408,7 @@
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
         <v>16</v>
@@ -3420,29 +3420,29 @@
         <v>14.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S16" t="n">
         <v>2.02</v>
       </c>
       <c r="T16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
         <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV16" t="n">
         <v>29</v>
       </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.76</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.79</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.88</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.93</v>
+        <v>20</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
         <v>1.87</v>
@@ -3679,40 +3679,40 @@
         <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="T17" t="n">
         <v>1.54</v>
       </c>
       <c r="U17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V17" t="n">
         <v>1.28</v>
@@ -3721,22 +3721,22 @@
         <v>2.14</v>
       </c>
       <c r="X17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
         <v>470</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
         <v>110</v>
@@ -3745,92 +3745,92 @@
         <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>110</v>
       </c>
       <c r="AJ17" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>85</v>
+        <v>7.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.45</v>
+        <v>26</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.45</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.46</v>
+        <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.46</v>
+        <v>15.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.46</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.43</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.46</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.43</v>
+        <v>11.5</v>
       </c>
       <c r="BE17" t="n">
         <v>16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
         <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>95</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.71</v>
+        <v>6.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.25</v>
+        <v>18.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.78</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
         <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.6</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.71</v>
+        <v>7.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.15</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.73</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.74</v>
+        <v>22</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.65</v>
+        <v>24</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.57</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -4085,25 +4085,25 @@
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
         <v>1.81</v>
       </c>
       <c r="S19" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T19" t="n">
         <v>1.44</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V19" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
         <v>1.87</v>
@@ -4115,22 +4115,22 @@
         <v>65</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA19" t="n">
         <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
         <v>970</v>
@@ -4145,49 +4145,49 @@
         <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AL19" t="n">
         <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BF19" t="n">
         <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4249,37 +4249,37 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
         <v>2.24</v>
@@ -4291,128 +4291,128 @@
         <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>16.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
         <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG20" t="n">
         <v>42</v>
       </c>
       <c r="AH20" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
         <v>160</v>
       </c>
       <c r="AJ20" t="n">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="AK20" t="n">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AL20" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AM20" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG20" t="n">
         <v>12</v>
       </c>
-      <c r="BC20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4443,127 +4443,127 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.25</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W21" t="n">
         <v>1.47</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
         <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK21" t="n">
         <v>36</v>
       </c>
-      <c r="AF21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>44</v>
-      </c>
       <c r="AL21" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO21" t="n">
         <v>500</v>
       </c>
       <c r="AP21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT21" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -4575,38 +4575,38 @@
         <v>28</v>
       </c>
       <c r="AX21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
         <v>38</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BF21" t="n">
         <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.15</v>
       </c>
       <c r="L22" t="n">
         <v>1.5</v>
@@ -4685,16 +4685,16 @@
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
         <v>10</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
         <v>23</v>
@@ -4739,10 +4739,10 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
@@ -4784,13 +4784,13 @@
         <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
         <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF22" t="n">
         <v>26</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G23" t="n">
         <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
         <v>3.25</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>3.45</v>
@@ -4852,28 +4852,28 @@
         <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
         <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U23" t="n">
         <v>2.2</v>
@@ -4927,13 +4927,13 @@
         <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
         <v>34</v>
@@ -4951,7 +4951,7 @@
         <v>46</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU23" t="n">
         <v>7</v>
@@ -4972,29 +4972,29 @@
         <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
         <v>32</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -5040,7 +5040,7 @@
         <v>6.2</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.31</v>
@@ -5049,19 +5049,19 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
         <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
         <v>2.64</v>
@@ -5073,16 +5073,16 @@
         <v>1.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
         <v>40</v>
       </c>
       <c r="Y24" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="n">
         <v>130</v>
@@ -5091,7 +5091,7 @@
         <v>640</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
         <v>14</v>
@@ -5100,10 +5100,10 @@
         <v>46</v>
       </c>
       <c r="AE24" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
@@ -5112,25 +5112,25 @@
         <v>34</v>
       </c>
       <c r="AI24" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
@@ -5139,22 +5139,22 @@
         <v>32</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
         <v>12.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW24" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX24" t="n">
         <v>7.2</v>
@@ -5163,13 +5163,13 @@
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC24" t="n">
         <v>13</v>
@@ -5178,17 +5178,17 @@
         <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG24" t="n">
         <v>18</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.34</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="H25" t="n">
         <v>10</v>
@@ -5231,7 +5231,7 @@
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
         <v>6.2</v>
@@ -5243,28 +5243,28 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S25" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T25" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
         <v>1.09</v>
@@ -5273,116 +5273,116 @@
         <v>3.55</v>
       </c>
       <c r="X25" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Y25" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>29</v>
+        <v>5.3</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.6</v>
+        <v>20</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.57</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.61</v>
+        <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.66</v>
+        <v>9.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.63</v>
+        <v>18</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.66</v>
+        <v>4.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.44</v>
@@ -5440,55 +5440,55 @@
         <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q26" t="n">
         <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y26" t="n">
         <v>13</v>
       </c>
-      <c r="Y26" t="n">
-        <v>13.5</v>
-      </c>
       <c r="Z26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF26" t="n">
         <v>14.5</v>
@@ -5500,40 +5500,40 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AJ26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
         <v>26</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
@@ -5542,19 +5542,19 @@
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB26" t="n">
         <v>10.5</v>
@@ -5563,20 +5563,20 @@
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>2.68</v>
       </c>
       <c r="G27" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H27" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I27" t="n">
         <v>2.8</v>
@@ -5622,7 +5622,7 @@
         <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -5634,31 +5634,31 @@
         <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
         <v>1.81</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
         <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
         <v>1.56</v>
       </c>
       <c r="W27" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X27" t="n">
         <v>90</v>
@@ -5697,7 +5697,7 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
@@ -5709,37 +5709,37 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO27" t="n">
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV27" t="n">
         <v>6.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
         <v>7</v>
@@ -5748,29 +5748,29 @@
         <v>9</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC27" t="n">
         <v>8</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>4</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5801,25 +5801,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
         <v>2.16</v>
       </c>
       <c r="H28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
         <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5834,13 +5834,13 @@
         <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
         <v>1.91</v>
@@ -5867,10 +5867,10 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>18</v>
@@ -5891,7 +5891,7 @@
         <v>170</v>
       </c>
       <c r="AJ28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK28" t="n">
         <v>26</v>
@@ -5918,7 +5918,7 @@
         <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -5930,7 +5930,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -5942,29 +5942,29 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="BB28" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
         <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G29" t="n">
         <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J29" t="n">
         <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>1.36</v>
@@ -6022,55 +6022,55 @@
         <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
         <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R29" t="n">
         <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
         <v>1.7</v>
       </c>
       <c r="U29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W29" t="n">
         <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AA29" t="n">
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="AC29" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AD29" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
         <v>90</v>
@@ -6079,7 +6079,7 @@
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
         <v>160</v>
@@ -6100,65 +6100,65 @@
         <v>250</v>
       </c>
       <c r="AO29" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR29" t="n">
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.98</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.99</v>
+        <v>9</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.88</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.97</v>
+        <v>9.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="BE29" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.72</v>
+        <v>6.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6189,28 +6189,28 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G30" t="n">
         <v>2.78</v>
       </c>
       <c r="H30" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I30" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J30" t="n">
         <v>3.85</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L30" t="n">
         <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
         <v>6</v>
@@ -6219,22 +6219,22 @@
         <v>1.16</v>
       </c>
       <c r="P30" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S30" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.47</v>
       </c>
       <c r="U30" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V30" t="n">
         <v>1.58</v>
@@ -6264,10 +6264,10 @@
         <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG30" t="n">
         <v>13.5</v>
@@ -6276,7 +6276,7 @@
         <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="n">
         <v>40</v>
@@ -6288,16 +6288,16 @@
         <v>60</v>
       </c>
       <c r="AM30" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AN30" t="n">
         <v>13.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>15.5</v>
@@ -6342,7 +6342,7 @@
         <v>14.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF30" t="n">
         <v>11</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6383,55 +6383,55 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="G31" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="H31" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.98</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.52</v>
@@ -6440,7 +6440,7 @@
         <v>26</v>
       </c>
       <c r="Y31" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z31" t="n">
         <v>970</v>
@@ -6455,16 +6455,16 @@
         <v>14</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF31" t="n">
         <v>970</v>
       </c>
       <c r="AG31" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AH31" t="n">
         <v>29</v>
@@ -6473,13 +6473,13 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6497,10 +6497,10 @@
         <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6512,10 +6512,10 @@
         <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6524,19 +6524,19 @@
         <v>9</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF31" t="n">
         <v>5.4</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="G32" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>5.8</v>
       </c>
       <c r="K32" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
         <v>1.25</v>
@@ -6610,25 +6610,25 @@
         <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R32" t="n">
         <v>1.86</v>
       </c>
       <c r="S32" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T32" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U32" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X32" t="n">
         <v>36</v>
@@ -6640,13 +6640,13 @@
         <v>55</v>
       </c>
       <c r="AA32" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD32" t="n">
         <v>23</v>
@@ -6661,13 +6661,13 @@
         <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK32" t="n">
         <v>13</v>
@@ -6679,22 +6679,22 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO32" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP32" t="n">
         <v>32</v>
       </c>
       <c r="AQ32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS32" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AT32" t="n">
         <v>14.5</v>
@@ -6706,10 +6706,10 @@
         <v>22</v>
       </c>
       <c r="AW32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY32" t="n">
         <v>10.5</v>
@@ -6718,29 +6718,29 @@
         <v>20</v>
       </c>
       <c r="BA32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB32" t="n">
         <v>13</v>
       </c>
       <c r="BC32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD32" t="n">
         <v>26</v>
       </c>
       <c r="BE32" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6789,34 +6789,34 @@
         <v>6.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="S33" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="V33" t="n">
         <v>1.08</v>
@@ -6825,73 +6825,73 @@
         <v>4.2</v>
       </c>
       <c r="X33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y33" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z33" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD33" t="n">
         <v>44</v>
       </c>
       <c r="AE33" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AF33" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AG33" t="n">
         <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI33" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM33" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AO33" t="n">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="AP33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ33" t="n">
         <v>32</v>
       </c>
       <c r="AR33" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AS33" t="n">
         <v>130</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU33" t="n">
         <v>13.5</v>
@@ -6900,41 +6900,41 @@
         <v>42</v>
       </c>
       <c r="AW33" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BA33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BB33" t="n">
         <v>9.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE33" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG33" t="n">
-        <v>55</v>
+        <v>260</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6965,85 +6965,85 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K34" t="n">
         <v>4.5</v>
       </c>
-      <c r="K34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M34" t="n">
         <v>1.03</v>
       </c>
       <c r="N34" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P34" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="R34" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="S34" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="U34" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X34" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA34" t="n">
         <v>50</v>
       </c>
       <c r="AB34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD34" t="n">
         <v>14.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF34" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG34" t="n">
         <v>11.5</v>
@@ -7052,83 +7052,83 @@
         <v>14.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK34" t="n">
         <v>18</v>
       </c>
       <c r="AL34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AP34" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AQ34" t="n">
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS34" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT34" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV34" t="n">
         <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX34" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY34" t="n">
         <v>11</v>
       </c>
       <c r="AZ34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA34" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE34" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG34" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7159,46 +7159,46 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K35" t="n">
         <v>4.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M35" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N35" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P35" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
       </c>
       <c r="S35" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T35" t="n">
         <v>2.72</v>
@@ -7207,10 +7207,10 @@
         <v>1.47</v>
       </c>
       <c r="V35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
@@ -7237,7 +7237,7 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AG35" t="n">
         <v>28</v>
@@ -7273,31 +7273,31 @@
         <v>9.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS35" t="n">
         <v>4.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU35" t="n">
         <v>5.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AW35" t="n">
         <v>4.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AY35" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA35" t="n">
         <v>4.2</v>
@@ -7306,13 +7306,13 @@
         <v>6.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF35" t="n">
         <v>11</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7353,64 +7353,64 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="G36" t="n">
         <v>1.35</v>
       </c>
       <c r="H36" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="S36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.78</v>
       </c>
-      <c r="T36" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W36" t="n">
         <v>3.85</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,104 +7419,104 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>900</v>
+        <v>10.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.69</v>
+        <v>11</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.42</v>
+        <v>4.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.69</v>
+        <v>11</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.59</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.69</v>
+        <v>7.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.52</v>
+        <v>8.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.65</v>
+        <v>16</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.68</v>
+        <v>7.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.69</v>
+        <v>8.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
         <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="T37" t="n">
         <v>2.08</v>
@@ -7697,7 +7697,7 @@
         <v>7.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE37" t="n">
         <v>8.4</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G38" t="n">
         <v>2.04</v>
@@ -7753,37 +7753,37 @@
         <v>5.2</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O38" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S38" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U38" t="n">
         <v>1.86</v>
@@ -7795,7 +7795,7 @@
         <v>1.96</v>
       </c>
       <c r="X38" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y38" t="n">
         <v>48</v>
@@ -7807,10 +7807,10 @@
         <v>700</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD38" t="n">
         <v>100</v>
@@ -7822,10 +7822,10 @@
         <v>11.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AH38" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI38" t="n">
         <v>700</v>
@@ -7858,7 +7858,7 @@
         <v>14.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>12</v>
+        <v>3.3</v>
       </c>
       <c r="AT38" t="n">
         <v>6.4</v>
@@ -7870,10 +7870,10 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX38" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY38" t="n">
         <v>6.2</v>
@@ -7882,7 +7882,7 @@
         <v>14.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7891,20 +7891,20 @@
         <v>11.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE38" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H39" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="J39" t="n">
         <v>3.2</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.54</v>
@@ -7959,37 +7959,37 @@
         <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P39" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T39" t="n">
         <v>2.06</v>
       </c>
       <c r="U39" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V39" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="W39" t="n">
         <v>1.27</v>
       </c>
       <c r="X39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y39" t="n">
         <v>7.4</v>
@@ -8004,10 +8004,10 @@
         <v>13</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE39" t="n">
         <v>29</v>
@@ -8016,22 +8016,22 @@
         <v>34</v>
       </c>
       <c r="AG39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH39" t="n">
         <v>24</v>
       </c>
       <c r="AI39" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ39" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL39" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -8043,19 +8043,19 @@
         <v>25</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT39" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>10</v>
       </c>
       <c r="AU39" t="n">
         <v>6.6</v>
@@ -8064,41 +8064,41 @@
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ39" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB39" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB39" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC39" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF39" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BG39" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G40" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H40" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I40" t="n">
         <v>6.6</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>1.45</v>
@@ -8153,13 +8153,13 @@
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>1.36</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q40" t="n">
         <v>2.1</v>
@@ -8171,22 +8171,22 @@
         <v>3.8</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U40" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="Z40" t="n">
         <v>500</v>
@@ -8195,10 +8195,10 @@
         <v>900</v>
       </c>
       <c r="AB40" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD40" t="n">
         <v>120</v>
@@ -8207,7 +8207,7 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AG40" t="n">
         <v>17.5</v>
@@ -8219,10 +8219,10 @@
         <v>700</v>
       </c>
       <c r="AJ40" t="n">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AK40" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AL40" t="n">
         <v>1000</v>
@@ -8231,68 +8231,68 @@
         <v>580</v>
       </c>
       <c r="AN40" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS40" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT40" t="n">
         <v>6.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY40" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE40" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA40" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>10</v>
-      </c>
       <c r="BF40" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G41" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="H41" t="n">
         <v>2.52</v>
@@ -8338,13 +8338,13 @@
         <v>2.98</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="L41" t="n">
         <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N41" t="n">
         <v>2.68</v>
@@ -8353,16 +8353,16 @@
         <v>1.5</v>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S41" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T41" t="n">
         <v>2.02</v>
@@ -8374,19 +8374,19 @@
         <v>1.58</v>
       </c>
       <c r="W41" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB41" t="n">
         <v>11</v>
@@ -8431,7 +8431,7 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ41" t="n">
         <v>7.2</v>
@@ -8440,7 +8440,7 @@
         <v>13.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
         <v>8.4</v>
@@ -8452,7 +8452,7 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX41" t="n">
         <v>17.5</v>
@@ -8464,29 +8464,29 @@
         <v>18.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB41" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC41" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD41" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -8517,34 +8517,34 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G42" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
         <v>6.2</v>
       </c>
-      <c r="I42" t="n">
-        <v>6.8</v>
-      </c>
       <c r="J42" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K42" t="n">
         <v>3.65</v>
       </c>
       <c r="L42" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
         <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O42" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P42" t="n">
         <v>1.59</v>
@@ -8556,7 +8556,7 @@
         <v>1.21</v>
       </c>
       <c r="S42" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T42" t="n">
         <v>2.36</v>
@@ -8565,19 +8565,19 @@
         <v>1.69</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X42" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA42" t="n">
         <v>900</v>
@@ -8589,7 +8589,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AE42" t="n">
         <v>700</v>
@@ -8601,13 +8601,13 @@
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AI42" t="n">
         <v>700</v>
       </c>
       <c r="AJ42" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK42" t="n">
         <v>25</v>
@@ -8643,28 +8643,28 @@
         <v>7.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW42" t="n">
         <v>40</v>
       </c>
       <c r="AX42" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY42" t="n">
         <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA42" t="n">
         <v>44</v>
       </c>
       <c r="BB42" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD42" t="n">
         <v>46</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -8711,170 +8711,170 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="G43" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="H43" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="I43" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P43" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R43" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS43" t="n">
         <v>4.4</v>
       </c>
-      <c r="T43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AT43" t="n">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.14</v>
+        <v>6.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.16</v>
+        <v>16</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.17</v>
+        <v>4.3</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.17</v>
+        <v>14</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.17</v>
+        <v>4.4</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.17</v>
+        <v>18.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.17</v>
+        <v>20</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.17</v>
+        <v>4.5</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.55</v>
+        <v>16</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G44" t="n">
         <v>1.88</v>
@@ -8914,82 +8914,82 @@
         <v>4.9</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
         <v>3.55</v>
       </c>
       <c r="K44" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M44" t="n">
         <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O44" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T44" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="U44" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="V44" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W44" t="n">
         <v>2.12</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB44" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -8998,77 +8998,77 @@
         <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL44" t="n">
         <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>26</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.56</v>
+        <v>10.5</v>
       </c>
       <c r="AT44" t="n">
         <v>6.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.32</v>
+        <v>7.4</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.48</v>
+        <v>10</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="BB44" t="n">
         <v>15.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.56</v>
+        <v>7.8</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.42</v>
+        <v>9</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.56</v>
+        <v>10.5</v>
       </c>
       <c r="BF44" t="n">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.56</v>
+        <v>10.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -9099,61 +9099,61 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="G45" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K45" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="L45" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M45" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="O45" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="P45" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="R45" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S45" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="V45" t="n">
         <v>1.16</v>
       </c>
       <c r="W45" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X45" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
         <v>1000</v>
@@ -9165,13 +9165,13 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
         <v>42</v>
       </c>
       <c r="AD45" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AE45" t="n">
         <v>1000</v>
@@ -9201,68 +9201,68 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ45" t="n">
         <v>8.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AT45" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU45" t="n">
         <v>5.1</v>
       </c>
       <c r="AV45" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AX45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY45" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AZ45" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="BB45" t="n">
-        <v>2.7</v>
+        <v>1.87</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="BF45" t="n">
         <v>4</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -9293,85 +9293,85 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H46" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="J46" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="K46" t="n">
-        <v>500</v>
+        <v>3.6</v>
       </c>
       <c r="L46" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M46" t="n">
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P46" t="n">
         <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T46" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U46" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V46" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG46" t="n">
         <v>1000</v>
@@ -9383,80 +9383,80 @@
         <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN46" t="n">
         <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -9490,61 +9490,61 @@
         <v>3.7</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H47" t="n">
         <v>2.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J47" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K47" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="L47" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O47" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P47" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
         <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U47" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V47" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W47" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X47" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -9604,7 +9604,7 @@
         <v>12</v>
       </c>
       <c r="AS47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT47" t="n">
         <v>8</v>
@@ -9613,44 +9613,44 @@
         <v>6.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX47" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AZ47" t="n">
         <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB47" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC47" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BD47" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF47" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>3.15</v>
@@ -9690,37 +9690,37 @@
         <v>3.15</v>
       </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J48" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="K48" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O48" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="P48" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="S48" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="T48" t="n">
         <v>2.84</v>
@@ -9729,13 +9729,13 @@
         <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W48" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X48" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y48" t="n">
         <v>7.4</v>
@@ -9747,22 +9747,22 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC48" t="n">
         <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH48" t="n">
         <v>1000</v>
@@ -9798,10 +9798,10 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU48" t="n">
         <v>6.2</v>
@@ -9822,7 +9822,7 @@
         <v>24</v>
       </c>
       <c r="BA48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB48" t="n">
         <v>32</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.4</v>
+        <v>55</v>
       </c>
       <c r="BF48" t="n">
         <v>38</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -9878,64 +9878,64 @@
         <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I49" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J49" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M49" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="Q49" t="n">
         <v>2.3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S49" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T49" t="n">
         <v>1.95</v>
       </c>
       <c r="U49" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="V49" t="n">
         <v>1.58</v>
       </c>
       <c r="W49" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -9944,7 +9944,7 @@
         <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD49" t="n">
         <v>1000</v>
@@ -9974,7 +9974,7 @@
         <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN49" t="n">
         <v>1000</v>
@@ -9983,62 +9983,62 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.35</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW2" t="n">
         <v>30</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AX2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>17</v>
       </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
         <v>32</v>
       </c>
-      <c r="AK2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BC2" t="n">
         <v>27</v>
       </c>
-      <c r="AX2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BG2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3" t="n">
         <v>2.78</v>
@@ -984,7 +984,7 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -993,19 +993,19 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
         <v>60</v>
@@ -1017,13 +1017,13 @@
         <v>250</v>
       </c>
       <c r="AB3" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>250</v>
@@ -1032,7 +1032,7 @@
         <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="n">
         <v>65</v>
@@ -1044,7 +1044,7 @@
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AL3" t="n">
         <v>250</v>
@@ -1059,7 +1059,7 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.6</v>
@@ -1071,16 +1071,16 @@
         <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
         <v>8.4</v>
@@ -1092,29 +1092,29 @@
         <v>9.6</v>
       </c>
       <c r="BA3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>18</v>
-      </c>
       <c r="BC3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
         <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1145,34 +1145,34 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="P4" t="n">
         <v>1.33</v>
@@ -1184,25 +1184,25 @@
         <v>1.11</v>
       </c>
       <c r="S4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
         <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
@@ -1223,7 +1223,7 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG4" t="n">
         <v>1000</v>
@@ -1253,28 +1253,28 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>2.86</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.65</v>
+        <v>2.86</v>
       </c>
       <c r="AX4" t="n">
         <v>6.6</v>
@@ -1283,32 +1283,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG4" t="n">
         <v>2.64</v>
       </c>
-      <c r="BG4" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>6.2</v>
@@ -1363,37 +1363,37 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
         <v>2.32</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
         <v>26</v>
@@ -1414,7 +1414,7 @@
         <v>23</v>
       </c>
       <c r="AE5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
         <v>12.5</v>
@@ -1423,10 +1423,10 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
@@ -1438,7 +1438,7 @@
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>7.6</v>
@@ -1447,62 +1447,62 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5</v>
-      </c>
       <c r="AU5" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.79</v>
       </c>
       <c r="G6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
         <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.45</v>
@@ -1563,7 +1563,7 @@
         <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
@@ -1575,7 +1575,7 @@
         <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
         <v>1.92</v>
@@ -1584,16 +1584,16 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AA6" t="n">
         <v>700</v>
@@ -1611,7 +1611,7 @@
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1620,7 +1620,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="AJ6" t="n">
         <v>21</v>
@@ -1635,7 +1635,7 @@
         <v>700</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,13 +1644,13 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.8</v>
@@ -1671,10 +1671,10 @@
         <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
         <v>16.5</v>
@@ -1683,20 +1683,20 @@
         <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1727,61 +1727,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.76</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.78</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.97</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.04</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.08</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.88</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.79</v>
+        <v>2.68</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="X8" t="n">
         <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,31 +1987,31 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AK8" t="n">
         <v>18.5</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.29</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.31</v>
-      </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>6.8</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2157,40 +2157,40 @@
         <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="X9" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="Y9" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA9" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AE9" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF9" t="n">
         <v>8.800000000000001</v>
@@ -2205,49 +2205,49 @@
         <v>460</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="n">
         <v>13.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="AN9" t="n">
         <v>4.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AP9" t="n">
         <v>30</v>
       </c>
       <c r="AQ9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
         <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AW9" t="n">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
@@ -2256,29 +2256,29 @@
         <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9" t="n">
         <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K10" t="n">
         <v>5.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>1.23</v>
@@ -2333,34 +2333,34 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
         <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X10" t="n">
         <v>42</v>
@@ -2375,10 +2375,10 @@
         <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>23</v>
@@ -2393,25 +2393,25 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
         <v>13</v>
       </c>
       <c r="AL10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO10" t="n">
         <v>44</v>
@@ -2432,7 +2432,7 @@
         <v>16</v>
       </c>
       <c r="AU10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
         <v>22</v>
@@ -2447,13 +2447,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
         <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
@@ -2465,14 +2465,14 @@
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
         <v>38</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -2530,7 +2530,7 @@
         <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
         <v>2.24</v>
@@ -2542,10 +2542,10 @@
         <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
         <v>2.28</v>
@@ -2554,13 +2554,13 @@
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>75</v>
@@ -2614,10 +2614,10 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>12</v>
@@ -2632,7 +2632,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -2644,7 +2644,7 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2703,19 +2703,19 @@
         <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2724,7 +2724,7 @@
         <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
         <v>2.2</v>
@@ -2739,10 +2739,10 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V12" t="n">
         <v>1.36</v>
@@ -2751,28 +2751,28 @@
         <v>1.84</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
         <v>15.5</v>
@@ -2796,7 +2796,7 @@
         <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN12" t="n">
         <v>13.5</v>
@@ -2805,28 +2805,28 @@
         <v>34</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -2838,7 +2838,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BB12" t="n">
         <v>12.5</v>
@@ -2847,20 +2847,20 @@
         <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I13" t="n">
         <v>6.6</v>
       </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.5</v>
@@ -2915,146 +2915,146 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA13" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="n">
         <v>6.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AF13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AJ13" t="n">
         <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AS13" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
         <v>22</v>
       </c>
       <c r="AW13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD13" t="n">
         <v>42</v>
       </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>23</v>
-      </c>
       <c r="BE13" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="U14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="X14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>32</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.18</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.22</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.21</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.22</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.19</v>
+        <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.21</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.22</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.22</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.21</v>
+        <v>13</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.21</v>
+        <v>17.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.22</v>
+        <v>12.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.22</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.55</v>
+        <v>17</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H15" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="J15" t="n">
         <v>3.2</v>
@@ -3297,7 +3297,7 @@
         <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -3306,13 +3306,13 @@
         <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
@@ -3321,10 +3321,10 @@
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3336,40 +3336,40 @@
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
         <v>85</v>
@@ -3381,43 +3381,43 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT15" t="n">
         <v>9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
         <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
         <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
@@ -3432,17 +3432,17 @@
         <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG15" t="n">
         <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
         <v>7.2</v>
@@ -3512,16 +3512,16 @@
         <v>1.92</v>
       </c>
       <c r="S16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
         <v>4.3</v>
@@ -3545,10 +3545,10 @@
         <v>18</v>
       </c>
       <c r="AD16" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AE16" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -3572,25 +3572,25 @@
         <v>29</v>
       </c>
       <c r="AM16" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AO16" t="n">
         <v>120</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>130</v>
       </c>
       <c r="AP16" t="n">
         <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -3599,10 +3599,10 @@
         <v>14.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -3614,7 +3614,7 @@
         <v>23</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB16" t="n">
         <v>10</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
         <v>20</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BG16" t="n">
         <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.26</v>
@@ -3691,40 +3691,40 @@
         <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.16</v>
       </c>
       <c r="P17" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="U17" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -3733,40 +3733,40 @@
         <v>470</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
         <v>110</v>
       </c>
       <c r="AE17" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
         <v>22</v>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN17" t="n">
         <v>7.2</v>
@@ -3775,7 +3775,7 @@
         <v>290</v>
       </c>
       <c r="AP17" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
@@ -3808,7 +3808,7 @@
         <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
         <v>18</v>
@@ -3817,20 +3817,20 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BF17" t="n">
         <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
         <v>4.3</v>
@@ -3894,10 +3894,10 @@
         <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
         <v>2.78</v>
@@ -3909,10 +3909,10 @@
         <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3921,7 +3921,7 @@
         <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="AA18" t="n">
         <v>700</v>
@@ -3933,7 +3933,7 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>190</v>
@@ -3945,7 +3945,7 @@
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>170</v>
@@ -3966,43 +3966,43 @@
         <v>8.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
         <v>14.5</v>
@@ -4011,20 +4011,20 @@
         <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
         <v>3.9</v>
@@ -4070,7 +4070,7 @@
         <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -4079,34 +4079,34 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V19" t="n">
         <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X19" t="n">
         <v>80</v>
@@ -4121,13 +4121,13 @@
         <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
         <v>36</v>
@@ -4139,7 +4139,7 @@
         <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>85</v>
@@ -4148,43 +4148,43 @@
         <v>120</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="AN19" t="n">
         <v>8.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
         <v>14.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
         <v>14.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
@@ -4193,32 +4193,32 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB19" t="n">
         <v>24</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BC19" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC19" t="n">
-        <v>16</v>
-      </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="BE19" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4252,167 +4252,167 @@
         <v>6.2</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I20" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.48</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="U20" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="V20" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="W20" t="n">
         <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AB20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD20" t="n">
         <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
         <v>48</v>
       </c>
       <c r="AG20" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
         <v>210</v>
       </c>
       <c r="AK20" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL20" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AO20" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>42</v>
       </c>
       <c r="AY20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BD20" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BF20" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4443,37 +4443,37 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G21" t="n">
         <v>3.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I21" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
         <v>2.14</v>
@@ -4482,22 +4482,22 @@
         <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
         <v>10.5</v>
@@ -4515,7 +4515,7 @@
         <v>7.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>32</v>
@@ -4527,13 +4527,13 @@
         <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AK21" t="n">
         <v>36</v>
@@ -4545,31 +4545,31 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>28</v>
@@ -4581,32 +4581,32 @@
         <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC21" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF21" t="n">
         <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>3.05</v>
@@ -4655,7 +4655,7 @@
         <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M22" t="n">
         <v>1.11</v>
@@ -4673,34 +4673,34 @@
         <v>2.36</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
         <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB22" t="n">
         <v>9.199999999999999</v>
@@ -4709,7 +4709,7 @@
         <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>46</v>
@@ -4718,7 +4718,7 @@
         <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -4745,19 +4745,19 @@
         <v>50</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4766,13 +4766,13 @@
         <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
@@ -4790,17 +4790,17 @@
         <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BF22" t="n">
         <v>26</v>
       </c>
       <c r="BG22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
         <v>3.25</v>
@@ -4861,10 +4861,10 @@
         <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
@@ -4906,7 +4906,7 @@
         <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF23" t="n">
         <v>16</v>
@@ -4969,7 +4969,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA23" t="n">
         <v>40</v>
@@ -4984,7 +4984,7 @@
         <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF23" t="n">
         <v>19.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K24" t="n">
         <v>6.8</v>
@@ -5049,16 +5049,16 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
         <v>1.58</v>
@@ -5070,7 +5070,7 @@
         <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V24" t="n">
         <v>1.07</v>
@@ -5088,10 +5088,10 @@
         <v>130</v>
       </c>
       <c r="AA24" t="n">
-        <v>640</v>
+        <v>580</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
         <v>14</v>
@@ -5100,7 +5100,7 @@
         <v>46</v>
       </c>
       <c r="AE24" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AF24" t="n">
         <v>7.8</v>
@@ -5115,10 +5115,10 @@
         <v>180</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL24" t="n">
         <v>42</v>
@@ -5130,34 +5130,34 @@
         <v>4.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR24" t="n">
         <v>28</v>
       </c>
       <c r="AS24" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>12.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW24" t="n">
         <v>22</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
@@ -5166,7 +5166,7 @@
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>8.800000000000001</v>
@@ -5184,11 +5184,11 @@
         <v>4.3</v>
       </c>
       <c r="BG24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G25" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H25" t="n">
         <v>10</v>
@@ -5231,40 +5231,40 @@
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="R25" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.09</v>
@@ -5273,10 +5273,10 @@
         <v>3.55</v>
       </c>
       <c r="X25" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z25" t="n">
         <v>540</v>
@@ -5285,10 +5285,10 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD25" t="n">
         <v>40</v>
@@ -5297,10 +5297,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>29</v>
@@ -5309,58 +5309,58 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK25" t="n">
         <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>9.4</v>
@@ -5372,17 +5372,17 @@
         <v>18</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="H26" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="I26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.44</v>
@@ -5437,76 +5437,76 @@
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>42</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
       </c>
       <c r="AR26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD26" t="n">
         <v>21</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="BE26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG26" t="n">
         <v>10</v>
       </c>
-      <c r="AT26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>2.68</v>
       </c>
       <c r="G27" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H27" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1.37</v>
@@ -5640,7 +5640,7 @@
         <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
         <v>1.44</v>
@@ -5649,7 +5649,7 @@
         <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U27" t="n">
         <v>2.28</v>
@@ -5697,7 +5697,7 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
@@ -5706,7 +5706,7 @@
         <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
         <v>55</v>
@@ -5715,62 +5715,62 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV27" t="n">
         <v>6.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ27" t="n">
         <v>9</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BF27" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5816,37 +5816,37 @@
         <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
         <v>1.29</v>
@@ -5855,10 +5855,10 @@
         <v>1.86</v>
       </c>
       <c r="X28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
         <v>32</v>
@@ -5867,16 +5867,16 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="n">
         <v>13</v>
@@ -5885,7 +5885,7 @@
         <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>170</v>
@@ -5894,19 +5894,19 @@
         <v>27</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AP28" t="n">
         <v>9.800000000000001</v>
@@ -5918,7 +5918,7 @@
         <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -5930,7 +5930,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -5942,29 +5942,29 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BG28" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G29" t="n">
         <v>4.1</v>
       </c>
       <c r="H29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I29" t="n">
         <v>2.14</v>
@@ -6010,10 +6010,10 @@
         <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -6028,19 +6028,19 @@
         <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
         <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U29" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V29" t="n">
         <v>1.89</v>
@@ -6061,7 +6061,7 @@
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
         <v>12</v>
@@ -6070,7 +6070,7 @@
         <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AF29" t="n">
         <v>90</v>
@@ -6079,7 +6079,7 @@
         <v>970</v>
       </c>
       <c r="AH29" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
         <v>160</v>
@@ -6097,7 +6097,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="AO29" t="n">
         <v>55</v>
@@ -6106,28 +6106,28 @@
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
         <v>9</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
@@ -6136,29 +6136,29 @@
         <v>9</v>
       </c>
       <c r="BA29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC29" t="n">
+      <c r="BE29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF29" t="n">
         <v>10</v>
       </c>
-      <c r="BD29" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G30" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I30" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J30" t="n">
         <v>3.85</v>
@@ -6225,13 +6225,13 @@
         <v>1.52</v>
       </c>
       <c r="R30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T30" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="U30" t="n">
         <v>2.72</v>
@@ -6252,7 +6252,7 @@
         <v>24</v>
       </c>
       <c r="AA30" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
         <v>19</v>
@@ -6294,7 +6294,7 @@
         <v>13.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
@@ -6342,7 +6342,7 @@
         <v>14.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF30" t="n">
         <v>11</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6383,28 +6383,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G31" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I31" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
         <v>3.1</v>
@@ -6416,31 +6416,31 @@
         <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="V31" t="n">
         <v>1.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
         <v>26</v>
       </c>
       <c r="Y31" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
         <v>970</v>
@@ -6449,7 +6449,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>14</v>
@@ -6476,10 +6476,10 @@
         <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL31" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6491,28 +6491,28 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
         <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX31" t="n">
         <v>9</v>
@@ -6524,29 +6524,29 @@
         <v>9</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>6.2</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>5.8</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.25</v>
@@ -6610,7 +6610,7 @@
         <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R32" t="n">
         <v>1.86</v>
@@ -6622,13 +6622,13 @@
         <v>1.68</v>
       </c>
       <c r="U32" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V32" t="n">
         <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X32" t="n">
         <v>36</v>
@@ -6643,7 +6643,7 @@
         <v>160</v>
       </c>
       <c r="AB32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC32" t="n">
         <v>13.5</v>
@@ -6652,7 +6652,7 @@
         <v>23</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF32" t="n">
         <v>11.5</v>
@@ -6679,10 +6679,10 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP32" t="n">
         <v>32</v>
@@ -6697,7 +6697,7 @@
         <v>130</v>
       </c>
       <c r="AT32" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU32" t="n">
         <v>13</v>
@@ -6706,7 +6706,7 @@
         <v>22</v>
       </c>
       <c r="AW32" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6736,11 +6736,11 @@
         <v>4.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>1.31</v>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I33" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J33" t="n">
         <v>6.6</v>
@@ -6807,22 +6807,22 @@
         <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T33" t="n">
         <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
         <v>1.08</v>
       </c>
       <c r="W33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X33" t="n">
         <v>22</v>
@@ -6831,7 +6831,7 @@
         <v>34</v>
       </c>
       <c r="Z33" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
@@ -6855,34 +6855,34 @@
         <v>10.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI33" t="n">
         <v>190</v>
       </c>
       <c r="AJ33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL33" t="n">
         <v>44</v>
       </c>
       <c r="AM33" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN33" t="n">
         <v>5.1</v>
       </c>
       <c r="AO33" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR33" t="n">
         <v>100</v>
@@ -6897,10 +6897,10 @@
         <v>13.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AW33" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AX33" t="n">
         <v>6.8</v>
@@ -6912,29 +6912,29 @@
         <v>34</v>
       </c>
       <c r="BA33" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="BB33" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC33" t="n">
         <v>13.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BF33" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
         <v>3.2</v>
@@ -6977,10 +6977,10 @@
         <v>3.25</v>
       </c>
       <c r="J34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.26</v>
@@ -6992,7 +6992,7 @@
         <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
@@ -7001,10 +7001,10 @@
         <v>1.48</v>
       </c>
       <c r="R34" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T34" t="n">
         <v>1.49</v>
@@ -7013,10 +7013,10 @@
         <v>2.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W34" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>32</v>
@@ -7052,7 +7052,7 @@
         <v>14.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ34" t="n">
         <v>27</v>
@@ -7064,7 +7064,7 @@
         <v>23</v>
       </c>
       <c r="AM34" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN34" t="n">
         <v>8.4</v>
@@ -7118,7 +7118,7 @@
         <v>22</v>
       </c>
       <c r="BE34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF34" t="n">
         <v>8.199999999999999</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>8.4</v>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J35" t="n">
         <v>3.55</v>
@@ -7177,7 +7177,7 @@
         <v>4.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
         <v>1.13</v>
@@ -7192,7 +7192,7 @@
         <v>1.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
@@ -7240,7 +7240,7 @@
         <v>11.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AH35" t="n">
         <v>1000</v>
@@ -7267,13 +7267,13 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR35" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AS35" t="n">
         <v>4.2</v>
@@ -7282,47 +7282,47 @@
         <v>4.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AW35" t="n">
         <v>4.2</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY35" t="n">
         <v>7</v>
       </c>
       <c r="AZ35" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA35" t="n">
         <v>4.2</v>
       </c>
       <c r="BB35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF35" t="n">
         <v>6.4</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>11</v>
       </c>
       <c r="BG35" t="n">
         <v>4.2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7353,31 +7353,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="G36" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="H36" t="n">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="I36" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="K36" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.42</v>
@@ -7386,31 +7386,31 @@
         <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
         <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="X36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y36" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,104 +7419,104 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>10.5</v>
       </c>
       <c r="AK36" t="n">
         <v>20</v>
       </c>
       <c r="AL36" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AR36" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS36" t="n">
         <v>8.6</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW36" t="n">
         <v>8.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC36" t="n">
         <v>16</v>
       </c>
       <c r="BD36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7550,43 +7550,43 @@
         <v>2.66</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K37" t="n">
         <v>3.25</v>
       </c>
       <c r="L37" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="M37" t="n">
         <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="O37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P37" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
         <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T37" t="n">
         <v>2.08</v>
@@ -7595,7 +7595,7 @@
         <v>1.73</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W37" t="n">
         <v>1.55</v>
@@ -7655,22 +7655,22 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AS37" t="n">
         <v>7.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU37" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
         <v>5.9</v>
@@ -7679,13 +7679,13 @@
         <v>7.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
         <v>7.8</v>
@@ -7694,23 +7694,23 @@
         <v>7.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD37" t="n">
         <v>7.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF37" t="n">
         <v>7.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7741,61 +7741,61 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G38" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N38" t="n">
         <v>3.5</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O38" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P38" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="U38" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="n">
         <v>48</v>
@@ -7807,10 +7807,10 @@
         <v>700</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD38" t="n">
         <v>100</v>
@@ -7819,13 +7819,13 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AG38" t="n">
         <v>32</v>
       </c>
       <c r="AH38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI38" t="n">
         <v>700</v>
@@ -7834,7 +7834,7 @@
         <v>130</v>
       </c>
       <c r="AK38" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AL38" t="n">
         <v>290</v>
@@ -7843,13 +7843,13 @@
         <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>12</v>
@@ -7858,31 +7858,31 @@
         <v>14.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV38" t="n">
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AX38" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY38" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
         <v>14.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7891,20 +7891,20 @@
         <v>11.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BE38" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG38" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
         <v>3.2</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.54</v>
@@ -7968,19 +7968,19 @@
         <v>1.59</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
         <v>4.8</v>
       </c>
       <c r="T39" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V39" t="n">
         <v>1.89</v>
@@ -8001,37 +8001,37 @@
         <v>27</v>
       </c>
       <c r="AB39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC39" t="n">
         <v>8</v>
       </c>
       <c r="AD39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF39" t="n">
         <v>34</v>
       </c>
       <c r="AG39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI39" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK39" t="n">
         <v>500</v>
       </c>
       <c r="AL39" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -8043,16 +8043,16 @@
         <v>25</v>
       </c>
       <c r="AP39" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR39" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT39" t="n">
         <v>10.5</v>
@@ -8064,7 +8064,7 @@
         <v>9.4</v>
       </c>
       <c r="AW39" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
@@ -8073,32 +8073,32 @@
         <v>16</v>
       </c>
       <c r="AZ39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG39" t="n">
         <v>20</v>
       </c>
-      <c r="BA39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>18</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G40" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H40" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I40" t="n">
         <v>6.6</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K40" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L40" t="n">
         <v>1.45</v>
@@ -8153,13 +8153,13 @@
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O40" t="n">
         <v>1.36</v>
       </c>
       <c r="P40" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q40" t="n">
         <v>2.1</v>
@@ -8168,19 +8168,19 @@
         <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T40" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X40" t="n">
         <v>12.5</v>
@@ -8189,13 +8189,13 @@
         <v>75</v>
       </c>
       <c r="Z40" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AA40" t="n">
         <v>900</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC40" t="n">
         <v>8.4</v>
@@ -8207,7 +8207,7 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG40" t="n">
         <v>17.5</v>
@@ -8219,7 +8219,7 @@
         <v>700</v>
       </c>
       <c r="AJ40" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AK40" t="n">
         <v>42</v>
@@ -8243,7 +8243,7 @@
         <v>15.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AS40" t="n">
         <v>11.5</v>
@@ -8258,7 +8258,7 @@
         <v>17.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AX40" t="n">
         <v>8.4</v>
@@ -8273,7 +8273,7 @@
         <v>11</v>
       </c>
       <c r="BB40" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC40" t="n">
         <v>17</v>
@@ -8282,17 +8282,17 @@
         <v>19.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF40" t="n">
         <v>11</v>
       </c>
       <c r="BG40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -8323,58 +8323,58 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G41" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="I41" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J41" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
         <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P41" t="n">
         <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R41" t="n">
         <v>1.2</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T41" t="n">
         <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W41" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X41" t="n">
         <v>9.4</v>
@@ -8383,13 +8383,13 @@
         <v>9.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC41" t="n">
         <v>7.4</v>
@@ -8398,13 +8398,13 @@
         <v>13.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
         <v>22</v>
       </c>
       <c r="AG41" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="n">
         <v>23</v>
@@ -8440,10 +8440,10 @@
         <v>13.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU41" t="n">
         <v>6.2</v>
@@ -8452,41 +8452,41 @@
         <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AY41" t="n">
         <v>12</v>
       </c>
       <c r="AZ41" t="n">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BA41" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC41" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF41" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF41" t="n">
-        <v>7</v>
-      </c>
       <c r="BG41" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
         <v>46</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU42" t="n">
         <v>7.4</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -8711,170 +8711,170 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H43" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="K43" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L43" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M43" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X43" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT43" t="n">
         <v>1.38</v>
       </c>
-      <c r="P43" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AU43" t="n">
-        <v>6.4</v>
+        <v>1.32</v>
       </c>
       <c r="AV43" t="n">
-        <v>16</v>
+        <v>1.42</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.3</v>
+        <v>1.45</v>
       </c>
       <c r="AX43" t="n">
-        <v>10</v>
+        <v>1.43</v>
       </c>
       <c r="AY43" t="n">
-        <v>8.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>14</v>
+        <v>1.42</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.4</v>
+        <v>1.45</v>
       </c>
       <c r="BB43" t="n">
-        <v>18.5</v>
+        <v>1.45</v>
       </c>
       <c r="BC43" t="n">
-        <v>20</v>
+        <v>1.43</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.2</v>
+        <v>1.44</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF43" t="n">
-        <v>16</v>
+        <v>1.55</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G44" t="n">
         <v>1.88</v>
       </c>
       <c r="H44" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L44" t="n">
         <v>1.46</v>
@@ -8935,25 +8935,25 @@
         <v>1.38</v>
       </c>
       <c r="P44" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
         <v>2.12</v>
       </c>
       <c r="R44" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T44" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U44" t="n">
         <v>1.91</v>
       </c>
       <c r="V44" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W44" t="n">
         <v>2.12</v>
@@ -8968,10 +8968,10 @@
         <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC44" t="n">
         <v>8.4</v>
@@ -8983,13 +8983,13 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG44" t="n">
         <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -9004,10 +9004,10 @@
         <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
@@ -9019,10 +9019,10 @@
         <v>11.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT44" t="n">
         <v>6.8</v>
@@ -9031,10 +9031,10 @@
         <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX44" t="n">
         <v>9.4</v>
@@ -9043,32 +9043,32 @@
         <v>9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB44" t="n">
         <v>15.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE44" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF44" t="n">
         <v>11</v>
       </c>
       <c r="BG44" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -9102,55 +9102,55 @@
         <v>1.68</v>
       </c>
       <c r="G45" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H45" t="n">
         <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
         <v>3.9</v>
       </c>
       <c r="L45" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R45" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V45" t="n">
         <v>1.16</v>
       </c>
       <c r="W45" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9192,7 +9192,7 @@
         <v>900</v>
       </c>
       <c r="AK45" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL45" t="n">
         <v>1000</v>
@@ -9201,7 +9201,7 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
@@ -9213,13 +9213,13 @@
         <v>8.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AT45" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU45" t="n">
         <v>5.1</v>
@@ -9228,41 +9228,41 @@
         <v>7.4</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="AX45" t="n">
         <v>4.9</v>
       </c>
       <c r="AY45" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AZ45" t="n">
         <v>7.2</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="BF45" t="n">
         <v>4</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G46" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H46" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I46" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J46" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K46" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L46" t="n">
         <v>1.55</v>
@@ -9317,7 +9317,7 @@
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
         <v>1.5</v>
@@ -9326,7 +9326,7 @@
         <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R46" t="n">
         <v>1.21</v>
@@ -9335,7 +9335,7 @@
         <v>5.1</v>
       </c>
       <c r="T46" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U46" t="n">
         <v>1.72</v>
@@ -9344,7 +9344,7 @@
         <v>2.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X46" t="n">
         <v>9.800000000000001</v>
@@ -9371,7 +9371,7 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
         <v>1000</v>
@@ -9383,13 +9383,13 @@
         <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK46" t="n">
         <v>120</v>
       </c>
       <c r="AL46" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM46" t="n">
         <v>240</v>
@@ -9410,7 +9410,7 @@
         <v>8.6</v>
       </c>
       <c r="AS46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT46" t="n">
         <v>11.5</v>
@@ -9428,7 +9428,7 @@
         <v>7.4</v>
       </c>
       <c r="AY46" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ46" t="n">
         <v>21</v>
@@ -9437,26 +9437,26 @@
         <v>40</v>
       </c>
       <c r="BB46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC46" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC46" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE46" t="n">
         <v>8.6</v>
       </c>
       <c r="BF46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG46" t="n">
         <v>16</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G47" t="n">
         <v>3.9</v>
@@ -9496,7 +9496,7 @@
         <v>2.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J47" t="n">
         <v>2.88</v>
@@ -9517,7 +9517,7 @@
         <v>1.75</v>
       </c>
       <c r="P47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q47" t="n">
         <v>3.45</v>
@@ -9526,16 +9526,16 @@
         <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U47" t="n">
         <v>1.6</v>
       </c>
       <c r="V47" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W47" t="n">
         <v>1.34</v>
@@ -9595,7 +9595,7 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ47" t="n">
         <v>5.8</v>
@@ -9604,7 +9604,7 @@
         <v>12</v>
       </c>
       <c r="AS47" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT47" t="n">
         <v>8</v>
@@ -9613,25 +9613,25 @@
         <v>6.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW47" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX47" t="n">
         <v>6.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AZ47" t="n">
         <v>25</v>
       </c>
       <c r="BA47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB47" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC47" t="n">
         <v>7.6</v>
@@ -9640,17 +9640,17 @@
         <v>7.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF47" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -9681,37 +9681,37 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G48" t="n">
         <v>3.15</v>
       </c>
       <c r="H48" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I48" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K48" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="M48" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="N48" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O48" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="P48" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q48" t="n">
         <v>4.2</v>
@@ -9729,49 +9729,49 @@
         <v>1.44</v>
       </c>
       <c r="V48" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X48" t="n">
         <v>5.7</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="n">
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG48" t="n">
         <v>28</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK48" t="n">
         <v>1000</v>
@@ -9789,43 +9789,43 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ48" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR48" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AT48" t="n">
         <v>5.9</v>
       </c>
       <c r="AU48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV48" t="n">
         <v>16</v>
       </c>
       <c r="AW48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX48" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BA48" t="n">
         <v>44</v>
       </c>
       <c r="BB48" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BC48" t="n">
         <v>32</v>
@@ -9834,17 +9834,17 @@
         <v>44</v>
       </c>
       <c r="BE48" t="n">
-        <v>55</v>
+        <v>4.3</v>
       </c>
       <c r="BF48" t="n">
         <v>38</v>
       </c>
       <c r="BG48" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="I49" t="n">
         <v>2.72</v>
@@ -9890,7 +9890,7 @@
         <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L49" t="n">
         <v>1.49</v>
@@ -9905,22 +9905,22 @@
         <v>1.43</v>
       </c>
       <c r="P49" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R49" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S49" t="n">
         <v>4.4</v>
       </c>
       <c r="T49" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="U49" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V49" t="n">
         <v>1.58</v>
@@ -9929,13 +9929,13 @@
         <v>1.47</v>
       </c>
       <c r="X49" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z49" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
         <v>1000</v>
@@ -9944,7 +9944,7 @@
         <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD49" t="n">
         <v>1000</v>
@@ -9983,16 +9983,16 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ49" t="n">
         <v>7.8</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS49" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT49" t="n">
         <v>8.800000000000001</v>
@@ -10001,44 +10001,44 @@
         <v>6.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX49" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>5.9</v>
       </c>
       <c r="AY49" t="n">
         <v>11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA49" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB49" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC49" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD49" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE49" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF49" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF49" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG49" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH48"/>
+  <dimension ref="A1:BH49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.54</v>
@@ -781,16 +781,16 @@
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
         <v>1.49</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.22</v>
@@ -799,128 +799,128 @@
         <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF2" t="n">
         <v>16</v>
       </c>
-      <c r="BA2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>21</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="L3" t="n">
         <v>1.86</v>
@@ -975,10 +975,10 @@
         <v>1.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="P3" t="n">
         <v>1.33</v>
@@ -990,25 +990,25 @@
         <v>1.11</v>
       </c>
       <c r="S3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X3" t="n">
         <v>6.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AH3" t="n">
         <v>500</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BB3" t="n">
         <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>300</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>9</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE4" t="n">
         <v>110</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>28</v>
-      </c>
       <c r="BF4" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
         <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1369,22 +1369,22 @@
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
         <v>1.21</v>
@@ -1393,116 +1393,116 @@
         <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
         <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BF5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,10 @@
         <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.85</v>
@@ -1560,10 +1560,10 @@
         <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.64</v>
@@ -1575,10 +1575,10 @@
         <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V6" t="n">
         <v>1.32</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,13 +1641,13 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>4.8</v>
@@ -1677,26 +1677,26 @@
         <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.45</v>
+        <v>2.14</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L7" t="n">
         <v>1.39</v>
       </c>
-      <c r="H7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.11</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="W7" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
         <v>38</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1921,28 +1921,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
         <v>6.6</v>
@@ -1954,37 +1954,37 @@
         <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
         <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X8" t="n">
         <v>32</v>
       </c>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z8" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
-        <v>640</v>
+        <v>460</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -1993,98 +1993,98 @@
         <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE8" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
         <v>13.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AP8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AR8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV8" t="n">
         <v>36</v>
       </c>
-      <c r="AS8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>38</v>
-      </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>95</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
         <v>5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -2142,19 +2142,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
         <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
         <v>1.59</v>
@@ -2163,22 +2163,22 @@
         <v>2.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
         <v>2.84</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
         <v>17</v>
@@ -2199,16 +2199,16 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL9" t="n">
         <v>24</v>
@@ -2220,49 +2220,49 @@
         <v>4.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
         <v>38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AT9" t="n">
         <v>16</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
         <v>50</v>
       </c>
       <c r="AX9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
         <v>23</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2336,13 +2336,13 @@
         <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
         <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
@@ -2354,52 +2354,52 @@
         <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
         <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG10" t="n">
         <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
         <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK10" t="n">
         <v>22</v>
@@ -2414,34 +2414,34 @@
         <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>15.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
         <v>9.6</v>
@@ -2453,26 +2453,26 @@
         <v>60</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
         <v>19.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE10" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>17.5</v>
+        <v>170</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.29</v>
@@ -2533,64 +2533,64 @@
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
         <v>1.54</v>
       </c>
       <c r="U11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB11" t="n">
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
         <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
         <v>32</v>
@@ -2599,74 +2599,74 @@
         <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AT11" t="n">
         <v>12</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
         <v>16.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
@@ -2730,70 +2730,70 @@
         <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y12" t="n">
         <v>19</v>
       </c>
-      <c r="Y12" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AA12" t="n">
         <v>330</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
         <v>200</v>
@@ -2805,28 +2805,28 @@
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2835,32 +2835,32 @@
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
         <v>2.18</v>
@@ -2939,122 +2939,122 @@
         <v>2.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="n">
         <v>14.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>29</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
         <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.86</v>
       </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3103,7 +3103,7 @@
         <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3118,10 +3118,10 @@
         <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
         <v>3.9</v>
@@ -3130,7 +3130,7 @@
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3142,16 +3142,16 @@
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
         <v>7.8</v>
@@ -3160,10 +3160,10 @@
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -3172,16 +3172,16 @@
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="n">
         <v>75</v>
       </c>
       <c r="AL14" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
@@ -3190,7 +3190,7 @@
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
         <v>9.800000000000001</v>
@@ -3199,13 +3199,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
@@ -3214,22 +3214,22 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
@@ -3238,17 +3238,17 @@
         <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3279,52 +3279,52 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
         <v>11.5</v>
       </c>
       <c r="J15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
         <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="R15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
         <v>1.09</v>
@@ -3336,7 +3336,7 @@
         <v>42</v>
       </c>
       <c r="Y15" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>150</v>
@@ -3345,104 +3345,104 @@
         <v>550</v>
       </c>
       <c r="AB15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC15" t="n">
         <v>17</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>16</v>
       </c>
       <c r="AD15" t="n">
         <v>40</v>
       </c>
       <c r="AE15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
         <v>130</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
         <v>13</v>
       </c>
       <c r="AL15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AO15" t="n">
         <v>110</v>
       </c>
       <c r="AP15" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>15.5</v>
       </c>
-      <c r="AS15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AV15" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC15" t="n">
         <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>4.4</v>
@@ -3503,7 +3503,7 @@
         <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q16" t="n">
         <v>1.49</v>
@@ -3515,10 +3515,10 @@
         <v>2.22</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U16" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="V16" t="n">
         <v>1.29</v>
@@ -3536,7 +3536,7 @@
         <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="n">
         <v>16</v>
@@ -3560,7 +3560,7 @@
         <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
@@ -3569,7 +3569,7 @@
         <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
@@ -3578,19 +3578,19 @@
         <v>7</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR16" t="n">
         <v>32</v>
       </c>
       <c r="AS16" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AT16" t="n">
         <v>13.5</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
@@ -3626,17 +3626,17 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="BF16" t="n">
         <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
         <v>1.62</v>
@@ -3682,7 +3682,7 @@
         <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3700,7 +3700,7 @@
         <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
         <v>1.55</v>
@@ -3712,19 +3712,19 @@
         <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>1.18</v>
       </c>
       <c r="W17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
         <v>55</v>
@@ -3733,16 +3733,16 @@
         <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AF17" t="n">
         <v>11</v>
@@ -3751,10 +3751,10 @@
         <v>10.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
         <v>15.5</v>
@@ -3763,22 +3763,22 @@
         <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>20</v>
@@ -3787,19 +3787,19 @@
         <v>48</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW17" t="n">
         <v>55</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
         <v>9.199999999999999</v>
@@ -3811,26 +3811,26 @@
         <v>50</v>
       </c>
       <c r="BB17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
         <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
         <v>50</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>3.95</v>
@@ -3894,115 +3894,115 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R18" t="n">
         <v>1.84</v>
       </c>
       <c r="S18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
         <v>1.87</v>
       </c>
       <c r="X18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z18" t="n">
         <v>34</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>38</v>
       </c>
       <c r="AA18" t="n">
         <v>75</v>
       </c>
       <c r="AB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="AE18" t="n">
         <v>36</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AM18" t="n">
         <v>55</v>
       </c>
       <c r="AN18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT18" t="n">
         <v>16</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW18" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>14.5</v>
@@ -4011,20 +4011,20 @@
         <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>6.2</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
         <v>1.75</v>
       </c>
       <c r="I19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>1.52</v>
@@ -4079,7 +4079,7 @@
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
         <v>1.47</v>
@@ -4103,16 +4103,16 @@
         <v>1.76</v>
       </c>
       <c r="V19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z19" t="n">
         <v>8.800000000000001</v>
@@ -4121,10 +4121,10 @@
         <v>17.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
@@ -4133,13 +4133,13 @@
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG19" t="n">
         <v>25</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
@@ -4160,7 +4160,7 @@
         <v>200</v>
       </c>
       <c r="AO19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP19" t="n">
         <v>9.4</v>
@@ -4172,10 +4172,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
@@ -4187,7 +4187,7 @@
         <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -4196,29 +4196,29 @@
         <v>24</v>
       </c>
       <c r="BA19" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG19" t="n">
         <v>14</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
         <v>17.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE20" t="n">
         <v>28</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H21" t="n">
         <v>3.2</v>
@@ -4455,10 +4455,10 @@
         <v>3.3</v>
       </c>
       <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.51</v>
@@ -4476,10 +4476,10 @@
         <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
         <v>4.5</v>
@@ -4488,16 +4488,16 @@
         <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y21" t="n">
         <v>10.5</v>
@@ -4509,19 +4509,19 @@
         <v>60</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE21" t="n">
         <v>42</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
         <v>12.5</v>
@@ -4548,22 +4548,22 @@
         <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>48</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
@@ -4575,7 +4575,7 @@
         <v>36</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY21" t="n">
         <v>11.5</v>
@@ -4584,7 +4584,7 @@
         <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>34</v>
@@ -4593,10 +4593,10 @@
         <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE21" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BF21" t="n">
         <v>29</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
         <v>2.58</v>
@@ -4661,7 +4661,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
@@ -4676,13 +4676,13 @@
         <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
         <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V22" t="n">
         <v>1.45</v>
@@ -4709,7 +4709,7 @@
         <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>36</v>
@@ -4718,7 +4718,7 @@
         <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
         <v>17</v>
@@ -4733,7 +4733,7 @@
         <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="n">
         <v>95</v>
@@ -4760,7 +4760,7 @@
         <v>9.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4775,7 +4775,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>40</v>
@@ -4790,7 +4790,7 @@
         <v>36</v>
       </c>
       <c r="BE22" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="BF22" t="n">
         <v>19.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H23" t="n">
         <v>13</v>
@@ -4843,13 +4843,13 @@
         <v>14.5</v>
       </c>
       <c r="J23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K23" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -4873,16 +4873,16 @@
         <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V23" t="n">
         <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
         <v>25</v>
@@ -4894,19 +4894,19 @@
         <v>130</v>
       </c>
       <c r="AA23" t="n">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="AB23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
         <v>48</v>
       </c>
       <c r="AE23" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF23" t="n">
         <v>8</v>
@@ -4921,7 +4921,7 @@
         <v>180</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
@@ -4936,19 +4936,19 @@
         <v>4.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AP23" t="n">
         <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>8.4</v>
@@ -4957,10 +4957,10 @@
         <v>13</v>
       </c>
       <c r="AV23" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AW23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>7.2</v>
@@ -4969,13 +4969,13 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BA23" t="n">
         <v>36</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
         <v>13</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF23" t="n">
         <v>4.3</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G24" t="n">
         <v>2.04</v>
@@ -5058,7 +5058,7 @@
         <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.31</v>
@@ -5094,16 +5094,16 @@
         <v>8.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
         <v>11</v>
@@ -5121,16 +5121,16 @@
         <v>23</v>
       </c>
       <c r="AL24" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>16.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
@@ -5139,13 +5139,13 @@
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
@@ -5166,7 +5166,7 @@
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB24" t="n">
         <v>19.5</v>
@@ -5184,11 +5184,11 @@
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G25" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H25" t="n">
         <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.32</v>
@@ -5249,19 +5249,19 @@
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
         <v>1.81</v>
@@ -5270,40 +5270,40 @@
         <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X25" t="n">
         <v>23</v>
       </c>
       <c r="Y25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5312,7 +5312,7 @@
         <v>11.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL25" t="n">
         <v>40</v>
@@ -5330,59 +5330,59 @@
         <v>18.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>7.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV25" t="n">
         <v>32</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
         <v>7.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB25" t="n">
         <v>9.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD25" t="n">
         <v>19</v>
       </c>
       <c r="BE25" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
         <v>4.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H26" t="n">
         <v>2.56</v>
@@ -5431,7 +5431,7 @@
         <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5467,52 +5467,52 @@
         <v>1.52</v>
       </c>
       <c r="X26" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
         <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH26" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ26" t="n">
         <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>55</v>
@@ -5524,28 +5524,28 @@
         <v>9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR26" t="n">
         <v>9</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
         <v>6.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
         <v>7.2</v>
@@ -5566,17 +5566,17 @@
         <v>16.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG26" t="n">
         <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G27" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.27</v>
@@ -5634,7 +5634,7 @@
         <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P27" t="n">
         <v>2.72</v>
@@ -5643,22 +5643,22 @@
         <v>1.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S27" t="n">
         <v>2.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.57</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.56</v>
       </c>
       <c r="X27" t="n">
         <v>70</v>
@@ -5685,7 +5685,7 @@
         <v>42</v>
       </c>
       <c r="AF27" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>13.5</v>
@@ -5697,7 +5697,7 @@
         <v>75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AK27" t="n">
         <v>25</v>
@@ -5712,7 +5712,7 @@
         <v>13.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5724,7 +5724,7 @@
         <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AT27" t="n">
         <v>15</v>
@@ -5751,7 +5751,7 @@
         <v>14.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BC27" t="n">
         <v>20</v>
@@ -5760,7 +5760,7 @@
         <v>14.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
         <v>11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5801,37 +5801,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G28" t="n">
         <v>4.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I28" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
         <v>1.8</v>
@@ -5840,19 +5840,19 @@
         <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U28" t="n">
         <v>2.28</v>
       </c>
       <c r="V28" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
         <v>48</v>
@@ -5894,10 +5894,10 @@
         <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL28" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5912,7 +5912,7 @@
         <v>9</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
         <v>7</v>
@@ -5927,7 +5927,7 @@
         <v>5.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW28" t="n">
         <v>10.5</v>
@@ -5945,7 +5945,7 @@
         <v>10</v>
       </c>
       <c r="BB28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
         <v>10.5</v>
@@ -5954,17 +5954,17 @@
         <v>12.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
         <v>4</v>
@@ -6007,7 +6007,7 @@
         <v>4.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
         <v>3.75</v>
@@ -6019,34 +6019,34 @@
         <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
         <v>1.87</v>
       </c>
       <c r="U29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
         <v>1.29</v>
       </c>
       <c r="W29" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>13</v>
@@ -6070,7 +6070,7 @@
         <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
@@ -6094,13 +6094,13 @@
         <v>120</v>
       </c>
       <c r="AM29" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN29" t="n">
         <v>19</v>
       </c>
       <c r="AO29" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP29" t="n">
         <v>9.800000000000001</v>
@@ -6112,7 +6112,7 @@
         <v>13</v>
       </c>
       <c r="AS29" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
         <v>7.4</v>
@@ -6136,7 +6136,7 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -6148,7 +6148,7 @@
         <v>20</v>
       </c>
       <c r="BE29" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF29" t="n">
         <v>15</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6189,64 +6189,64 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="n">
         <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I30" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
         <v>3.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X30" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
         <v>970</v>
@@ -6255,38 +6255,38 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AC30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE30" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="n">
         <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ30" t="n">
         <v>900</v>
       </c>
       <c r="AK30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL30" t="n">
         <v>500</v>
       </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ30" t="n">
         <v>6.2</v>
@@ -6306,7 +6306,7 @@
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
         <v>6.2</v>
@@ -6333,26 +6333,26 @@
         <v>20</v>
       </c>
       <c r="BB30" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC30" t="n">
         <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG30" t="n">
         <v>5.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.48</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.49</v>
       </c>
       <c r="H31" t="n">
         <v>6.2</v>
@@ -6395,34 +6395,34 @@
         <v>6.4</v>
       </c>
       <c r="J31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
         <v>6.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R31" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T31" t="n">
         <v>1.67</v>
@@ -6440,10 +6440,10 @@
         <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
         <v>160</v>
@@ -6464,13 +6464,13 @@
         <v>11.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
         <v>22</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
         <v>13.5</v>
@@ -6488,10 +6488,10 @@
         <v>4.4</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ31" t="n">
         <v>30</v>
@@ -6503,10 +6503,10 @@
         <v>130</v>
       </c>
       <c r="AT31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV31" t="n">
         <v>22</v>
@@ -6518,10 +6518,10 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>50</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>12.5</v>
       </c>
       <c r="I32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J32" t="n">
         <v>6.4</v>
@@ -6598,7 +6598,7 @@
         <v>1.34</v>
       </c>
       <c r="M32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N32" t="n">
         <v>4.8</v>
@@ -6619,10 +6619,10 @@
         <v>2.96</v>
       </c>
       <c r="T32" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
         <v>1.08</v>
@@ -6631,7 +6631,7 @@
         <v>4.2</v>
       </c>
       <c r="X32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y32" t="n">
         <v>34</v>
@@ -6652,7 +6652,7 @@
         <v>44</v>
       </c>
       <c r="AE32" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF32" t="n">
         <v>7.2</v>
@@ -6661,16 +6661,16 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI32" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK32" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
@@ -6682,7 +6682,7 @@
         <v>5.2</v>
       </c>
       <c r="AO32" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AP32" t="n">
         <v>20</v>
@@ -6694,53 +6694,53 @@
         <v>100</v>
       </c>
       <c r="AS32" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU32" t="n">
         <v>13.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW32" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY32" t="n">
         <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BA32" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BB32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD32" t="n">
         <v>42</v>
       </c>
       <c r="BE32" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG32" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G33" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H33" t="n">
         <v>3.1</v>
@@ -6789,43 +6789,43 @@
         <v>4.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.48</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.49</v>
-      </c>
       <c r="U33" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V33" t="n">
         <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y33" t="n">
         <v>21</v>
@@ -6837,34 +6837,34 @@
         <v>50</v>
       </c>
       <c r="AB33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC33" t="n">
         <v>11</v>
       </c>
       <c r="AD33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF33" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG33" t="n">
         <v>11.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ33" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK33" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
         <v>24</v>
@@ -6873,13 +6873,13 @@
         <v>48</v>
       </c>
       <c r="AN33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO33" t="n">
         <v>16</v>
       </c>
       <c r="AP33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ33" t="n">
         <v>20</v>
@@ -6891,7 +6891,7 @@
         <v>48</v>
       </c>
       <c r="AT33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU33" t="n">
         <v>10.5</v>
@@ -6900,10 +6900,10 @@
         <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX33" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY33" t="n">
         <v>11</v>
@@ -6915,7 +6915,7 @@
         <v>28</v>
       </c>
       <c r="BB33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC33" t="n">
         <v>18</v>
@@ -6930,11 +6930,11 @@
         <v>8.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>1.61</v>
       </c>
       <c r="H34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>11</v>
@@ -6989,7 +6989,7 @@
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.56</v>
@@ -7019,7 +7019,7 @@
         <v>2.62</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y34" t="n">
         <v>1000</v>
@@ -7031,7 +7031,7 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
@@ -7043,10 +7043,10 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AH34" t="n">
         <v>1000</v>
@@ -7055,10 +7055,10 @@
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
         <v>460</v>
@@ -7079,56 +7079,56 @@
         <v>9</v>
       </c>
       <c r="AR34" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT34" t="n">
         <v>4.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AZ34" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BB34" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G35" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H35" t="n">
         <v>12.5</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K35" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L35" t="n">
         <v>1.47</v>
@@ -7183,37 +7183,37 @@
         <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P35" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q35" t="n">
         <v>2.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="U35" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="V35" t="n">
         <v>1.07</v>
       </c>
       <c r="W35" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X35" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y35" t="n">
         <v>32</v>
@@ -7222,19 +7222,19 @@
         <v>140</v>
       </c>
       <c r="AA35" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD35" t="n">
         <v>60</v>
       </c>
       <c r="AE35" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="AF35" t="n">
         <v>6.6</v>
@@ -7246,7 +7246,7 @@
         <v>50</v>
       </c>
       <c r="AI35" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
         <v>10.5</v>
@@ -7258,25 +7258,25 @@
         <v>70</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AN35" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO35" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR35" t="n">
         <v>11</v>
       </c>
-      <c r="AQ35" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AS35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT35" t="n">
         <v>5.5</v>
@@ -7285,22 +7285,22 @@
         <v>10.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY35" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB35" t="n">
         <v>9.199999999999999</v>
@@ -7309,20 +7309,20 @@
         <v>16</v>
       </c>
       <c r="BD35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G36" t="n">
         <v>3.1</v>
@@ -7362,13 +7362,13 @@
         <v>3.05</v>
       </c>
       <c r="I36" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K36" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L36" t="n">
         <v>1.62</v>
@@ -7377,10 +7377,10 @@
         <v>1.14</v>
       </c>
       <c r="N36" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O36" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P36" t="n">
         <v>1.46</v>
@@ -7392,16 +7392,16 @@
         <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T36" t="n">
         <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V36" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W36" t="n">
         <v>1.48</v>
@@ -7431,7 +7431,7 @@
         <v>120</v>
       </c>
       <c r="AF36" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG36" t="n">
         <v>14.5</v>
@@ -7470,7 +7470,7 @@
         <v>16.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT36" t="n">
         <v>6.8</v>
@@ -7482,7 +7482,7 @@
         <v>12.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX36" t="n">
         <v>14.5</v>
@@ -7494,19 +7494,19 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD36" t="n">
         <v>29</v>
       </c>
       <c r="BE36" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF36" t="n">
         <v>36</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7547,61 +7547,61 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="G37" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H37" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J37" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L37" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P37" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V37" t="n">
         <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X37" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y37" t="n">
         <v>29</v>
@@ -7613,31 +7613,31 @@
         <v>700</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD37" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG37" t="n">
         <v>32</v>
       </c>
       <c r="AH37" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AI37" t="n">
         <v>700</v>
       </c>
       <c r="AJ37" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AK37" t="n">
         <v>70</v>
@@ -7649,37 +7649,37 @@
         <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AS37" t="n">
         <v>13.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV37" t="n">
         <v>18</v>
       </c>
       <c r="AW37" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
@@ -7688,10 +7688,10 @@
         <v>17.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BB37" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC37" t="n">
         <v>11.5</v>
@@ -7703,14 +7703,14 @@
         <v>46</v>
       </c>
       <c r="BF37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G38" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I38" t="n">
         <v>2.12</v>
@@ -7756,7 +7756,7 @@
         <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L38" t="n">
         <v>1.54</v>
@@ -7771,7 +7771,7 @@
         <v>1.48</v>
       </c>
       <c r="P38" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q38" t="n">
         <v>2.46</v>
@@ -7783,7 +7783,7 @@
         <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
         <v>1.79</v>
@@ -7792,19 +7792,19 @@
         <v>1.89</v>
       </c>
       <c r="W38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
         <v>10</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB38" t="n">
         <v>13</v>
@@ -7819,7 +7819,7 @@
         <v>28</v>
       </c>
       <c r="AF38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG38" t="n">
         <v>21</v>
@@ -7828,17 +7828,17 @@
         <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL38" t="n">
         <v>500</v>
       </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
@@ -7846,7 +7846,7 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP38" t="n">
         <v>8.4</v>
@@ -7855,16 +7855,16 @@
         <v>6.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS38" t="n">
         <v>21</v>
       </c>
       <c r="AT38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV38" t="n">
         <v>9.4</v>
@@ -7876,35 +7876,35 @@
         <v>18</v>
       </c>
       <c r="AY38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ38" t="n">
         <v>19.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB38" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD38" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE38" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF38" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG38" t="n">
         <v>20</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7935,19 +7935,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G39" t="n">
         <v>1.81</v>
       </c>
       <c r="H39" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I39" t="n">
         <v>6.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K39" t="n">
         <v>3.75</v>
@@ -7956,40 +7956,40 @@
         <v>1.45</v>
       </c>
       <c r="M39" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
         <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V39" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y39" t="n">
         <v>75</v>
@@ -8019,19 +8019,19 @@
         <v>17.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI39" t="n">
         <v>700</v>
       </c>
       <c r="AJ39" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AK39" t="n">
         <v>42</v>
       </c>
       <c r="AL39" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
         <v>580</v>
@@ -8049,7 +8049,7 @@
         <v>15.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="AS39" t="n">
         <v>12.5</v>
@@ -8070,10 +8070,10 @@
         <v>8.4</v>
       </c>
       <c r="AY39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA39" t="n">
         <v>11.5</v>
@@ -8085,10 +8085,10 @@
         <v>10.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BE39" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF39" t="n">
         <v>11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -8129,25 +8129,25 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J40" t="n">
         <v>3.05</v>
       </c>
-      <c r="G40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3</v>
-      </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M40" t="n">
         <v>1.12</v>
@@ -8156,10 +8156,10 @@
         <v>2.78</v>
       </c>
       <c r="O40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q40" t="n">
         <v>2.58</v>
@@ -8174,19 +8174,19 @@
         <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V40" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W40" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X40" t="n">
         <v>9.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z40" t="n">
         <v>17</v>
@@ -8207,7 +8207,7 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG40" t="n">
         <v>15</v>
@@ -8234,19 +8234,19 @@
         <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR40" t="n">
         <v>13.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT40" t="n">
         <v>8</v>
@@ -8255,44 +8255,44 @@
         <v>6.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY40" t="n">
         <v>12</v>
       </c>
       <c r="AZ40" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB40" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG40" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
@@ -8335,16 +8335,16 @@
         <v>6.4</v>
       </c>
       <c r="J41" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L41" t="n">
         <v>1.56</v>
       </c>
       <c r="M41" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N41" t="n">
         <v>2.82</v>
@@ -8353,7 +8353,7 @@
         <v>1.52</v>
       </c>
       <c r="P41" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q41" t="n">
         <v>2.6</v>
@@ -8365,7 +8365,7 @@
         <v>5.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U41" t="n">
         <v>1.71</v>
@@ -8374,19 +8374,19 @@
         <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z41" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AA41" t="n">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AB41" t="n">
         <v>6.2</v>
@@ -8395,31 +8395,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AE41" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH41" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI41" t="n">
         <v>700</v>
       </c>
       <c r="AJ41" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM41" t="n">
         <v>700</v>
@@ -8428,16 +8428,16 @@
         <v>17.5</v>
       </c>
       <c r="AO41" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AP41" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR41" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS41" t="n">
         <v>46</v>
@@ -8446,10 +8446,10 @@
         <v>5.7</v>
       </c>
       <c r="AU41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW41" t="n">
         <v>40</v>
@@ -8458,22 +8458,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA41" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB41" t="n">
         <v>16.5</v>
       </c>
       <c r="BC41" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE41" t="n">
         <v>110</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -8517,61 +8517,61 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="G42" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>1.49</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O42" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W42" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
         <v>14.5</v>
@@ -8580,114 +8580,114 @@
         <v>34</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG42" t="n">
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI42" t="n">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="AJ42" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT42" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG42" t="n">
         <v>10</v>
       </c>
-      <c r="AY42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,191 +8697,191 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G43" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K43" t="n">
         <v>3.55</v>
       </c>
-      <c r="K43" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L43" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T43" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="X43" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA43" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB43" t="n">
         <v>7.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF43" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ43" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AK43" t="n">
         <v>24</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="n">
         <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP43" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AS43" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AT43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU43" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU43" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV43" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW43" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX43" t="n">
         <v>9.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BA43" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB43" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BD43" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE43" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG43" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8896,70 +8896,70 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="H44" t="n">
+        <v>5</v>
+      </c>
+      <c r="I44" t="n">
         <v>5.7</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>3.55</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L44" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M44" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P44" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T44" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="U44" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="V44" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W44" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y44" t="n">
         <v>1000</v>
@@ -8968,28 +8968,28 @@
         <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG44" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -8998,84 +8998,84 @@
         <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="AL44" t="n">
         <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN44" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP44" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AQ44" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.58</v>
+        <v>9.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="AX44" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>2.06</v>
+        <v>9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.04</v>
+        <v>10.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.16</v>
+        <v>20</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.14</v>
+        <v>11.5</v>
       </c>
       <c r="BF44" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.93</v>
+        <v>11.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,191 +9085,191 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F45" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU45" t="n">
         <v>5.1</v>
       </c>
-      <c r="G45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K45" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="AV45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB45" t="n">
         <v>5.1</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X45" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX45" t="n">
+      <c r="BC45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE45" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY45" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF45" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG45" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,184 +9279,184 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="G46" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="H46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q46" t="n">
         <v>2.52</v>
       </c>
-      <c r="I46" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R46" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S46" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="T46" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U46" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V46" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU46" t="n">
         <v>7</v>
       </c>
-      <c r="Y46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV46" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AX46" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>21</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BA46" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG46" t="n">
         <v>16</v>
       </c>
-      <c r="AZ46" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -9478,103 +9478,103 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="G47" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="H47" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="J47" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="K47" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="N47" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="P47" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="V47" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="W47" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="X47" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC47" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z47" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD47" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AE47" t="n">
         <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ47" t="n">
         <v>1000</v>
@@ -9583,10 +9583,10 @@
         <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN47" t="n">
         <v>1000</v>
@@ -9595,69 +9595,69 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ47" t="n">
         <v>5.9</v>
       </c>
       <c r="AR47" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC47" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS47" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>48</v>
-      </c>
       <c r="BD47" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>38</v>
+        <v>4.4</v>
       </c>
       <c r="BG47" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9667,120 +9667,120 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I48" t="n">
         <v>3.2</v>
       </c>
-      <c r="H48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>2.68</v>
       </c>
-      <c r="J48" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K48" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="L48" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>1.97</v>
       </c>
       <c r="O48" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
 